--- a/AAII_Financials/Quarterly/CHPT_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CHPT_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
@@ -656,141 +656,145 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:U102"/>
+  <dimension ref="A5:V102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45230</v>
+      </c>
+      <c r="E7" s="2">
         <v>45138</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45046</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44957</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44865</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44773</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44681</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44592</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44500</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44408</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44316</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44227</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44135</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44012</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>43921</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43830</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43738</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43646</v>
       </c>
-      <c r="U7" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>110300</v>
+      </c>
+      <c r="E8" s="3">
         <v>150500</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>130000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>152800</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>125300</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>108300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>81600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>79300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>65000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>56100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>40500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>42400</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>36400</v>
       </c>
-      <c r="P8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q8" s="3" t="s">
         <v>3</v>
       </c>
@@ -800,56 +804,59 @@
       <c r="S8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T8" s="3">
-        <v>0</v>
+      <c r="T8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>92200</v>
+      </c>
+      <c r="E9" s="3">
         <v>121400</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>99500</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>119800</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>102700</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>90100</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>69500</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>61900</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>49000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>45300</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>31300</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>33500</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>29100</v>
       </c>
-      <c r="P9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q9" s="3" t="s">
         <v>3</v>
       </c>
@@ -865,50 +872,53 @@
       <c r="U9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>18100</v>
+      </c>
+      <c r="E10" s="3">
         <v>29100</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>30500</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>33000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>22600</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>18200</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>12100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>17400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>16000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>10800</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>9200</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>8900</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>7300</v>
       </c>
-      <c r="P10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q10" s="3" t="s">
         <v>3</v>
       </c>
@@ -924,8 +934,11 @@
       <c r="U10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -947,50 +960,51 @@
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
-    </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V11" s="3"/>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>56500</v>
+      </c>
+      <c r="E12" s="3">
         <v>59600</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>49400</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>46700</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>48100</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>51800</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>48300</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>42500</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>36800</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>40400</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>25400</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>20900</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>18900</v>
       </c>
-      <c r="P12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1006,8 +1020,11 @@
       <c r="U12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1065,17 +1082,20 @@
       <c r="U13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>42000</v>
+      </c>
+      <c r="E14" s="3">
         <v>28000</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="F14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1088,15 +1108,15 @@
       <c r="I14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J14" s="3">
+      <c r="J14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K14" s="3">
         <v>200</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>4800</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1109,8 +1129,8 @@
       <c r="P14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
+      <c r="Q14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R14" s="3">
         <v>0</v>
@@ -1124,8 +1144,11 @@
       <c r="U14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1183,8 +1206,11 @@
       <c r="U15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1203,109 +1229,113 @@
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
-    </row>
-    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V16" s="3"/>
+    </row>
+    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>264100</v>
+      </c>
+      <c r="E17" s="3">
         <v>273800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>210000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>231100</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>208600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>198700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>171500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>158600</v>
-      </c>
-      <c r="K17" s="3">
-        <v>130400</v>
       </c>
       <c r="L17" s="3">
         <v>130400</v>
       </c>
       <c r="M17" s="3">
+        <v>130400</v>
+      </c>
+      <c r="N17" s="3">
         <v>87100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>77700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>69000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>600</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>100</v>
       </c>
-      <c r="U17" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-153800</v>
+      </c>
+      <c r="E18" s="3">
         <v>-123300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-80000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-78300</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-83300</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-90400</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-89900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-79300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-65400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-74300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-46600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-35300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-32600</v>
       </c>
-      <c r="P18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1315,14 +1345,17 @@
       <c r="S18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T18" s="3">
+      <c r="T18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U18" s="3">
         <v>-100</v>
       </c>
-      <c r="U18" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1344,50 +1377,51 @@
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
-    </row>
-    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V19" s="3"/>
+    </row>
+    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="E20" s="3">
         <v>1900</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>3100</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>3200</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>1000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>200</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-300</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>16400</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-4400</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-10600</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>130400</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-54600</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-7400</v>
       </c>
-      <c r="P20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1397,56 +1431,59 @@
       <c r="S20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T20" s="3">
-        <v>0</v>
-      </c>
-      <c r="U20" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="T20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U20" s="3">
+        <v>0</v>
+      </c>
+      <c r="V20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-147600</v>
+      </c>
+      <c r="E21" s="3">
         <v>-114500</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-69800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-68700</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-76200</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-83900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-84000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-56600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-65200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-82000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>86600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-87300</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-37200</v>
       </c>
-      <c r="P21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1462,32 +1499,35 @@
       <c r="U21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>2900</v>
+        <v>3800</v>
       </c>
       <c r="E22" s="3">
         <v>2900</v>
       </c>
       <c r="F22" s="3">
+        <v>2900</v>
+      </c>
+      <c r="G22" s="3">
         <v>3000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>2600</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>2900</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>900</v>
       </c>
-      <c r="J22" s="3">
-        <v>0</v>
-      </c>
       <c r="K22" s="3">
         <v>0</v>
       </c>
@@ -1495,16 +1535,16 @@
         <v>0</v>
       </c>
       <c r="M22" s="3">
+        <v>0</v>
+      </c>
+      <c r="N22" s="3">
         <v>1500</v>
-      </c>
-      <c r="N22" s="3">
-        <v>800</v>
       </c>
       <c r="O22" s="3">
         <v>800</v>
       </c>
-      <c r="P22" s="3" t="s">
-        <v>3</v>
+      <c r="P22" s="3">
+        <v>800</v>
       </c>
       <c r="Q22" s="3" t="s">
         <v>3</v>
@@ -1515,132 +1555,141 @@
       <c r="S22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T22" s="3">
-        <v>0</v>
+      <c r="T22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-158500</v>
+      </c>
+      <c r="E23" s="3">
         <v>-124400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-79800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-78100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-84900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-93100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-91100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-62900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-69800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-84900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>82300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-90800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-40800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-400</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>400</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-100</v>
       </c>
-      <c r="U23" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E24" s="3">
         <v>900</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-400</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>500</v>
-      </c>
-      <c r="G24" s="3">
-        <v>-400</v>
       </c>
       <c r="H24" s="3">
         <v>-400</v>
       </c>
       <c r="I24" s="3">
+        <v>-400</v>
+      </c>
+      <c r="J24" s="3">
         <v>-1900</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-2700</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-300</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>100</v>
       </c>
-      <c r="M24" s="3">
-        <v>0</v>
-      </c>
       <c r="N24" s="3">
         <v>0</v>
       </c>
       <c r="O24" s="3">
+        <v>0</v>
+      </c>
+      <c r="P24" s="3">
         <v>100</v>
       </c>
-      <c r="P24" s="3">
-        <v>0</v>
-      </c>
       <c r="Q24" s="3">
+        <v>0</v>
+      </c>
+      <c r="R24" s="3">
         <v>200</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>300</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>200</v>
       </c>
-      <c r="T24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1698,126 +1747,135 @@
       <c r="U25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-158200</v>
+      </c>
+      <c r="E26" s="3">
         <v>-125300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-79400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-78700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-84500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-92700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-89300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-60100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-69400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-84900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>82300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-90700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-40900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-600</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-100</v>
       </c>
-      <c r="U26" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-158200</v>
+      </c>
+      <c r="E27" s="3">
         <v>-125300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-79400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-78700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-84500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-92700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-89300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-60100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-69400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-84900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-84500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-103600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-46600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-600</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-100</v>
       </c>
-      <c r="U27" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1875,8 +1933,11 @@
       <c r="U28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1934,8 +1995,11 @@
       <c r="U29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1993,8 +2057,11 @@
       <c r="U30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2052,50 +2119,53 @@
       <c r="U31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-1900</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-3100</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-3200</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-1000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-200</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>300</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-16400</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>4400</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>10600</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-130400</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>54600</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>7400</v>
       </c>
-      <c r="P32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2105,73 +2175,79 @@
       <c r="S32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T32" s="3">
-        <v>0</v>
-      </c>
-      <c r="U32" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="T32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U32" s="3">
+        <v>0</v>
+      </c>
+      <c r="V32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-158200</v>
+      </c>
+      <c r="E33" s="3">
         <v>-125300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-79400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-78700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-84500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-92700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-89300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-60100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-69400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-84900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-84500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-103600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-46600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-600</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>200</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-100</v>
       </c>
-      <c r="U33" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2229,131 +2305,140 @@
       <c r="U34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-158200</v>
+      </c>
+      <c r="E35" s="3">
         <v>-125300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-79400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-78700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-84500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-92700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-89300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-60100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-69400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-84900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-84500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-103600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-46600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-600</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>200</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-100</v>
       </c>
-      <c r="U35" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45230</v>
+      </c>
+      <c r="E38" s="2">
         <v>45138</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45046</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44957</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44865</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44773</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44681</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44592</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44500</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44408</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44316</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44227</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44135</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44012</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>43921</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43830</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43738</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43646</v>
       </c>
-      <c r="U38" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2375,8 +2460,9 @@
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
-    </row>
-    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V39" s="3"/>
+    </row>
+    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2398,67 +2484,71 @@
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
-    </row>
-    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V40" s="3"/>
+    </row>
+    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>367000</v>
+      </c>
+      <c r="E41" s="3">
         <v>233500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>283300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>264200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>188300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>187700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>540600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>315200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>365500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>618100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>609800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>145500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>168700</v>
       </c>
-      <c r="P41" s="3">
-        <v>0</v>
-      </c>
       <c r="Q41" s="3">
+        <v>0</v>
+      </c>
+      <c r="R41" s="3">
         <v>200</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>400</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>800</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>100</v>
       </c>
-      <c r="U41" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2469,17 +2559,17 @@
         <v>0</v>
       </c>
       <c r="F42" s="3">
+        <v>0</v>
+      </c>
+      <c r="G42" s="3">
         <v>105000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>208900</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>283900</v>
       </c>
-      <c r="I42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2495,8 +2585,8 @@
       <c r="N42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O42" s="3">
-        <v>0</v>
+      <c r="O42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P42" s="3">
         <v>0</v>
@@ -2516,50 +2606,53 @@
       <c r="U42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>151800</v>
+      </c>
+      <c r="E43" s="3">
         <v>202100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>165100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>164900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>123000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>109900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>79900</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>75900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>66100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>42700</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>34900</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>35100</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>28300</v>
       </c>
-      <c r="P43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2569,56 +2662,59 @@
       <c r="S43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T43" s="3">
-        <v>0</v>
+      <c r="T43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>199100</v>
+      </c>
+      <c r="E44" s="3">
         <v>143600</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>115200</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>68700</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>62400</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>53400</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>45300</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>35900</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>29900</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>27900</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>28900</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>33600</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>30700</v>
       </c>
-      <c r="P44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q44" s="3" t="s">
         <v>3</v>
       </c>
@@ -2628,132 +2724,141 @@
       <c r="S44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T44" s="3">
-        <v>0</v>
+      <c r="T44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>106500</v>
+      </c>
+      <c r="E45" s="3">
         <v>113100</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>118500</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>101400</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>59000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>45300</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>46500</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>37000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>33100</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>22500</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>20300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>12500</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>15200</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>200</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>300</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>400</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>300</v>
       </c>
-      <c r="T45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>824400</v>
+      </c>
+      <c r="E46" s="3">
         <v>692200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>682200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>704200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>641600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>680200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>712200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>464100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>494600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>711300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>693900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>226600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>242900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>300</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>500</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>800</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>1100</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>100</v>
       </c>
-      <c r="U46" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2794,67 +2899,70 @@
         <v>0</v>
       </c>
       <c r="P47" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q47" s="3">
         <v>317400</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>317300</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>316400</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>315100</v>
       </c>
-      <c r="T47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>62900</v>
+        <v>60300</v>
       </c>
       <c r="E48" s="3">
         <v>62900</v>
       </c>
       <c r="F48" s="3">
+        <v>62900</v>
+      </c>
+      <c r="G48" s="3">
         <v>62300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>60600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>59300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>59200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>60100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>58300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>53100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>53000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>51800</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>50800</v>
       </c>
-      <c r="P48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2864,43 +2972,46 @@
       <c r="S48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T48" s="3">
-        <v>0</v>
+      <c r="T48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>294200</v>
+      </c>
+      <c r="E49" s="3">
         <v>304500</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>307500</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>306400</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>291400</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>300100</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>309600</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>325700</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>343200</v>
-      </c>
-      <c r="L49" s="3">
-        <v>1200</v>
       </c>
       <c r="M49" s="3">
         <v>1200</v>
@@ -2911,8 +3022,8 @@
       <c r="O49" s="3">
         <v>1200</v>
       </c>
-      <c r="P49" s="3" t="s">
-        <v>3</v>
+      <c r="P49" s="3">
+        <v>1200</v>
       </c>
       <c r="Q49" s="3" t="s">
         <v>3</v>
@@ -2923,14 +3034,17 @@
       <c r="S49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T49" s="3">
-        <v>0</v>
+      <c r="T49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2988,8 +3102,11 @@
       <c r="U50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3047,8 +3164,11 @@
       <c r="U51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3056,58 +3176,61 @@
         <v>8700</v>
       </c>
       <c r="E52" s="3">
+        <v>8700</v>
+      </c>
+      <c r="F52" s="3">
         <v>7300</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>7100</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>7000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>6500</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>6300</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>6000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>5300</v>
-      </c>
-      <c r="L52" s="3">
-        <v>5000</v>
       </c>
       <c r="M52" s="3">
         <v>5000</v>
       </c>
       <c r="N52" s="3">
+        <v>5000</v>
+      </c>
+      <c r="O52" s="3">
         <v>10500</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>4300</v>
       </c>
-      <c r="P52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R52" s="3">
+      <c r="R52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S52" s="3">
         <v>316400</v>
       </c>
-      <c r="S52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T52" s="3">
+      <c r="T52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U52" s="3">
         <v>300</v>
       </c>
-      <c r="U52" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3165,67 +3288,73 @@
       <c r="U53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1187700</v>
+      </c>
+      <c r="E54" s="3">
         <v>1068400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1059800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1080000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1000600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1046000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1087300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>855900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>901500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>770600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>753100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>290100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>299300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>317700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>317800</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>317200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>316200</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>400</v>
       </c>
-      <c r="U54" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3247,8 +3376,9 @@
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
-    </row>
-    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V55" s="3"/>
+    </row>
+    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3270,67 +3400,71 @@
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
-    </row>
-    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V56" s="3"/>
+    </row>
+    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>101700</v>
+      </c>
+      <c r="E57" s="3">
         <v>99000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>62000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>62100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>44500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>45100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>35400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>27600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>32100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>28400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>18100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>19800</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>16700</v>
-      </c>
-      <c r="P57" s="3">
-        <v>100</v>
       </c>
       <c r="Q57" s="3">
         <v>100</v>
       </c>
       <c r="R57" s="3">
+        <v>100</v>
+      </c>
+      <c r="S57" s="3">
         <v>200</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>100</v>
       </c>
-      <c r="T57" s="3">
-        <v>0</v>
-      </c>
-      <c r="U57" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="U57" s="3">
+        <v>0</v>
+      </c>
+      <c r="V57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3365,173 +3499,182 @@
         <v>0</v>
       </c>
       <c r="N58" s="3">
+        <v>0</v>
+      </c>
+      <c r="O58" s="3">
         <v>10200</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>5800</v>
       </c>
-      <c r="P58" s="3">
-        <v>0</v>
-      </c>
       <c r="Q58" s="3">
         <v>0</v>
       </c>
       <c r="R58" s="3">
         <v>0</v>
       </c>
-      <c r="S58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T58" s="3">
+      <c r="S58" s="3">
+        <v>0</v>
+      </c>
+      <c r="T58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U58" s="3">
         <v>100</v>
       </c>
-      <c r="U58" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>251000</v>
+      </c>
+      <c r="E59" s="3">
         <v>241500</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>226400</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>222300</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>193800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>193600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>177500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>161500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>135400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>99700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>86800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>88100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>76700</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>900</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>800</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>600</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>400</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>300</v>
       </c>
-      <c r="U59" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>352600</v>
+      </c>
+      <c r="E60" s="3">
         <v>340500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>288400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>284300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>238400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>238800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>212800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>189000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>167400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>128200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>104900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>118100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>99300</v>
-      </c>
-      <c r="P60" s="3">
-        <v>1000</v>
       </c>
       <c r="Q60" s="3">
         <v>1000</v>
       </c>
       <c r="R60" s="3">
+        <v>1000</v>
+      </c>
+      <c r="S60" s="3">
         <v>800</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>500</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>400</v>
       </c>
-      <c r="U60" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>282700</v>
+      </c>
+      <c r="E61" s="3">
         <v>295500</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>295200</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>294900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>294600</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>294300</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>294100</v>
       </c>
-      <c r="J61" s="3">
-        <v>0</v>
-      </c>
       <c r="K61" s="3">
         <v>0</v>
       </c>
@@ -3542,14 +3685,14 @@
         <v>0</v>
       </c>
       <c r="N61" s="3">
+        <v>0</v>
+      </c>
+      <c r="O61" s="3">
         <v>24700</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>28900</v>
       </c>
-      <c r="P61" s="3">
-        <v>0</v>
-      </c>
       <c r="Q61" s="3">
         <v>0</v>
       </c>
@@ -3565,67 +3708,73 @@
       <c r="U61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>159700</v>
+      </c>
+      <c r="E62" s="3">
         <v>157100</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>148700</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>145700</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>129000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>121200</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>115300</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>119800</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>148600</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>107400</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>163800</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>148200</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>86300</v>
-      </c>
-      <c r="P62" s="3">
-        <v>10900</v>
       </c>
       <c r="Q62" s="3">
         <v>10900</v>
       </c>
       <c r="R62" s="3">
+        <v>10900</v>
+      </c>
+      <c r="S62" s="3">
         <v>20500</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>10900</v>
       </c>
-      <c r="T62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3683,8 +3832,11 @@
       <c r="U63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3742,8 +3894,11 @@
       <c r="U64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3801,67 +3956,73 @@
       <c r="U65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>795100</v>
+      </c>
+      <c r="E66" s="3">
         <v>793200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>732300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>725000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>662000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>654300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>622200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>308900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>316100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>235600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>268700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>290900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>214500</v>
-      </c>
-      <c r="P66" s="3">
-        <v>11900</v>
       </c>
       <c r="Q66" s="3">
         <v>11900</v>
       </c>
       <c r="R66" s="3">
+        <v>11900</v>
+      </c>
+      <c r="S66" s="3">
         <v>21300</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>11400</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>400</v>
       </c>
-      <c r="U66" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3883,8 +4044,9 @@
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
-    </row>
-    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V67" s="3"/>
+    </row>
+    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3942,8 +4104,11 @@
       <c r="U68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4001,8 +4166,11 @@
       <c r="U69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4037,14 +4205,14 @@
         <v>0</v>
       </c>
       <c r="N70" s="3">
+        <v>0</v>
+      </c>
+      <c r="O70" s="3">
         <v>615700</v>
       </c>
-      <c r="O70" s="3">
+      <c r="P70" s="3">
         <v>615800</v>
       </c>
-      <c r="P70" s="3">
-        <v>0</v>
-      </c>
       <c r="Q70" s="3">
         <v>0</v>
       </c>
@@ -4060,8 +4228,11 @@
       <c r="U70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4119,67 +4290,73 @@
       <c r="U71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-1519600</v>
+      </c>
+      <c r="E72" s="3">
         <v>-1361400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-1236200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-1156800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-1078100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-993600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-900900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-811700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-751500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-682100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-597100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>200</v>
       </c>
-      <c r="O72" s="3">
-        <v>0</v>
-      </c>
       <c r="P72" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q72" s="3">
         <v>1100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>1200</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>300</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>100</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-100</v>
       </c>
-      <c r="U72" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4237,8 +4414,11 @@
       <c r="U73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4296,8 +4476,11 @@
       <c r="U74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4355,67 +4538,73 @@
       <c r="U75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>392600</v>
+      </c>
+      <c r="E76" s="3">
         <v>275200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>327500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>355000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>338600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>391700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>465100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>547000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>585400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>535000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>484300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>-616500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>-531000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>305800</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>305900</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>295900</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>304800</v>
       </c>
-      <c r="T76" s="3">
-        <v>0</v>
-      </c>
-      <c r="U76" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="U76" s="3">
+        <v>0</v>
+      </c>
+      <c r="V76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4473,131 +4662,140 @@
       <c r="U77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45230</v>
+      </c>
+      <c r="E80" s="2">
         <v>45138</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45046</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44957</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44865</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44773</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44681</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44592</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44500</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44408</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44316</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44227</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44135</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44012</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>43921</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43830</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43738</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43646</v>
       </c>
-      <c r="U80" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-158200</v>
+      </c>
+      <c r="E81" s="3">
         <v>-125300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-79400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-78700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-84500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-92700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-89300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-60100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-69400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-84900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-84500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-103600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-46600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-600</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>200</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-100</v>
       </c>
-      <c r="U81" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4619,50 +4817,51 @@
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
-    </row>
-    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V82" s="3"/>
+    </row>
+    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>7100</v>
+      </c>
+      <c r="E83" s="3">
         <v>7000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>7100</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>6500</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>6100</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>6300</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>6200</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>6300</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>4600</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>2800</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>2700</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>2600</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>2800</v>
       </c>
-      <c r="P83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q83" s="3" t="s">
         <v>3</v>
       </c>
@@ -4672,14 +4871,17 @@
       <c r="S83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T83" s="3">
-        <v>0</v>
+      <c r="T83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4737,8 +4939,11 @@
       <c r="U84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4796,8 +5001,11 @@
       <c r="U85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4855,8 +5063,11 @@
       <c r="U86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4914,8 +5125,11 @@
       <c r="U87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4973,67 +5187,73 @@
       <c r="U88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-96900</v>
+      </c>
+      <c r="E89" s="3">
         <v>-86400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-104200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-50400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-83000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-62900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-70800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-48100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-47900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-23700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-37500</v>
-      </c>
-      <c r="N89" s="3">
-        <v>-20900</v>
       </c>
       <c r="O89" s="3">
         <v>-20900</v>
       </c>
       <c r="P89" s="3">
+        <v>-20900</v>
+      </c>
+      <c r="Q89" s="3">
         <v>-100</v>
-      </c>
-      <c r="Q89" s="3">
-        <v>-300</v>
       </c>
       <c r="R89" s="3">
         <v>-300</v>
       </c>
       <c r="S89" s="3">
+        <v>-300</v>
+      </c>
+      <c r="T89" s="3">
         <v>-700</v>
       </c>
-      <c r="T89" s="3">
-        <v>0</v>
-      </c>
-      <c r="U89" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="U89" s="3">
+        <v>0</v>
+      </c>
+      <c r="V89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5055,50 +5275,51 @@
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
-    </row>
-    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V90" s="3"/>
+    </row>
+    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-4800</v>
+      </c>
+      <c r="E91" s="3">
         <v>-4000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-5800</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-4400</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-5300</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-5700</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-3200</v>
-      </c>
-      <c r="J91" s="3">
-        <v>-4300</v>
       </c>
       <c r="K91" s="3">
         <v>-4300</v>
       </c>
       <c r="L91" s="3">
+        <v>-4300</v>
+      </c>
+      <c r="M91" s="3">
         <v>-3700</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-4100</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-2600</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-3000</v>
       </c>
-      <c r="P91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q91" s="3" t="s">
         <v>3</v>
       </c>
@@ -5108,14 +5329,17 @@
       <c r="S91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T91" s="3">
-        <v>0</v>
+      <c r="T91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5173,8 +5397,11 @@
       <c r="U92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5232,58 +5459,61 @@
       <c r="U93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-4800</v>
+      </c>
+      <c r="E94" s="3">
         <v>-4000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>99200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>100600</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>69700</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-290500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-5900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-4300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-209600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-3700</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-4100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-2600</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-3000</v>
       </c>
-      <c r="P94" s="3">
-        <v>0</v>
-      </c>
       <c r="Q94" s="3">
+        <v>0</v>
+      </c>
+      <c r="R94" s="3">
         <v>100</v>
       </c>
-      <c r="R94" s="3">
-        <v>0</v>
-      </c>
-      <c r="S94" s="3" t="s">
-        <v>3</v>
+      <c r="S94" s="3">
+        <v>0</v>
       </c>
       <c r="T94" s="3" t="s">
         <v>3</v>
@@ -5291,8 +5521,11 @@
       <c r="U94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5314,8 +5547,9 @@
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
-    </row>
-    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V95" s="3"/>
+    </row>
+    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5373,8 +5607,11 @@
       <c r="U96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5432,8 +5669,11 @@
       <c r="U97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5491,8 +5731,11 @@
       <c r="U98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5550,108 +5793,114 @@
       <c r="U99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>236700</v>
+      </c>
+      <c r="E100" s="3">
         <v>40300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>23800</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>54900</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>14400</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>303100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>2500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>5600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>35600</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>506000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>200</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>3400</v>
       </c>
-      <c r="P100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R100" s="3">
+      <c r="R100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S100" s="3">
         <v>-100</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>315500</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>100</v>
       </c>
-      <c r="U100" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="E101" s="3">
         <v>300</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>500</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>800</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-500</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-100</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-1000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-300</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-700</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
-      </c>
       <c r="M101" s="3">
         <v>0</v>
       </c>
       <c r="N101" s="3">
+        <v>0</v>
+      </c>
+      <c r="O101" s="3">
         <v>100</v>
       </c>
-      <c r="O101" s="3">
-        <v>0</v>
-      </c>
-      <c r="P101" s="3" t="s">
-        <v>3</v>
+      <c r="P101" s="3">
+        <v>0</v>
       </c>
       <c r="Q101" s="3" t="s">
         <v>3</v>
@@ -5662,69 +5911,75 @@
       <c r="S101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T101" s="3">
-        <v>0</v>
+      <c r="T101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>133500</v>
+      </c>
+      <c r="E102" s="3">
         <v>-49800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>19200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>105900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-352900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>225300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-50300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-252600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>8300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>464300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-23200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-20400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-200</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-400</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>800</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>100</v>
       </c>
-      <c r="U102" s="3" t="s">
+      <c r="V102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/CHPT_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CHPT_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="92">
   <si>
     <t>CHPT</t>
   </si>
@@ -656,213 +656,226 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:V102"/>
+  <dimension ref="A5:X102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45412</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45322</v>
+      </c>
+      <c r="F7" s="2">
         <v>45230</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45138</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45046</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>44957</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44865</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44773</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44681</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44592</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44500</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44408</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44316</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44227</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44135</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>43738</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>43646</v>
       </c>
-      <c r="V7" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="X7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>107000</v>
+      </c>
+      <c r="E8" s="3">
+        <v>115800</v>
+      </c>
+      <c r="F8" s="3">
         <v>110300</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>150500</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>130000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>152800</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>125300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>108300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>81600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>79300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>65000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>56100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>40500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>42400</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>36400</v>
       </c>
-      <c r="Q8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S8" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U8" s="3">
-        <v>0</v>
-      </c>
-      <c r="V8" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="U8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W8" s="3">
+        <v>0</v>
+      </c>
+      <c r="X8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>83400</v>
+      </c>
+      <c r="E9" s="3">
+        <v>93400</v>
+      </c>
+      <c r="F9" s="3">
         <v>92200</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>121400</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>99500</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>119800</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>102700</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>90100</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>69500</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>61900</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>49000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>45300</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>31300</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>33500</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>29100</v>
       </c>
-      <c r="Q9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S9" s="3" t="s">
         <v>3</v>
       </c>
@@ -875,56 +888,62 @@
       <c r="V9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>23600</v>
+      </c>
+      <c r="E10" s="3">
+        <v>22400</v>
+      </c>
+      <c r="F10" s="3">
         <v>18100</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>29100</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>30500</v>
       </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
         <v>33000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>22600</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>18200</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>12100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>17400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>16000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>10800</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>9200</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>8900</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>7300</v>
       </c>
-      <c r="Q10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S10" s="3" t="s">
         <v>3</v>
       </c>
@@ -937,8 +956,14 @@
       <c r="V10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -961,56 +986,58 @@
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W11" s="3"/>
+      <c r="X11" s="3"/>
+    </row>
+    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
-        <v>56500</v>
+        <v>36100</v>
       </c>
       <c r="E12" s="3">
+        <v>51900</v>
+      </c>
+      <c r="F12" s="3">
+        <v>52300</v>
+      </c>
+      <c r="G12" s="3">
         <v>59600</v>
       </c>
-      <c r="F12" s="3">
+      <c r="H12" s="3">
         <v>49400</v>
       </c>
-      <c r="G12" s="3">
+      <c r="I12" s="3">
         <v>46700</v>
       </c>
-      <c r="H12" s="3">
+      <c r="J12" s="3">
         <v>48100</v>
       </c>
-      <c r="I12" s="3">
+      <c r="K12" s="3">
         <v>51800</v>
       </c>
-      <c r="J12" s="3">
+      <c r="L12" s="3">
         <v>48300</v>
       </c>
-      <c r="K12" s="3">
+      <c r="M12" s="3">
         <v>42500</v>
       </c>
-      <c r="L12" s="3">
+      <c r="N12" s="3">
         <v>36800</v>
       </c>
-      <c r="M12" s="3">
+      <c r="O12" s="3">
         <v>40400</v>
       </c>
-      <c r="N12" s="3">
+      <c r="P12" s="3">
         <v>25400</v>
       </c>
-      <c r="O12" s="3">
+      <c r="Q12" s="3">
         <v>20900</v>
       </c>
-      <c r="P12" s="3">
+      <c r="R12" s="3">
         <v>18900</v>
       </c>
-      <c r="Q12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1023,8 +1050,14 @@
       <c r="V12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1085,23 +1118,29 @@
       <c r="V13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W13" s="3">
+        <v>0</v>
+      </c>
+      <c r="X13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>42000</v>
+      <c r="D14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E14" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="F14" s="3">
+        <v>56600</v>
+      </c>
+      <c r="G14" s="3">
         <v>28000</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1111,18 +1150,18 @@
       <c r="J14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K14" s="3">
+      <c r="K14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M14" s="3">
         <v>200</v>
       </c>
-      <c r="L14" s="3">
+      <c r="N14" s="3">
         <v>4800</v>
       </c>
-      <c r="M14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1132,11 +1171,11 @@
       <c r="Q14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R14" s="3">
-        <v>0</v>
-      </c>
-      <c r="S14" s="3">
-        <v>0</v>
+      <c r="R14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T14" s="3">
         <v>0</v>
@@ -1147,8 +1186,14 @@
       <c r="V14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W14" s="3">
+        <v>0</v>
+      </c>
+      <c r="X14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1209,8 +1254,14 @@
       <c r="V15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W15" s="3">
+        <v>0</v>
+      </c>
+      <c r="X15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1230,132 +1281,146 @@
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
-    </row>
-    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W16" s="3"/>
+      <c r="X16" s="3"/>
+    </row>
+    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>174200</v>
+      </c>
+      <c r="E17" s="3">
+        <v>208800</v>
+      </c>
+      <c r="F17" s="3">
         <v>264100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>273800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>210000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>231100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>208600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>198700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>171500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>158600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>130400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>130400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>87100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>77700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>69000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>300</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>1600</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>600</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>100</v>
       </c>
-      <c r="V17" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="X17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-67200</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-93000</v>
+      </c>
+      <c r="F18" s="3">
         <v>-153800</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>-123300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>-80000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>-78300</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>-83300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>-90400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>-89900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>-79300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>-65400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>-74300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>-46600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>-35300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>-32600</v>
       </c>
-      <c r="Q18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U18" s="3">
+      <c r="U18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W18" s="3">
         <v>-100</v>
       </c>
-      <c r="V18" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="X18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1378,118 +1443,126 @@
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
-    </row>
-    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W19" s="3"/>
+      <c r="X19" s="3"/>
+    </row>
+    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E20" s="3">
+        <v>4600</v>
+      </c>
+      <c r="F20" s="3">
         <v>-1000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="G20" s="3">
         <v>1900</v>
       </c>
-      <c r="F20" s="3">
+      <c r="H20" s="3">
         <v>3100</v>
       </c>
-      <c r="G20" s="3">
+      <c r="I20" s="3">
         <v>3200</v>
       </c>
-      <c r="H20" s="3">
+      <c r="J20" s="3">
         <v>1000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>200</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>-300</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>16400</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>-4400</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>-10600</v>
       </c>
-      <c r="N20" s="3">
+      <c r="P20" s="3">
         <v>130400</v>
       </c>
-      <c r="O20" s="3">
+      <c r="Q20" s="3">
         <v>-54600</v>
       </c>
-      <c r="P20" s="3">
+      <c r="R20" s="3">
         <v>-7400</v>
       </c>
-      <c r="Q20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S20" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U20" s="3">
-        <v>0</v>
+      <c r="U20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W20" s="3">
+        <v>0</v>
+      </c>
+      <c r="X20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-57300</v>
+      </c>
+      <c r="E21" s="3">
+        <v>-81000</v>
+      </c>
+      <c r="F21" s="3">
         <v>-147600</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>-114500</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>-69800</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>-68700</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>-76200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>-83900</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>-84000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>-56600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>-65200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>-82000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>86600</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>-87300</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>-37200</v>
       </c>
-      <c r="Q21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1502,194 +1575,218 @@
       <c r="V21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>6600</v>
+      </c>
+      <c r="E22" s="3">
+        <v>6600</v>
+      </c>
+      <c r="F22" s="3">
         <v>3800</v>
       </c>
-      <c r="E22" s="3">
+      <c r="G22" s="3">
         <v>2900</v>
       </c>
-      <c r="F22" s="3">
+      <c r="H22" s="3">
         <v>2900</v>
       </c>
-      <c r="G22" s="3">
+      <c r="I22" s="3">
         <v>3000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="J22" s="3">
         <v>2600</v>
       </c>
-      <c r="I22" s="3">
+      <c r="K22" s="3">
         <v>2900</v>
       </c>
-      <c r="J22" s="3">
+      <c r="L22" s="3">
         <v>900</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
-      </c>
-      <c r="L22" s="3">
-        <v>0</v>
-      </c>
       <c r="M22" s="3">
         <v>0</v>
       </c>
       <c r="N22" s="3">
+        <v>0</v>
+      </c>
+      <c r="O22" s="3">
+        <v>0</v>
+      </c>
+      <c r="P22" s="3">
         <v>1500</v>
       </c>
-      <c r="O22" s="3">
+      <c r="Q22" s="3">
         <v>800</v>
       </c>
-      <c r="P22" s="3">
+      <c r="R22" s="3">
         <v>800</v>
       </c>
-      <c r="Q22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S22" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U22" s="3">
-        <v>0</v>
-      </c>
-      <c r="V22" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="U22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W22" s="3">
+        <v>0</v>
+      </c>
+      <c r="X22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-71400</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-94900</v>
+      </c>
+      <c r="F23" s="3">
         <v>-158500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-124400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>-79800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>-78100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>-84900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>-93100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-91100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-62900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>-69800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>-84900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>82300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>-90800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>-40800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>-100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>700</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>-400</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>400</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>-100</v>
       </c>
-      <c r="V23" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="X23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>400</v>
+      </c>
+      <c r="E24" s="3">
+        <v>-200</v>
+      </c>
+      <c r="F24" s="3">
         <v>-300</v>
       </c>
-      <c r="E24" s="3">
+      <c r="G24" s="3">
         <v>900</v>
-      </c>
-      <c r="F24" s="3">
-        <v>-400</v>
-      </c>
-      <c r="G24" s="3">
-        <v>500</v>
       </c>
       <c r="H24" s="3">
         <v>-400</v>
       </c>
       <c r="I24" s="3">
+        <v>500</v>
+      </c>
+      <c r="J24" s="3">
         <v>-400</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
+        <v>-400</v>
+      </c>
+      <c r="L24" s="3">
         <v>-1900</v>
       </c>
-      <c r="K24" s="3">
+      <c r="M24" s="3">
         <v>-2700</v>
       </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
         <v>-300</v>
       </c>
-      <c r="M24" s="3">
+      <c r="O24" s="3">
         <v>100</v>
       </c>
-      <c r="N24" s="3">
-        <v>0</v>
-      </c>
-      <c r="O24" s="3">
-        <v>0</v>
-      </c>
       <c r="P24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="3">
+        <v>0</v>
+      </c>
+      <c r="R24" s="3">
         <v>100</v>
       </c>
-      <c r="Q24" s="3">
-        <v>0</v>
-      </c>
-      <c r="R24" s="3">
-        <v>200</v>
-      </c>
       <c r="S24" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="T24" s="3">
         <v>200</v>
       </c>
-      <c r="U24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V24" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="U24" s="3">
+        <v>300</v>
+      </c>
+      <c r="V24" s="3">
+        <v>200</v>
+      </c>
+      <c r="W24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1750,132 +1847,150 @@
       <c r="V25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W25" s="3">
+        <v>0</v>
+      </c>
+      <c r="X25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-71800</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-94700</v>
+      </c>
+      <c r="F26" s="3">
         <v>-158200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-125300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>-79400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>-78700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>-84500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>-92700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-89300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-60100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>-69400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>-84900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>82300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>-90700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>-40900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>-100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>-600</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>-100</v>
       </c>
-      <c r="V26" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="X26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-71800</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-94700</v>
+      </c>
+      <c r="F27" s="3">
         <v>-158200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-125300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>-79400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>-78700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>-84500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>-92700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-89300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-60100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>-69400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>-84900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>-84500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>-103600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>-46600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>-100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>500</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>-600</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>200</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>-100</v>
       </c>
-      <c r="V27" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="X27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1936,8 +2051,14 @@
       <c r="V28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W28" s="3">
+        <v>0</v>
+      </c>
+      <c r="X28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1998,8 +2119,14 @@
       <c r="V29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W29" s="3">
+        <v>0</v>
+      </c>
+      <c r="X29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2060,8 +2187,14 @@
       <c r="V30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W30" s="3">
+        <v>0</v>
+      </c>
+      <c r="X30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2122,132 +2255,150 @@
       <c r="V31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W31" s="3">
+        <v>0</v>
+      </c>
+      <c r="X31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="E32" s="3">
+        <v>-4600</v>
+      </c>
+      <c r="F32" s="3">
         <v>1000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="G32" s="3">
         <v>-1900</v>
       </c>
-      <c r="F32" s="3">
+      <c r="H32" s="3">
         <v>-3100</v>
       </c>
-      <c r="G32" s="3">
+      <c r="I32" s="3">
         <v>-3200</v>
       </c>
-      <c r="H32" s="3">
+      <c r="J32" s="3">
         <v>-1000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>-200</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>300</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>-16400</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>4400</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>10600</v>
       </c>
-      <c r="N32" s="3">
+      <c r="P32" s="3">
         <v>-130400</v>
       </c>
-      <c r="O32" s="3">
+      <c r="Q32" s="3">
         <v>54600</v>
       </c>
-      <c r="P32" s="3">
+      <c r="R32" s="3">
         <v>7400</v>
       </c>
-      <c r="Q32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S32" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U32" s="3">
-        <v>0</v>
+      <c r="U32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W32" s="3">
+        <v>0</v>
+      </c>
+      <c r="X32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-71800</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-94700</v>
+      </c>
+      <c r="F33" s="3">
         <v>-158200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-125300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>-79400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>-78700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>-84500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-92700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-89300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-60100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>-69400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>-84900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>-84500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>-103600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>-46600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>-100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>500</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>-600</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>200</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>-100</v>
       </c>
-      <c r="V33" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="X33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2308,137 +2459,155 @@
       <c r="V34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W34" s="3">
+        <v>0</v>
+      </c>
+      <c r="X34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-71800</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-94700</v>
+      </c>
+      <c r="F35" s="3">
         <v>-158200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-125300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>-79400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>-78700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>-84500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-92700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-89300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-60100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>-69400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>-84900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>-84500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>-103600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>-46600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>-100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>500</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>-600</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>200</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>-100</v>
       </c>
-      <c r="V35" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="X35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45412</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45322</v>
+      </c>
+      <c r="F38" s="2">
         <v>45230</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45138</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45046</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>44957</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44865</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44773</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44681</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44592</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44500</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44408</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44316</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44227</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44135</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>43738</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>43646</v>
       </c>
-      <c r="V38" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="X38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2461,8 +2630,10 @@
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
-    </row>
-    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W39" s="3"/>
+      <c r="X39" s="3"/>
+    </row>
+    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2485,75 +2656,83 @@
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
-    </row>
-    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W40" s="3"/>
+      <c r="X40" s="3"/>
+    </row>
+    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>261900</v>
+      </c>
+      <c r="E41" s="3">
+        <v>327400</v>
+      </c>
+      <c r="F41" s="3">
         <v>367000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>233500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>283300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>264200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>188300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>187700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>540600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>315200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>365500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>618100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>609800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>145500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>168700</v>
       </c>
-      <c r="Q41" s="3">
-        <v>0</v>
-      </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
+        <v>0</v>
+      </c>
+      <c r="T41" s="3">
         <v>200</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>400</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>800</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>100</v>
       </c>
-      <c r="V41" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="X41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D42" s="3">
-        <v>0</v>
+      <c r="D42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E42" s="3">
         <v>0</v>
@@ -2562,20 +2741,20 @@
         <v>0</v>
       </c>
       <c r="G42" s="3">
+        <v>0</v>
+      </c>
+      <c r="H42" s="3">
+        <v>0</v>
+      </c>
+      <c r="I42" s="3">
         <v>105000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="J42" s="3">
         <v>208900</v>
       </c>
-      <c r="I42" s="3">
+      <c r="K42" s="3">
         <v>283900</v>
       </c>
-      <c r="J42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2588,11 +2767,11 @@
       <c r="O42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P42" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q42" s="3">
-        <v>0</v>
+      <c r="P42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R42" s="3">
         <v>0</v>
@@ -2609,256 +2788,286 @@
       <c r="V42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W42" s="3">
+        <v>0</v>
+      </c>
+      <c r="X42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>117800</v>
+      </c>
+      <c r="E43" s="3">
+        <v>124000</v>
+      </c>
+      <c r="F43" s="3">
         <v>151800</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>202100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>165100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>164900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>123000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>109900</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>79900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>75900</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>66100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>42700</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>34900</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>35100</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>28300</v>
       </c>
-      <c r="Q43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S43" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U43" s="3">
-        <v>0</v>
-      </c>
-      <c r="V43" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="U43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W43" s="3">
+        <v>0</v>
+      </c>
+      <c r="X43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>223600</v>
+      </c>
+      <c r="E44" s="3">
+        <v>198600</v>
+      </c>
+      <c r="F44" s="3">
         <v>199100</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>143600</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>115200</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>68700</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>62400</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>53400</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>45300</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>35900</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>29900</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>27900</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>28900</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>33600</v>
       </c>
-      <c r="P44" s="3">
+      <c r="R44" s="3">
         <v>30700</v>
       </c>
-      <c r="Q44" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S44" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U44" s="3">
-        <v>0</v>
-      </c>
-      <c r="V44" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="U44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W44" s="3">
+        <v>0</v>
+      </c>
+      <c r="X44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>95100</v>
+      </c>
+      <c r="E45" s="3">
+        <v>92600</v>
+      </c>
+      <c r="F45" s="3">
         <v>106500</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>113100</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>118500</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>101400</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>59000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>45300</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>46500</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>37000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>33100</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>22500</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>20300</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>12500</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>15200</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>200</v>
-      </c>
-      <c r="R45" s="3">
-        <v>300</v>
-      </c>
-      <c r="S45" s="3">
-        <v>400</v>
       </c>
       <c r="T45" s="3">
         <v>300</v>
       </c>
-      <c r="U45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V45" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="U45" s="3">
+        <v>400</v>
+      </c>
+      <c r="V45" s="3">
+        <v>300</v>
+      </c>
+      <c r="W45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>698300</v>
+      </c>
+      <c r="E46" s="3">
+        <v>742700</v>
+      </c>
+      <c r="F46" s="3">
         <v>824400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>692200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>682200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>704200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>641600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>680200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>712200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>464100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>494600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>711300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>693900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>226600</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>242900</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>300</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>500</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>800</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>1100</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>100</v>
       </c>
-      <c r="V46" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="X46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2902,122 +3111,134 @@
         <v>0</v>
       </c>
       <c r="Q47" s="3">
+        <v>0</v>
+      </c>
+      <c r="R47" s="3">
+        <v>0</v>
+      </c>
+      <c r="S47" s="3">
         <v>317400</v>
       </c>
-      <c r="R47" s="3">
+      <c r="T47" s="3">
         <v>317300</v>
       </c>
-      <c r="S47" s="3">
+      <c r="U47" s="3">
         <v>316400</v>
       </c>
-      <c r="T47" s="3">
+      <c r="V47" s="3">
         <v>315100</v>
       </c>
-      <c r="U47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V47" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>55600</v>
+      </c>
+      <c r="E48" s="3">
+        <v>57800</v>
+      </c>
+      <c r="F48" s="3">
         <v>60300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>62900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>62900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>62300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>60600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>59300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>59200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>60100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>58300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>53100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>53000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>51800</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>50800</v>
       </c>
-      <c r="Q48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S48" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U48" s="3">
-        <v>0</v>
-      </c>
-      <c r="V48" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="U48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W48" s="3">
+        <v>0</v>
+      </c>
+      <c r="X48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>289300</v>
+      </c>
+      <c r="E49" s="3">
+        <v>294300</v>
+      </c>
+      <c r="F49" s="3">
         <v>294200</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>304500</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>307500</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>306400</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>291400</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>300100</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>309600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>325700</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>343200</v>
-      </c>
-      <c r="M49" s="3">
-        <v>1200</v>
-      </c>
-      <c r="N49" s="3">
-        <v>1200</v>
       </c>
       <c r="O49" s="3">
         <v>1200</v>
@@ -3025,11 +3246,11 @@
       <c r="P49" s="3">
         <v>1200</v>
       </c>
-      <c r="Q49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R49" s="3" t="s">
-        <v>3</v>
+      <c r="Q49" s="3">
+        <v>1200</v>
+      </c>
+      <c r="R49" s="3">
+        <v>1200</v>
       </c>
       <c r="S49" s="3" t="s">
         <v>3</v>
@@ -3037,14 +3258,20 @@
       <c r="T49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U49" s="3">
-        <v>0</v>
-      </c>
-      <c r="V49" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="U49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W49" s="3">
+        <v>0</v>
+      </c>
+      <c r="X49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3105,8 +3332,14 @@
       <c r="V50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W50" s="3">
+        <v>0</v>
+      </c>
+      <c r="X50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3167,70 +3400,82 @@
       <c r="V51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W51" s="3">
+        <v>0</v>
+      </c>
+      <c r="X51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>8000</v>
+      </c>
+      <c r="E52" s="3">
+        <v>8600</v>
+      </c>
+      <c r="F52" s="3">
         <v>8700</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>8700</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>7300</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>7100</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>7000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>6500</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>6300</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>6000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>5300</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>5000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>5000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>10500</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>4300</v>
       </c>
-      <c r="Q52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S52" s="3">
+      <c r="S52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U52" s="3">
         <v>316400</v>
       </c>
-      <c r="T52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W52" s="3">
         <v>300</v>
       </c>
-      <c r="V52" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="X52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3291,70 +3536,82 @@
       <c r="V53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W53" s="3">
+        <v>0</v>
+      </c>
+      <c r="X53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1051200</v>
+      </c>
+      <c r="E54" s="3">
+        <v>1103400</v>
+      </c>
+      <c r="F54" s="3">
         <v>1187700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>1068400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>1059800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>1080000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>1000600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>1046000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>1087300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>855900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>901500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>770600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>753100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>290100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>299300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>317700</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>317800</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>317200</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>316200</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>400</v>
       </c>
-      <c r="V54" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="X54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3377,8 +3634,10 @@
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
-    </row>
-    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W55" s="3"/>
+      <c r="X55" s="3"/>
+    </row>
+    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3401,70 +3660,78 @@
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
-    </row>
-    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W56" s="3"/>
+      <c r="X56" s="3"/>
+    </row>
+    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>84100</v>
+      </c>
+      <c r="E57" s="3">
+        <v>71100</v>
+      </c>
+      <c r="F57" s="3">
         <v>101700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>99000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>62000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>62100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>44500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>45100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>35400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>27600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>32100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>28400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>18100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>19800</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>16700</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>100</v>
-      </c>
-      <c r="R57" s="3">
-        <v>100</v>
-      </c>
-      <c r="S57" s="3">
-        <v>200</v>
       </c>
       <c r="T57" s="3">
         <v>100</v>
       </c>
       <c r="U57" s="3">
-        <v>0</v>
-      </c>
-      <c r="V57" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
+        <v>200</v>
+      </c>
+      <c r="V57" s="3">
+        <v>100</v>
+      </c>
+      <c r="W57" s="3">
+        <v>0</v>
+      </c>
+      <c r="X57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3502,185 +3769,203 @@
         <v>0</v>
       </c>
       <c r="O58" s="3">
+        <v>0</v>
+      </c>
+      <c r="P58" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q58" s="3">
         <v>10200</v>
       </c>
-      <c r="P58" s="3">
+      <c r="R58" s="3">
         <v>5800</v>
       </c>
-      <c r="Q58" s="3">
-        <v>0</v>
-      </c>
-      <c r="R58" s="3">
-        <v>0</v>
-      </c>
       <c r="S58" s="3">
         <v>0</v>
       </c>
-      <c r="T58" s="3" t="s">
-        <v>3</v>
+      <c r="T58" s="3">
+        <v>0</v>
       </c>
       <c r="U58" s="3">
+        <v>0</v>
+      </c>
+      <c r="V58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W58" s="3">
         <v>100</v>
       </c>
-      <c r="V58" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="X58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>243700</v>
+      </c>
+      <c r="E59" s="3">
+        <v>259100</v>
+      </c>
+      <c r="F59" s="3">
         <v>251000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>241500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>226400</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>222300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>193800</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>193600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>177500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>161500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>135400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>99700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>86800</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>88100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>76700</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>900</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>800</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>600</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>400</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>300</v>
       </c>
-      <c r="V59" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="X59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>327800</v>
+      </c>
+      <c r="E60" s="3">
+        <v>330200</v>
+      </c>
+      <c r="F60" s="3">
         <v>352600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>340500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>288400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>284300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>238400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>238800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>212800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>189000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>167400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>128200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>104900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>118100</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>99300</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>1000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>1000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>800</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>500</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>400</v>
       </c>
-      <c r="V60" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="X60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>284700</v>
+      </c>
+      <c r="E61" s="3">
+        <v>283700</v>
+      </c>
+      <c r="F61" s="3">
         <v>282700</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>295500</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>295200</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>294900</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>294600</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>294300</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>294100</v>
       </c>
-      <c r="K61" s="3">
-        <v>0</v>
-      </c>
-      <c r="L61" s="3">
-        <v>0</v>
-      </c>
       <c r="M61" s="3">
         <v>0</v>
       </c>
@@ -3688,17 +3973,17 @@
         <v>0</v>
       </c>
       <c r="O61" s="3">
+        <v>0</v>
+      </c>
+      <c r="P61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q61" s="3">
         <v>24700</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>28900</v>
       </c>
-      <c r="Q61" s="3">
-        <v>0</v>
-      </c>
-      <c r="R61" s="3">
-        <v>0</v>
-      </c>
       <c r="S61" s="3">
         <v>0</v>
       </c>
@@ -3711,70 +3996,82 @@
       <c r="V61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W61" s="3">
+        <v>0</v>
+      </c>
+      <c r="X61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>160800</v>
+      </c>
+      <c r="E62" s="3">
+        <v>161800</v>
+      </c>
+      <c r="F62" s="3">
         <v>159700</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>157100</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>148700</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>145700</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>129000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>121200</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>115300</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>119800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>148600</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>107400</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>163800</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>148200</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>86300</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>10900</v>
-      </c>
-      <c r="R62" s="3">
-        <v>10900</v>
-      </c>
-      <c r="S62" s="3">
-        <v>20500</v>
       </c>
       <c r="T62" s="3">
         <v>10900</v>
       </c>
-      <c r="U62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V62" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="U62" s="3">
+        <v>20500</v>
+      </c>
+      <c r="V62" s="3">
+        <v>10900</v>
+      </c>
+      <c r="W62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3835,8 +4132,14 @@
       <c r="V63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W63" s="3">
+        <v>0</v>
+      </c>
+      <c r="X63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3897,8 +4200,14 @@
       <c r="V64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W64" s="3">
+        <v>0</v>
+      </c>
+      <c r="X64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3959,70 +4268,82 @@
       <c r="V65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W65" s="3">
+        <v>0</v>
+      </c>
+      <c r="X65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>773300</v>
+      </c>
+      <c r="E66" s="3">
+        <v>775700</v>
+      </c>
+      <c r="F66" s="3">
         <v>795100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>793200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>732300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>725000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>662000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>654300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>622200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>308900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>316100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>235600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>268700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>290900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>214500</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>11900</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>11900</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>21300</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>11400</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>400</v>
       </c>
-      <c r="V66" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="X66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4045,8 +4366,10 @@
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
-    </row>
-    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W67" s="3"/>
+      <c r="X67" s="3"/>
+    </row>
+    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4107,8 +4430,14 @@
       <c r="V68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W68" s="3">
+        <v>0</v>
+      </c>
+      <c r="X68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4169,8 +4498,14 @@
       <c r="V69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W69" s="3">
+        <v>0</v>
+      </c>
+      <c r="X69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4208,17 +4543,17 @@
         <v>0</v>
       </c>
       <c r="O70" s="3">
+        <v>0</v>
+      </c>
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="3">
         <v>615700</v>
       </c>
-      <c r="P70" s="3">
+      <c r="R70" s="3">
         <v>615800</v>
       </c>
-      <c r="Q70" s="3">
-        <v>0</v>
-      </c>
-      <c r="R70" s="3">
-        <v>0</v>
-      </c>
       <c r="S70" s="3">
         <v>0</v>
       </c>
@@ -4231,8 +4566,14 @@
       <c r="V70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W70" s="3">
+        <v>0</v>
+      </c>
+      <c r="X70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4293,70 +4634,82 @@
       <c r="V71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W71" s="3">
+        <v>0</v>
+      </c>
+      <c r="X71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-1686200</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-1614400</v>
+      </c>
+      <c r="F72" s="3">
         <v>-1519600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-1361400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-1236200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-1156800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-1078100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-993600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-900900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-811700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-751500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-682100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-597100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>200</v>
       </c>
-      <c r="P72" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
+        <v>0</v>
+      </c>
+      <c r="S72" s="3">
         <v>1100</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>1200</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>300</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>100</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>-100</v>
       </c>
-      <c r="V72" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="X72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4417,8 +4770,14 @@
       <c r="V73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W73" s="3">
+        <v>0</v>
+      </c>
+      <c r="X73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4479,8 +4838,14 @@
       <c r="V74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W74" s="3">
+        <v>0</v>
+      </c>
+      <c r="X74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4541,70 +4906,82 @@
       <c r="V75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W75" s="3">
+        <v>0</v>
+      </c>
+      <c r="X75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>277900</v>
+      </c>
+      <c r="E76" s="3">
+        <v>327700</v>
+      </c>
+      <c r="F76" s="3">
         <v>392600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>275200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>327500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>355000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>338600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>391700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>465100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>547000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>585400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>535000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>484300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>-616500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>-531000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>305800</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>305900</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>295900</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>304800</v>
       </c>
-      <c r="U76" s="3">
-        <v>0</v>
-      </c>
-      <c r="V76" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W76" s="3">
+        <v>0</v>
+      </c>
+      <c r="X76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4665,137 +5042,155 @@
       <c r="V77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W77" s="3">
+        <v>0</v>
+      </c>
+      <c r="X77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45412</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45322</v>
+      </c>
+      <c r="F80" s="2">
         <v>45230</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45138</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45046</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>44957</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44865</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44773</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44681</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44592</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44500</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44408</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44316</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44227</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44135</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>43738</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>43646</v>
       </c>
-      <c r="V80" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="X80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-71800</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-94700</v>
+      </c>
+      <c r="F81" s="3">
         <v>-158200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-125300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>-79400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>-78700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>-84500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-92700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-89300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-60100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>-69400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>-84900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>-84500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>-103600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>-46600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>-100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>500</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>-600</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>200</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>-100</v>
       </c>
-      <c r="V81" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="X81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4818,70 +5213,78 @@
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
-    </row>
-    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W82" s="3"/>
+      <c r="X82" s="3"/>
+    </row>
+    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>7100</v>
+        <v>7400</v>
       </c>
       <c r="E83" s="3">
-        <v>7000</v>
+        <v>7300</v>
       </c>
       <c r="F83" s="3">
         <v>7100</v>
       </c>
       <c r="G83" s="3">
+        <v>7000</v>
+      </c>
+      <c r="H83" s="3">
+        <v>7100</v>
+      </c>
+      <c r="I83" s="3">
         <v>6500</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>6100</v>
-      </c>
-      <c r="I83" s="3">
-        <v>6300</v>
-      </c>
-      <c r="J83" s="3">
-        <v>6200</v>
       </c>
       <c r="K83" s="3">
         <v>6300</v>
       </c>
       <c r="L83" s="3">
+        <v>6200</v>
+      </c>
+      <c r="M83" s="3">
+        <v>6300</v>
+      </c>
+      <c r="N83" s="3">
         <v>4600</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>2800</v>
       </c>
-      <c r="N83" s="3">
+      <c r="P83" s="3">
         <v>2700</v>
       </c>
-      <c r="O83" s="3">
+      <c r="Q83" s="3">
         <v>2600</v>
       </c>
-      <c r="P83" s="3">
+      <c r="R83" s="3">
         <v>2800</v>
       </c>
-      <c r="Q83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S83" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U83" s="3">
-        <v>0</v>
-      </c>
-      <c r="V83" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="U83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W83" s="3">
+        <v>0</v>
+      </c>
+      <c r="X83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4942,8 +5345,14 @@
       <c r="V84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W84" s="3">
+        <v>0</v>
+      </c>
+      <c r="X84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5004,8 +5413,14 @@
       <c r="V85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W85" s="3">
+        <v>0</v>
+      </c>
+      <c r="X85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5066,8 +5481,14 @@
       <c r="V86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W86" s="3">
+        <v>0</v>
+      </c>
+      <c r="X86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5128,8 +5549,14 @@
       <c r="V87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W87" s="3">
+        <v>0</v>
+      </c>
+      <c r="X87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5190,70 +5617,82 @@
       <c r="V88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W88" s="3">
+        <v>0</v>
+      </c>
+      <c r="X88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-62500</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-41500</v>
+      </c>
+      <c r="F89" s="3">
         <v>-96900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>-86400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>-104200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>-50400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>-83000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-62900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-70800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>-48100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>-47900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>-23700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>-37500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>-20900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>-20900</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>-100</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>-300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>-300</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>-700</v>
       </c>
-      <c r="U89" s="3">
-        <v>0</v>
-      </c>
-      <c r="V89" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W89" s="3">
+        <v>0</v>
+      </c>
+      <c r="X89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5276,70 +5715,78 @@
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
-    </row>
-    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W90" s="3"/>
+      <c r="X90" s="3"/>
+    </row>
+    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="E91" s="3">
         <v>-4800</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
+        <v>-4800</v>
+      </c>
+      <c r="G91" s="3">
         <v>-4000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-5800</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-4400</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-5300</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-5700</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-3200</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-4300</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-4300</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-3700</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-4100</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-2600</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>-3000</v>
       </c>
-      <c r="Q91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S91" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U91" s="3">
-        <v>0</v>
-      </c>
-      <c r="V91" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="U91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W91" s="3">
+        <v>0</v>
+      </c>
+      <c r="X91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5400,8 +5847,14 @@
       <c r="V92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W92" s="3">
+        <v>0</v>
+      </c>
+      <c r="X92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5462,70 +5915,82 @@
       <c r="V93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W93" s="3">
+        <v>0</v>
+      </c>
+      <c r="X93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="E94" s="3">
         <v>-4800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
+        <v>-4800</v>
+      </c>
+      <c r="G94" s="3">
         <v>-4000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>99200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>100600</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>69700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-290500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-5900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-4300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-209600</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-3700</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-4100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-2600</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-3000</v>
       </c>
-      <c r="Q94" s="3">
-        <v>0</v>
-      </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
+        <v>0</v>
+      </c>
+      <c r="T94" s="3">
         <v>100</v>
       </c>
-      <c r="S94" s="3">
-        <v>0</v>
-      </c>
-      <c r="T94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U94" s="3" t="s">
-        <v>3</v>
+      <c r="U94" s="3">
+        <v>0</v>
       </c>
       <c r="V94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5548,8 +6013,10 @@
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
-    </row>
-    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W95" s="3"/>
+      <c r="X95" s="3"/>
+    </row>
+    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5610,8 +6077,14 @@
       <c r="V96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W96" s="3">
+        <v>0</v>
+      </c>
+      <c r="X96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5672,8 +6145,14 @@
       <c r="V97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W97" s="3">
+        <v>0</v>
+      </c>
+      <c r="X97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5734,8 +6213,14 @@
       <c r="V98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W98" s="3">
+        <v>0</v>
+      </c>
+      <c r="X98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5796,117 +6281,129 @@
       <c r="V99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W99" s="3">
+        <v>0</v>
+      </c>
+      <c r="X99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E100" s="3">
+        <v>5800</v>
+      </c>
+      <c r="F100" s="3">
         <v>236700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>40300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>23800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>54900</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>14400</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>303100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>2500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>5600</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>35600</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>506000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>200</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>3400</v>
       </c>
-      <c r="Q100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S100" s="3">
+      <c r="S100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U100" s="3">
         <v>-100</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>315500</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>100</v>
       </c>
-      <c r="V100" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="X100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E101" s="3">
+        <v>800</v>
+      </c>
+      <c r="F101" s="3">
         <v>-1500</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>300</v>
       </c>
-      <c r="F101" s="3">
+      <c r="H101" s="3">
         <v>500</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>800</v>
       </c>
-      <c r="H101" s="3">
+      <c r="J101" s="3">
         <v>-500</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>-100</v>
       </c>
-      <c r="J101" s="3">
+      <c r="L101" s="3">
         <v>-1000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="M101" s="3">
         <v>-300</v>
       </c>
-      <c r="L101" s="3">
+      <c r="N101" s="3">
         <v>-700</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
-      </c>
-      <c r="N101" s="3">
-        <v>0</v>
-      </c>
       <c r="O101" s="3">
+        <v>0</v>
+      </c>
+      <c r="P101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q101" s="3">
         <v>100</v>
       </c>
-      <c r="P101" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R101" s="3" t="s">
-        <v>3</v>
+      <c r="R101" s="3">
+        <v>0</v>
       </c>
       <c r="S101" s="3" t="s">
         <v>3</v>
@@ -5914,72 +6411,84 @@
       <c r="T101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U101" s="3">
-        <v>0</v>
-      </c>
-      <c r="V101" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="U101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W101" s="3">
+        <v>0</v>
+      </c>
+      <c r="X101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-65600</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-39600</v>
+      </c>
+      <c r="F102" s="3">
         <v>133500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-49800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>19200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>105900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-352900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>225300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-50300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-252600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>8300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>464300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>-23200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>-20400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>-100</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>-200</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>-400</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>800</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>100</v>
       </c>
-      <c r="V102" s="3" t="s">
+      <c r="X102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/CHPT_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CHPT_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="92">
   <si>
     <t>CHPT</t>
   </si>
@@ -656,161 +656,165 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:X102"/>
+  <dimension ref="A5:Y102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45504</v>
+      </c>
+      <c r="E7" s="2">
         <v>45412</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45322</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45230</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45138</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45046</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44957</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44865</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44773</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44681</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44592</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44500</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44408</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44316</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44227</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44135</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43921</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43830</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43738</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43646</v>
       </c>
-      <c r="X7" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>108500</v>
+      </c>
+      <c r="E8" s="3">
         <v>107000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>115800</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>110300</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>150500</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>130000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>152800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>125300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>108300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>81600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>79300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>65000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>56100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>40500</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>42400</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>36400</v>
       </c>
-      <c r="S8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T8" s="3" t="s">
         <v>3</v>
       </c>
@@ -820,65 +824,68 @@
       <c r="V8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W8" s="3">
-        <v>0</v>
+      <c r="W8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>83000</v>
+      </c>
+      <c r="E9" s="3">
         <v>83400</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>93400</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>92200</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>121400</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>99500</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>119800</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>102700</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>90100</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>69500</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>61900</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>49000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>45300</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>31300</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>33500</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>29100</v>
       </c>
-      <c r="S9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T9" s="3" t="s">
         <v>3</v>
       </c>
@@ -894,59 +901,62 @@
       <c r="X9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>25500</v>
+      </c>
+      <c r="E10" s="3">
         <v>23600</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>22400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>18100</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>29100</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>30500</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>33000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>22600</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>18200</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>12100</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>17400</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>16000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>10800</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>9200</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>8900</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>7300</v>
       </c>
-      <c r="S10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T10" s="3" t="s">
         <v>3</v>
       </c>
@@ -962,8 +972,11 @@
       <c r="X10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -988,59 +1001,60 @@
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
-    </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y11" s="3"/>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>36500</v>
+      </c>
+      <c r="E12" s="3">
         <v>36100</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>51900</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>52300</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>59600</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>49400</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>46700</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>48100</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>51800</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>48300</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>42500</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>36800</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>40400</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>25400</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>20900</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>18900</v>
       </c>
-      <c r="S12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1056,8 +1070,11 @@
       <c r="X12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1124,26 +1141,29 @@
       <c r="X13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E14" s="3">
+      <c r="E14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F14" s="3">
         <v>-2600</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>56600</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>28000</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1156,15 +1176,15 @@
       <c r="L14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M14" s="3">
+      <c r="M14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N14" s="3">
         <v>200</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>4800</v>
       </c>
-      <c r="O14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1177,8 +1197,8 @@
       <c r="S14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T14" s="3">
-        <v>0</v>
+      <c r="T14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U14" s="3">
         <v>0</v>
@@ -1192,8 +1212,11 @@
       <c r="X14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1260,8 +1283,11 @@
       <c r="X15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1283,127 +1309,131 @@
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
-    </row>
-    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y16" s="3"/>
+    </row>
+    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>171300</v>
+      </c>
+      <c r="E17" s="3">
         <v>174200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>208800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>264100</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>273800</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>210000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>231100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>208600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>198700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>171500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>158600</v>
-      </c>
-      <c r="N17" s="3">
-        <v>130400</v>
       </c>
       <c r="O17" s="3">
         <v>130400</v>
       </c>
       <c r="P17" s="3">
+        <v>130400</v>
+      </c>
+      <c r="Q17" s="3">
         <v>87100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>77700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>69000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>200</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>300</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1600</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>600</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>100</v>
       </c>
-      <c r="X17" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-62800</v>
+      </c>
+      <c r="E18" s="3">
         <v>-67200</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-93000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-153800</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-123300</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-80000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-78300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-83300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-90400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-89900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-79300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-65400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-74300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-46600</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-35300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-32600</v>
       </c>
-      <c r="S18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1413,14 +1443,17 @@
       <c r="V18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W18" s="3">
+      <c r="W18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X18" s="3">
         <v>-100</v>
       </c>
-      <c r="X18" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1445,59 +1478,60 @@
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
-    </row>
-    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y19" s="3"/>
+    </row>
+    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E20" s="3">
         <v>2400</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>4600</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-1000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>1900</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>3100</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>3200</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>1000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>200</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-300</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>16400</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-4400</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-10600</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>130400</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-54600</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-7400</v>
       </c>
-      <c r="S20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1507,65 +1541,68 @@
       <c r="V20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W20" s="3">
-        <v>0</v>
-      </c>
-      <c r="X20" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="W20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-53200</v>
+      </c>
+      <c r="E21" s="3">
         <v>-57300</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-81000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-147600</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-114500</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-69800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-68700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-76200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-83900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-84000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-56600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-65200</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-82000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>86600</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-87300</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-37200</v>
       </c>
-      <c r="S21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1581,8 +1618,11 @@
       <c r="X21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1593,29 +1633,29 @@
         <v>6600</v>
       </c>
       <c r="F22" s="3">
+        <v>6600</v>
+      </c>
+      <c r="G22" s="3">
         <v>3800</v>
-      </c>
-      <c r="G22" s="3">
-        <v>2900</v>
       </c>
       <c r="H22" s="3">
         <v>2900</v>
       </c>
       <c r="I22" s="3">
+        <v>2900</v>
+      </c>
+      <c r="J22" s="3">
         <v>3000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>2600</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>2900</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>900</v>
       </c>
-      <c r="M22" s="3">
-        <v>0</v>
-      </c>
       <c r="N22" s="3">
         <v>0</v>
       </c>
@@ -1623,16 +1663,16 @@
         <v>0</v>
       </c>
       <c r="P22" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="3">
         <v>1500</v>
-      </c>
-      <c r="Q22" s="3">
-        <v>800</v>
       </c>
       <c r="R22" s="3">
         <v>800</v>
       </c>
-      <c r="S22" s="3" t="s">
-        <v>3</v>
+      <c r="S22" s="3">
+        <v>800</v>
       </c>
       <c r="T22" s="3" t="s">
         <v>3</v>
@@ -1643,150 +1683,159 @@
       <c r="V22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W22" s="3">
-        <v>0</v>
+      <c r="W22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-67200</v>
+      </c>
+      <c r="E23" s="3">
         <v>-71400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-94900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-158500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-124400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-79800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-78100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-84900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-93100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-91100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-62900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-69800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-84900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>82300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-90800</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-40800</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-100</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>700</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-400</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>400</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-100</v>
       </c>
-      <c r="X23" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E24" s="3">
         <v>400</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-200</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-300</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>900</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-400</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>500</v>
-      </c>
-      <c r="J24" s="3">
-        <v>-400</v>
       </c>
       <c r="K24" s="3">
         <v>-400</v>
       </c>
       <c r="L24" s="3">
+        <v>-400</v>
+      </c>
+      <c r="M24" s="3">
         <v>-1900</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-2700</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-300</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>100</v>
       </c>
-      <c r="P24" s="3">
-        <v>0</v>
-      </c>
       <c r="Q24" s="3">
         <v>0</v>
       </c>
       <c r="R24" s="3">
+        <v>0</v>
+      </c>
+      <c r="S24" s="3">
         <v>100</v>
       </c>
-      <c r="S24" s="3">
-        <v>0</v>
-      </c>
       <c r="T24" s="3">
+        <v>0</v>
+      </c>
+      <c r="U24" s="3">
         <v>200</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>300</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>200</v>
       </c>
-      <c r="W24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1853,144 +1902,153 @@
       <c r="X25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-68900</v>
+      </c>
+      <c r="E26" s="3">
         <v>-71800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-94700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-158200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-125300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-79400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-78700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-84500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-92700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-89300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-60100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-69400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-84900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>82300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-90700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-40900</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-100</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>500</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-600</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>200</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-100</v>
       </c>
-      <c r="X26" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-68900</v>
+      </c>
+      <c r="E27" s="3">
         <v>-71800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-94700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-158200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-125300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-79400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-78700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-84500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-92700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-89300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-60100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-69400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-84900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-84500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-103600</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-46600</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>500</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-600</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>200</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-100</v>
       </c>
-      <c r="X27" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2057,8 +2115,11 @@
       <c r="X28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2125,8 +2186,11 @@
       <c r="X29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2193,8 +2257,11 @@
       <c r="X30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2261,59 +2328,62 @@
       <c r="X31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="E32" s="3">
         <v>-2400</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-4600</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>1000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-1900</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-3100</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-3200</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-1000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-200</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>300</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-16400</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>4400</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>10600</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-130400</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>54600</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>7400</v>
       </c>
-      <c r="S32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2323,82 +2393,88 @@
       <c r="V32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W32" s="3">
-        <v>0</v>
-      </c>
-      <c r="X32" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="W32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-68900</v>
+      </c>
+      <c r="E33" s="3">
         <v>-71800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-94700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-158200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-125300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-79400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-78700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-84500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-92700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-89300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-60100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-69400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-84900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-84500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-103600</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-46600</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>500</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-600</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>200</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-100</v>
       </c>
-      <c r="X33" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2465,149 +2541,158 @@
       <c r="X34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-68900</v>
+      </c>
+      <c r="E35" s="3">
         <v>-71800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-94700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-158200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-125300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-79400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-78700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-84500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-92700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-89300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-60100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-69400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-84900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-84500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-103600</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-46600</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>500</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-600</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>200</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-100</v>
       </c>
-      <c r="X35" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45504</v>
+      </c>
+      <c r="E38" s="2">
         <v>45412</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45322</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45230</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45138</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45046</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44957</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44865</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44773</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44681</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44592</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44500</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44408</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44316</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44227</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44135</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43921</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43830</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43738</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43646</v>
       </c>
-      <c r="X38" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2632,8 +2717,9 @@
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
-    </row>
-    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y39" s="3"/>
+    </row>
+    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2658,84 +2744,88 @@
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
-    </row>
-    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y40" s="3"/>
+    </row>
+    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>243300</v>
+      </c>
+      <c r="E41" s="3">
         <v>261900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>327400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>367000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>233500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>283300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>264200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>188300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>187700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>540600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>315200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>365500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>618100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>609800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>145500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>168700</v>
       </c>
-      <c r="S41" s="3">
-        <v>0</v>
-      </c>
       <c r="T41" s="3">
+        <v>0</v>
+      </c>
+      <c r="U41" s="3">
         <v>200</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>400</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>800</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>100</v>
       </c>
-      <c r="X41" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E42" s="3">
-        <v>0</v>
+      <c r="E42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F42" s="3">
         <v>0</v>
@@ -2747,17 +2837,17 @@
         <v>0</v>
       </c>
       <c r="I42" s="3">
+        <v>0</v>
+      </c>
+      <c r="J42" s="3">
         <v>105000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>208900</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>283900</v>
       </c>
-      <c r="L42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2773,8 +2863,8 @@
       <c r="Q42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R42" s="3">
-        <v>0</v>
+      <c r="R42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S42" s="3">
         <v>0</v>
@@ -2794,59 +2884,62 @@
       <c r="X42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>111500</v>
+      </c>
+      <c r="E43" s="3">
         <v>117800</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>124000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>151800</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>202100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>165100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>164900</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>123000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>109900</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>79900</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>75900</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>66100</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>42700</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>34900</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>35100</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>28300</v>
       </c>
-      <c r="S43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2856,65 +2949,68 @@
       <c r="V43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W43" s="3">
-        <v>0</v>
+      <c r="W43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>228500</v>
+      </c>
+      <c r="E44" s="3">
         <v>223600</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>198600</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>199100</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>143600</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>115200</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>68700</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>62400</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>53400</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>45300</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>35900</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>29900</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>27900</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>28900</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>33600</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>30700</v>
       </c>
-      <c r="S44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T44" s="3" t="s">
         <v>3</v>
       </c>
@@ -2924,150 +3020,159 @@
       <c r="V44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W44" s="3">
-        <v>0</v>
+      <c r="W44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>69600</v>
+      </c>
+      <c r="E45" s="3">
         <v>95100</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>92600</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>106500</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>113100</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>118500</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>101400</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>59000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>45300</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>46500</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>37000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>33100</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>22500</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>20300</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>12500</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>15200</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>200</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>300</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>400</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>300</v>
       </c>
-      <c r="W45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>652900</v>
+      </c>
+      <c r="E46" s="3">
         <v>698300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>742700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>824400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>692200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>682200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>704200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>641600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>680200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>712200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>464100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>494600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>711300</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>693900</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>226600</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>242900</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>300</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>500</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>800</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>1100</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>100</v>
       </c>
-      <c r="X46" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3117,76 +3222,79 @@
         <v>0</v>
       </c>
       <c r="S47" s="3">
+        <v>0</v>
+      </c>
+      <c r="T47" s="3">
         <v>317400</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>317300</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>316400</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>315100</v>
       </c>
-      <c r="W47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>54900</v>
+      </c>
+      <c r="E48" s="3">
         <v>55600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>57800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>60300</v>
-      </c>
-      <c r="G48" s="3">
-        <v>62900</v>
       </c>
       <c r="H48" s="3">
         <v>62900</v>
       </c>
       <c r="I48" s="3">
+        <v>62900</v>
+      </c>
+      <c r="J48" s="3">
         <v>62300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>60600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>59300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>59200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>60100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>58300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>53100</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>53000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>51800</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>50800</v>
       </c>
-      <c r="S48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3196,52 +3304,55 @@
       <c r="V48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W48" s="3">
-        <v>0</v>
+      <c r="W48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>288200</v>
+      </c>
+      <c r="E49" s="3">
         <v>289300</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>294300</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>294200</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>304500</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>307500</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>306400</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>291400</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>300100</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>309600</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>325700</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>343200</v>
-      </c>
-      <c r="O49" s="3">
-        <v>1200</v>
       </c>
       <c r="P49" s="3">
         <v>1200</v>
@@ -3252,8 +3363,8 @@
       <c r="R49" s="3">
         <v>1200</v>
       </c>
-      <c r="S49" s="3" t="s">
-        <v>3</v>
+      <c r="S49" s="3">
+        <v>1200</v>
       </c>
       <c r="T49" s="3" t="s">
         <v>3</v>
@@ -3264,14 +3375,17 @@
       <c r="V49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W49" s="3">
-        <v>0</v>
+      <c r="W49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3338,8 +3452,11 @@
       <c r="X50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3406,76 +3523,82 @@
       <c r="X51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>7700</v>
+      </c>
+      <c r="E52" s="3">
         <v>8000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>8600</v>
-      </c>
-      <c r="F52" s="3">
-        <v>8700</v>
       </c>
       <c r="G52" s="3">
         <v>8700</v>
       </c>
       <c r="H52" s="3">
+        <v>8700</v>
+      </c>
+      <c r="I52" s="3">
         <v>7300</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>7100</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>7000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>6500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>6300</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>6000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>5300</v>
-      </c>
-      <c r="O52" s="3">
-        <v>5000</v>
       </c>
       <c r="P52" s="3">
         <v>5000</v>
       </c>
       <c r="Q52" s="3">
+        <v>5000</v>
+      </c>
+      <c r="R52" s="3">
         <v>10500</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>4300</v>
       </c>
-      <c r="S52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U52" s="3">
+      <c r="U52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V52" s="3">
         <v>316400</v>
       </c>
-      <c r="V52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W52" s="3">
+      <c r="W52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X52" s="3">
         <v>300</v>
       </c>
-      <c r="X52" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3542,76 +3665,82 @@
       <c r="X53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1003800</v>
+      </c>
+      <c r="E54" s="3">
         <v>1051200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1103400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1187700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1068400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1059800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1080000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1000600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1046000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1087300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>855900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>901500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>770600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>753100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>290100</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>299300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>317700</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>317800</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>317200</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>316200</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>400</v>
       </c>
-      <c r="X54" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3636,8 +3765,9 @@
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
-    </row>
-    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y55" s="3"/>
+    </row>
+    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3662,76 +3792,80 @@
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
-    </row>
-    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y56" s="3"/>
+    </row>
+    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>71400</v>
+      </c>
+      <c r="E57" s="3">
         <v>84100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>71100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>101700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>99000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>62000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>62100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>44500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>45100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>35400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>27600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>32100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>28400</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>18100</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>19800</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>16700</v>
-      </c>
-      <c r="S57" s="3">
-        <v>100</v>
       </c>
       <c r="T57" s="3">
         <v>100</v>
       </c>
       <c r="U57" s="3">
+        <v>100</v>
+      </c>
+      <c r="V57" s="3">
         <v>200</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>100</v>
       </c>
-      <c r="W57" s="3">
-        <v>0</v>
-      </c>
-      <c r="X57" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="X57" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3775,200 +3909,209 @@
         <v>0</v>
       </c>
       <c r="Q58" s="3">
+        <v>0</v>
+      </c>
+      <c r="R58" s="3">
         <v>10200</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>5800</v>
       </c>
-      <c r="S58" s="3">
-        <v>0</v>
-      </c>
       <c r="T58" s="3">
         <v>0</v>
       </c>
       <c r="U58" s="3">
         <v>0</v>
       </c>
-      <c r="V58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W58" s="3">
+      <c r="V58" s="3">
+        <v>0</v>
+      </c>
+      <c r="W58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X58" s="3">
         <v>100</v>
       </c>
-      <c r="X58" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>249500</v>
+      </c>
+      <c r="E59" s="3">
         <v>243700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>259100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>251000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>241500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>226400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>222300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>193800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>193600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>177500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>161500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>135400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>99700</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>86800</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>88100</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>76700</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>900</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>800</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>600</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>400</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>300</v>
       </c>
-      <c r="X59" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>321000</v>
+      </c>
+      <c r="E60" s="3">
         <v>327800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>330200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>352600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>340500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>288400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>284300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>238400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>238800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>212800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>189000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>167400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>128200</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>104900</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>118100</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>99300</v>
-      </c>
-      <c r="S60" s="3">
-        <v>1000</v>
       </c>
       <c r="T60" s="3">
         <v>1000</v>
       </c>
       <c r="U60" s="3">
+        <v>1000</v>
+      </c>
+      <c r="V60" s="3">
         <v>800</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>500</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>400</v>
       </c>
-      <c r="X60" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>285700</v>
+      </c>
+      <c r="E61" s="3">
         <v>284700</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>283700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>282700</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>295500</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>295200</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>294900</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>294600</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>294300</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>294100</v>
       </c>
-      <c r="M61" s="3">
-        <v>0</v>
-      </c>
       <c r="N61" s="3">
         <v>0</v>
       </c>
@@ -3979,14 +4122,14 @@
         <v>0</v>
       </c>
       <c r="Q61" s="3">
+        <v>0</v>
+      </c>
+      <c r="R61" s="3">
         <v>24700</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>28900</v>
       </c>
-      <c r="S61" s="3">
-        <v>0</v>
-      </c>
       <c r="T61" s="3">
         <v>0</v>
       </c>
@@ -4002,76 +4145,82 @@
       <c r="X61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>166200</v>
+      </c>
+      <c r="E62" s="3">
         <v>160800</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>161800</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>159700</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>157100</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>148700</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>145700</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>129000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>121200</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>115300</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>119800</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>148600</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>107400</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>163800</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>148200</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>86300</v>
-      </c>
-      <c r="S62" s="3">
-        <v>10900</v>
       </c>
       <c r="T62" s="3">
         <v>10900</v>
       </c>
       <c r="U62" s="3">
+        <v>10900</v>
+      </c>
+      <c r="V62" s="3">
         <v>20500</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>10900</v>
       </c>
-      <c r="W62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4138,8 +4287,11 @@
       <c r="X63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4206,8 +4358,11 @@
       <c r="X64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4274,76 +4429,82 @@
       <c r="X65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>772900</v>
+      </c>
+      <c r="E66" s="3">
         <v>773300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>775700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>795100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>793200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>732300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>725000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>662000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>654300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>622200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>308900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>316100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>235600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>268700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>290900</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>214500</v>
-      </c>
-      <c r="S66" s="3">
-        <v>11900</v>
       </c>
       <c r="T66" s="3">
         <v>11900</v>
       </c>
       <c r="U66" s="3">
+        <v>11900</v>
+      </c>
+      <c r="V66" s="3">
         <v>21300</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>11400</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>400</v>
       </c>
-      <c r="X66" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4368,8 +4529,9 @@
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
-    </row>
-    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y67" s="3"/>
+    </row>
+    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4436,8 +4598,11 @@
       <c r="X68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4504,8 +4669,11 @@
       <c r="X69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4549,14 +4717,14 @@
         <v>0</v>
       </c>
       <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+      <c r="R70" s="3">
         <v>615700</v>
       </c>
-      <c r="R70" s="3">
+      <c r="S70" s="3">
         <v>615800</v>
       </c>
-      <c r="S70" s="3">
-        <v>0</v>
-      </c>
       <c r="T70" s="3">
         <v>0</v>
       </c>
@@ -4572,8 +4740,11 @@
       <c r="X70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4640,76 +4811,82 @@
       <c r="X71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-1755000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-1686200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-1614400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-1519600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-1361400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-1236200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-1156800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-1078100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-993600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-900900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-811700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-751500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-682100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-597100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>200</v>
       </c>
-      <c r="R72" s="3">
-        <v>0</v>
-      </c>
       <c r="S72" s="3">
+        <v>0</v>
+      </c>
+      <c r="T72" s="3">
         <v>1100</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>1200</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>300</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>100</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-100</v>
       </c>
-      <c r="X72" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4776,8 +4953,11 @@
       <c r="X73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4844,8 +5024,11 @@
       <c r="X74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4912,76 +5095,82 @@
       <c r="X75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>230900</v>
+      </c>
+      <c r="E76" s="3">
         <v>277900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>327700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>392600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>275200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>327500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>355000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>338600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>391700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>465100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>547000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>585400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>535000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>484300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>-616500</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>-531000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>305800</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>305900</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>295900</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>304800</v>
       </c>
-      <c r="W76" s="3">
-        <v>0</v>
-      </c>
-      <c r="X76" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="X76" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5048,149 +5237,158 @@
       <c r="X77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45504</v>
+      </c>
+      <c r="E80" s="2">
         <v>45412</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45322</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45230</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45138</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45046</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44957</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44865</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44773</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44681</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44592</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44500</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44408</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44316</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44227</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44135</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43921</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43830</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43738</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43646</v>
       </c>
-      <c r="X80" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-68900</v>
+      </c>
+      <c r="E81" s="3">
         <v>-71800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-94700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-158200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-125300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-79400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-78700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-84500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-92700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-89300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-60100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-69400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-84900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-84500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-103600</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-46600</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>500</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-600</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>200</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-100</v>
       </c>
-      <c r="X81" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5215,59 +5413,60 @@
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
-    </row>
-    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y82" s="3"/>
+    </row>
+    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>7500</v>
+      </c>
+      <c r="E83" s="3">
         <v>7400</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>7300</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>7100</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>7000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>7100</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>6500</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>6100</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>6300</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>6200</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>6300</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>4600</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>2800</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>2700</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>2600</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>2800</v>
       </c>
-      <c r="S83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T83" s="3" t="s">
         <v>3</v>
       </c>
@@ -5277,14 +5476,17 @@
       <c r="V83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W83" s="3">
-        <v>0</v>
+      <c r="W83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5351,8 +5553,11 @@
       <c r="X84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5419,8 +5624,11 @@
       <c r="X85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5487,8 +5695,11 @@
       <c r="X86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5555,8 +5766,11 @@
       <c r="X87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5623,76 +5837,82 @@
       <c r="X88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-51200</v>
+      </c>
+      <c r="E89" s="3">
         <v>-62500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-41500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-96900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-86400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-104200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-50400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-83000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-62900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-70800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-48100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-47900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-23700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-37500</v>
-      </c>
-      <c r="Q89" s="3">
-        <v>-20900</v>
       </c>
       <c r="R89" s="3">
         <v>-20900</v>
       </c>
       <c r="S89" s="3">
+        <v>-20900</v>
+      </c>
+      <c r="T89" s="3">
         <v>-100</v>
-      </c>
-      <c r="T89" s="3">
-        <v>-300</v>
       </c>
       <c r="U89" s="3">
         <v>-300</v>
       </c>
       <c r="V89" s="3">
+        <v>-300</v>
+      </c>
+      <c r="W89" s="3">
         <v>-700</v>
       </c>
-      <c r="W89" s="3">
-        <v>0</v>
-      </c>
-      <c r="X89" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="X89" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5717,59 +5937,60 @@
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
-    </row>
-    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y90" s="3"/>
+    </row>
+    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-3800</v>
+      </c>
+      <c r="E91" s="3">
         <v>-3500</v>
-      </c>
-      <c r="E91" s="3">
-        <v>-4800</v>
       </c>
       <c r="F91" s="3">
         <v>-4800</v>
       </c>
       <c r="G91" s="3">
+        <v>-4800</v>
+      </c>
+      <c r="H91" s="3">
         <v>-4000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-5800</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-4400</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-5300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-5700</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-3200</v>
-      </c>
-      <c r="M91" s="3">
-        <v>-4300</v>
       </c>
       <c r="N91" s="3">
         <v>-4300</v>
       </c>
       <c r="O91" s="3">
+        <v>-4300</v>
+      </c>
+      <c r="P91" s="3">
         <v>-3700</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-4100</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-2600</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-3000</v>
       </c>
-      <c r="S91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T91" s="3" t="s">
         <v>3</v>
       </c>
@@ -5779,14 +6000,17 @@
       <c r="V91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W91" s="3">
-        <v>0</v>
+      <c r="W91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5853,8 +6077,11 @@
       <c r="X92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5921,67 +6148,70 @@
       <c r="X93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-3800</v>
+      </c>
+      <c r="E94" s="3">
         <v>-3500</v>
-      </c>
-      <c r="E94" s="3">
-        <v>-4800</v>
       </c>
       <c r="F94" s="3">
         <v>-4800</v>
       </c>
       <c r="G94" s="3">
+        <v>-4800</v>
+      </c>
+      <c r="H94" s="3">
         <v>-4000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>99200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>100600</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>69700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-290500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-5900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-4300</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-209600</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-3700</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-4100</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-2600</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-3000</v>
       </c>
-      <c r="S94" s="3">
-        <v>0</v>
-      </c>
       <c r="T94" s="3">
+        <v>0</v>
+      </c>
+      <c r="U94" s="3">
         <v>100</v>
       </c>
-      <c r="U94" s="3">
-        <v>0</v>
-      </c>
-      <c r="V94" s="3" t="s">
-        <v>3</v>
+      <c r="V94" s="3">
+        <v>0</v>
       </c>
       <c r="W94" s="3" t="s">
         <v>3</v>
@@ -5989,8 +6219,11 @@
       <c r="X94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6015,8 +6248,9 @@
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
-    </row>
-    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y95" s="3"/>
+    </row>
+    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6083,8 +6317,11 @@
       <c r="X96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6151,8 +6388,11 @@
       <c r="X97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6219,8 +6459,11 @@
       <c r="X98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6287,126 +6530,132 @@
       <c r="X99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>5900</v>
+      </c>
+      <c r="E100" s="3">
         <v>1000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>5800</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>236700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>40300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>23800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>54900</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>14400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>303100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>2500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>5600</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>35600</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>506000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>200</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>3400</v>
       </c>
-      <c r="S100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U100" s="3">
+      <c r="U100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V100" s="3">
         <v>-100</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>315500</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>100</v>
       </c>
-      <c r="X100" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>500</v>
+      </c>
+      <c r="E101" s="3">
         <v>-600</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>800</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-1500</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>300</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>500</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>800</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-500</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-100</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-1000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-300</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-700</v>
       </c>
-      <c r="O101" s="3">
-        <v>0</v>
-      </c>
       <c r="P101" s="3">
         <v>0</v>
       </c>
       <c r="Q101" s="3">
+        <v>0</v>
+      </c>
+      <c r="R101" s="3">
         <v>100</v>
       </c>
-      <c r="R101" s="3">
-        <v>0</v>
-      </c>
-      <c r="S101" s="3" t="s">
-        <v>3</v>
+      <c r="S101" s="3">
+        <v>0</v>
       </c>
       <c r="T101" s="3" t="s">
         <v>3</v>
@@ -6417,78 +6666,84 @@
       <c r="V101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W101" s="3">
-        <v>0</v>
+      <c r="W101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-48600</v>
+      </c>
+      <c r="E102" s="3">
         <v>-65600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-39600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>133500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-49800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>19200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>105900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-352900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>225300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-50300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-252600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>8300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>464300</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-23200</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-20400</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-100</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-200</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-400</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>800</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>100</v>
       </c>
-      <c r="X102" s="3" t="s">
+      <c r="Y102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/CHPT_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CHPT_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="92">
   <si>
     <t>CHPT</t>
   </si>
@@ -656,168 +656,172 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Y102"/>
+  <dimension ref="A5:Z102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45596</v>
+      </c>
+      <c r="E7" s="2">
         <v>45504</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45412</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45322</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45230</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45138</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45046</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44957</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44865</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44773</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44681</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44592</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44500</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44408</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44316</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44227</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44135</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44012</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43921</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43830</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43738</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43646</v>
       </c>
-      <c r="Y7" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>99600</v>
+      </c>
+      <c r="E8" s="3">
         <v>108500</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>107000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>115800</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>110300</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>150500</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>130000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>152800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>125300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>108300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>81600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>79300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>65000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>56100</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>40500</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>42400</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>36400</v>
       </c>
-      <c r="T8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U8" s="3" t="s">
         <v>3</v>
       </c>
@@ -827,68 +831,71 @@
       <c r="W8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X8" s="3">
-        <v>0</v>
+      <c r="X8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>75900</v>
+      </c>
+      <c r="E9" s="3">
         <v>83000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>83400</v>
       </c>
-      <c r="F9" s="3">
-        <v>93400</v>
-      </c>
       <c r="G9" s="3">
-        <v>92200</v>
+        <v>92800</v>
       </c>
       <c r="H9" s="3">
-        <v>121400</v>
+        <v>134200</v>
       </c>
       <c r="I9" s="3">
+        <v>149400</v>
+      </c>
+      <c r="J9" s="3">
         <v>99500</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>119800</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>102700</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>90100</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>69500</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>61900</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>49000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>45300</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>31300</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>33500</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>29100</v>
       </c>
-      <c r="T9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U9" s="3" t="s">
         <v>3</v>
       </c>
@@ -904,62 +911,65 @@
       <c r="Y9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>25500</v>
+        <v>23700</v>
       </c>
       <c r="E10" s="3">
+        <v>25600</v>
+      </c>
+      <c r="F10" s="3">
         <v>23600</v>
       </c>
-      <c r="F10" s="3">
-        <v>22400</v>
-      </c>
       <c r="G10" s="3">
-        <v>18100</v>
+        <v>23000</v>
       </c>
       <c r="H10" s="3">
-        <v>29100</v>
+        <v>-23900</v>
       </c>
       <c r="I10" s="3">
+        <v>1100</v>
+      </c>
+      <c r="J10" s="3">
         <v>30500</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>33000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>22600</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>18200</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>12100</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>17400</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>16000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>10800</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>9200</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>8900</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>7300</v>
       </c>
-      <c r="T10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U10" s="3" t="s">
         <v>3</v>
       </c>
@@ -975,8 +985,11 @@
       <c r="Y10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1002,62 +1015,63 @@
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
-    </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z11" s="3"/>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>35400</v>
+      </c>
+      <c r="E12" s="3">
         <v>36500</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>36100</v>
       </c>
-      <c r="F12" s="3">
-        <v>51900</v>
-      </c>
       <c r="G12" s="3">
-        <v>52300</v>
+        <v>47700</v>
       </c>
       <c r="H12" s="3">
+        <v>56500</v>
+      </c>
+      <c r="I12" s="3">
         <v>59600</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>49400</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>46700</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>48100</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>51800</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>48300</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>42500</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>36800</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>40400</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>25400</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>20900</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>18900</v>
       </c>
-      <c r="T12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1073,8 +1087,11 @@
       <c r="Y12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1144,25 +1161,28 @@
       <c r="Y13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>3</v>
+      <c r="D14" s="3">
+        <v>9800</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F14" s="3">
-        <v>-2600</v>
+      <c r="F14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G14" s="3">
-        <v>56600</v>
-      </c>
-      <c r="H14" s="3">
-        <v>28000</v>
+        <v>12700</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I14" s="3" t="s">
         <v>3</v>
@@ -1179,15 +1199,15 @@
       <c r="M14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N14" s="3">
+      <c r="N14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O14" s="3">
         <v>200</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>4800</v>
       </c>
-      <c r="P14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1200,8 +1220,8 @@
       <c r="T14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U14" s="3">
-        <v>0</v>
+      <c r="U14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V14" s="3">
         <v>0</v>
@@ -1215,31 +1235,34 @@
       <c r="Y14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>7300</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>7500</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>7400</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>7300</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>7100</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>7000</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>7100</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1286,8 +1309,11 @@
       <c r="Y15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1310,133 +1336,137 @@
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
-    </row>
-    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z16" s="3"/>
+    </row>
+    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>158000</v>
+      </c>
+      <c r="E17" s="3">
         <v>171300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>174200</v>
       </c>
-      <c r="F17" s="3">
-        <v>208800</v>
-      </c>
       <c r="G17" s="3">
+        <v>196100</v>
+      </c>
+      <c r="H17" s="3">
         <v>264100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>273800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>210000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>231100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>208600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>198700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>171500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>158600</v>
-      </c>
-      <c r="O17" s="3">
-        <v>130400</v>
       </c>
       <c r="P17" s="3">
         <v>130400</v>
       </c>
       <c r="Q17" s="3">
+        <v>130400</v>
+      </c>
+      <c r="R17" s="3">
         <v>87100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>77700</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>69000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>200</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>300</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1600</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>600</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>100</v>
       </c>
-      <c r="Y17" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-62800</v>
+        <v>-58300</v>
       </c>
       <c r="E18" s="3">
-        <v>-67200</v>
+        <v>-62700</v>
       </c>
       <c r="F18" s="3">
-        <v>-93000</v>
+        <v>-67100</v>
       </c>
       <c r="G18" s="3">
+        <v>-80300</v>
+      </c>
+      <c r="H18" s="3">
         <v>-153800</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-123300</v>
       </c>
-      <c r="I18" s="3">
-        <v>-80000</v>
-      </c>
       <c r="J18" s="3">
+        <v>-79900</v>
+      </c>
+      <c r="K18" s="3">
         <v>-78300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-83300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-90400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-89900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-79300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-65400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-74300</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-46600</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-35300</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-32600</v>
       </c>
-      <c r="T18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1446,14 +1476,17 @@
       <c r="W18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X18" s="3">
+      <c r="X18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y18" s="3">
         <v>-100</v>
       </c>
-      <c r="Y18" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1479,62 +1512,63 @@
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
-    </row>
-    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z19" s="3"/>
+    </row>
+    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>2100</v>
+        <v>200</v>
       </c>
       <c r="E20" s="3">
-        <v>2400</v>
+        <v>0</v>
       </c>
       <c r="F20" s="3">
-        <v>4600</v>
+        <v>900</v>
       </c>
       <c r="G20" s="3">
-        <v>-1000</v>
+        <v>-1200</v>
       </c>
       <c r="H20" s="3">
-        <v>1900</v>
+        <v>2800</v>
       </c>
       <c r="I20" s="3">
-        <v>3100</v>
+        <v>-100</v>
       </c>
       <c r="J20" s="3">
+        <v>-600</v>
+      </c>
+      <c r="K20" s="3">
         <v>3200</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>1000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>200</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-300</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>16400</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-4400</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-10600</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>130400</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-54600</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-7400</v>
       </c>
-      <c r="T20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1544,68 +1578,71 @@
       <c r="W20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X20" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y20" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="X20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-53200</v>
+        <v>-51200</v>
       </c>
       <c r="E21" s="3">
-        <v>-57300</v>
+        <v>-55300</v>
       </c>
       <c r="F21" s="3">
-        <v>-81000</v>
+        <v>-60500</v>
       </c>
       <c r="G21" s="3">
-        <v>-147600</v>
+        <v>-71800</v>
       </c>
       <c r="H21" s="3">
-        <v>-114500</v>
+        <v>-149400</v>
       </c>
       <c r="I21" s="3">
-        <v>-69800</v>
+        <v>-116300</v>
       </c>
       <c r="J21" s="3">
+        <v>-72300</v>
+      </c>
+      <c r="K21" s="3">
         <v>-68700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-76200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-83900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-84000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-56600</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-65200</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-82000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>86600</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-87300</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-37200</v>
       </c>
-      <c r="T21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1621,13 +1658,16 @@
       <c r="Y21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>6600</v>
+        <v>9300</v>
       </c>
       <c r="E22" s="3">
         <v>6600</v>
@@ -1636,29 +1676,29 @@
         <v>6600</v>
       </c>
       <c r="G22" s="3">
+        <v>6600</v>
+      </c>
+      <c r="H22" s="3">
         <v>3800</v>
-      </c>
-      <c r="H22" s="3">
-        <v>2900</v>
       </c>
       <c r="I22" s="3">
         <v>2900</v>
       </c>
       <c r="J22" s="3">
+        <v>2900</v>
+      </c>
+      <c r="K22" s="3">
         <v>3000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>2600</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>2900</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>900</v>
       </c>
-      <c r="N22" s="3">
-        <v>0</v>
-      </c>
       <c r="O22" s="3">
         <v>0</v>
       </c>
@@ -1666,16 +1706,16 @@
         <v>0</v>
       </c>
       <c r="Q22" s="3">
+        <v>0</v>
+      </c>
+      <c r="R22" s="3">
         <v>1500</v>
-      </c>
-      <c r="R22" s="3">
-        <v>800</v>
       </c>
       <c r="S22" s="3">
         <v>800</v>
       </c>
-      <c r="T22" s="3" t="s">
-        <v>3</v>
+      <c r="T22" s="3">
+        <v>800</v>
       </c>
       <c r="U22" s="3" t="s">
         <v>3</v>
@@ -1686,156 +1726,165 @@
       <c r="W22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X22" s="3">
-        <v>0</v>
+      <c r="X22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-76100</v>
+      </c>
+      <c r="E23" s="3">
         <v>-67200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-71400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-94900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-158500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-124400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-79800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-78100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-84900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-93100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-91100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-62900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-69800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-84900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>82300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-90800</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-40800</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-100</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>700</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-400</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>400</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-100</v>
       </c>
-      <c r="Y23" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E24" s="3">
         <v>1600</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>400</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-200</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-300</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>900</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-400</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>500</v>
-      </c>
-      <c r="K24" s="3">
-        <v>-400</v>
       </c>
       <c r="L24" s="3">
         <v>-400</v>
       </c>
       <c r="M24" s="3">
+        <v>-400</v>
+      </c>
+      <c r="N24" s="3">
         <v>-1900</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-2700</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-300</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>100</v>
       </c>
-      <c r="Q24" s="3">
-        <v>0</v>
-      </c>
       <c r="R24" s="3">
         <v>0</v>
       </c>
       <c r="S24" s="3">
+        <v>0</v>
+      </c>
+      <c r="T24" s="3">
         <v>100</v>
       </c>
-      <c r="T24" s="3">
-        <v>0</v>
-      </c>
       <c r="U24" s="3">
+        <v>0</v>
+      </c>
+      <c r="V24" s="3">
         <v>200</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>300</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>200</v>
       </c>
-      <c r="X24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1905,150 +1954,159 @@
       <c r="Y25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-77600</v>
+      </c>
+      <c r="E26" s="3">
         <v>-68900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-71800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-94700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-158200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-125300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-79400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-78700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-84500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-92700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-89300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-60100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-69400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-84900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>82300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-90700</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-40900</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-100</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>500</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-600</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>200</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-100</v>
       </c>
-      <c r="Y26" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-77600</v>
+      </c>
+      <c r="E27" s="3">
         <v>-68900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-71800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-94700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-158200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-125300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-79400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-78700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-84500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-92700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-89300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-60100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-69400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-84900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-84500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-103600</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-46600</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>500</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-600</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>200</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-100</v>
       </c>
-      <c r="Y27" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2118,8 +2176,11 @@
       <c r="Y28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2189,8 +2250,11 @@
       <c r="Y29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2260,8 +2324,11 @@
       <c r="Y30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2331,62 +2398,65 @@
       <c r="Y31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-2100</v>
+        <v>-200</v>
       </c>
       <c r="E32" s="3">
-        <v>-2400</v>
+        <v>0</v>
       </c>
       <c r="F32" s="3">
-        <v>-4600</v>
+        <v>-900</v>
       </c>
       <c r="G32" s="3">
-        <v>1000</v>
+        <v>1200</v>
       </c>
       <c r="H32" s="3">
-        <v>-1900</v>
+        <v>-2800</v>
       </c>
       <c r="I32" s="3">
-        <v>-3100</v>
+        <v>100</v>
       </c>
       <c r="J32" s="3">
+        <v>600</v>
+      </c>
+      <c r="K32" s="3">
         <v>-3200</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-1000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-200</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>300</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-16400</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>4400</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>10600</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-130400</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>54600</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>7400</v>
       </c>
-      <c r="T32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2396,85 +2466,91 @@
       <c r="W32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X32" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y32" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="X32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-77600</v>
+      </c>
+      <c r="E33" s="3">
         <v>-68900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-71800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-94700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-158200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-125300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-79400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-78700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-84500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-92700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-89300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-60100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-69400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-84900</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-84500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-103600</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-46600</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>500</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-600</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>200</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-100</v>
       </c>
-      <c r="Y33" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2544,155 +2620,164 @@
       <c r="Y34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-77600</v>
+      </c>
+      <c r="E35" s="3">
         <v>-68900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-71800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-94700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-158200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-125300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-79400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-78700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-84500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-92700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-89300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-60100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-69400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-84900</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-84500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-103600</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-46600</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>500</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-600</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>200</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-100</v>
       </c>
-      <c r="Y35" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45596</v>
+      </c>
+      <c r="E38" s="2">
         <v>45504</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45412</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45322</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45230</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45138</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45046</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44957</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44865</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44773</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44681</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44592</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44500</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44408</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44316</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44227</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44135</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44012</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43921</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43830</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43738</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43646</v>
       </c>
-      <c r="Y38" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2718,8 +2803,9 @@
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
-    </row>
-    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z39" s="3"/>
+    </row>
+    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2745,87 +2831,91 @@
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
-    </row>
-    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z40" s="3"/>
+    </row>
+    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>219400</v>
+      </c>
+      <c r="E41" s="3">
         <v>243300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>261900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>327400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>367000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>233500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>283300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>264200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>188300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>187700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>540600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>315200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>365500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>618100</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>609800</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>145500</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>168700</v>
       </c>
-      <c r="T41" s="3">
-        <v>0</v>
-      </c>
       <c r="U41" s="3">
+        <v>0</v>
+      </c>
+      <c r="V41" s="3">
         <v>200</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>400</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>800</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>100</v>
       </c>
-      <c r="Y41" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E42" s="3" t="s">
-        <v>3</v>
+      <c r="D42" s="3">
+        <v>0</v>
+      </c>
+      <c r="E42" s="3">
+        <v>0</v>
       </c>
       <c r="F42" s="3">
         <v>0</v>
@@ -2840,17 +2930,17 @@
         <v>0</v>
       </c>
       <c r="J42" s="3">
+        <v>0</v>
+      </c>
+      <c r="K42" s="3">
         <v>105000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>208900</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>283900</v>
       </c>
-      <c r="M42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2866,8 +2956,8 @@
       <c r="R42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S42" s="3">
-        <v>0</v>
+      <c r="S42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T42" s="3">
         <v>0</v>
@@ -2887,62 +2977,65 @@
       <c r="Y42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>111900</v>
+      </c>
+      <c r="E43" s="3">
         <v>111500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>117800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>124000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>151800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>202100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>165100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>164900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>123000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>109900</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>79900</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>75900</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>66100</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>42700</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>34900</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>35100</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>28300</v>
       </c>
-      <c r="T43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2952,68 +3045,71 @@
       <c r="W43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X43" s="3">
-        <v>0</v>
+      <c r="X43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>222000</v>
+      </c>
+      <c r="E44" s="3">
         <v>228500</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>223600</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>198600</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>199100</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>143600</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>115200</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>68700</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>62400</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>53400</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>45300</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>35900</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>29900</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>27900</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>28900</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>33600</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>30700</v>
       </c>
-      <c r="T44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U44" s="3" t="s">
         <v>3</v>
       </c>
@@ -3023,179 +3119,188 @@
       <c r="W44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X44" s="3">
-        <v>0</v>
+      <c r="X44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
-        <v>69600</v>
+      <c r="D45" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E45" s="3">
-        <v>95100</v>
+        <v>22300</v>
       </c>
       <c r="F45" s="3">
-        <v>92600</v>
+        <v>18700</v>
       </c>
       <c r="G45" s="3">
-        <v>106500</v>
+        <v>3000</v>
       </c>
       <c r="H45" s="3">
-        <v>113100</v>
+        <v>25500</v>
       </c>
       <c r="I45" s="3">
-        <v>118500</v>
+        <v>24700</v>
       </c>
       <c r="J45" s="3">
+        <v>23600</v>
+      </c>
+      <c r="K45" s="3">
         <v>101400</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>59000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>45300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>46500</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>37000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>33100</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>22500</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>20300</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>12500</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>15200</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>200</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>300</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>400</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>300</v>
       </c>
-      <c r="X45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>620100</v>
+      </c>
+      <c r="E46" s="3">
         <v>652900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>698300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>742700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>824400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>692200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>682200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>704200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>641600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>680200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>712200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>464100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>494600</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>711300</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>693900</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>226600</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>242900</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>300</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>500</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>800</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>1100</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>100</v>
       </c>
-      <c r="Y46" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>0</v>
-      </c>
-      <c r="E47" s="3">
-        <v>0</v>
-      </c>
-      <c r="F47" s="3">
-        <v>0</v>
-      </c>
-      <c r="G47" s="3">
-        <v>0</v>
-      </c>
-      <c r="H47" s="3">
-        <v>0</v>
-      </c>
-      <c r="I47" s="3">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3">
-        <v>0</v>
+      <c r="D47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -3225,79 +3330,82 @@
         <v>0</v>
       </c>
       <c r="T47" s="3">
+        <v>0</v>
+      </c>
+      <c r="U47" s="3">
         <v>317400</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>317300</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>316400</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>315100</v>
       </c>
-      <c r="X47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>52700</v>
+      </c>
+      <c r="E48" s="3">
         <v>54900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>55600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>57800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>60300</v>
-      </c>
-      <c r="H48" s="3">
-        <v>62900</v>
       </c>
       <c r="I48" s="3">
         <v>62900</v>
       </c>
       <c r="J48" s="3">
+        <v>62900</v>
+      </c>
+      <c r="K48" s="3">
         <v>62300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>60600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>59300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>59200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>60100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>58300</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>53100</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>53000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>51800</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>50800</v>
       </c>
-      <c r="T48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3307,55 +3415,58 @@
       <c r="W48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X48" s="3">
-        <v>0</v>
+      <c r="X48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>286000</v>
+      </c>
+      <c r="E49" s="3">
         <v>288200</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>289300</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>294300</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>294200</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>304500</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>307500</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>306400</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>291400</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>300100</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>309600</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>325700</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>343200</v>
-      </c>
-      <c r="P49" s="3">
-        <v>1200</v>
       </c>
       <c r="Q49" s="3">
         <v>1200</v>
@@ -3366,8 +3477,8 @@
       <c r="S49" s="3">
         <v>1200</v>
       </c>
-      <c r="T49" s="3" t="s">
-        <v>3</v>
+      <c r="T49" s="3">
+        <v>1200</v>
       </c>
       <c r="U49" s="3" t="s">
         <v>3</v>
@@ -3378,14 +3489,17 @@
       <c r="W49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X49" s="3">
-        <v>0</v>
+      <c r="X49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3455,8 +3569,11 @@
       <c r="Y50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3526,79 +3643,85 @@
       <c r="Y51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>7600</v>
+      </c>
+      <c r="E52" s="3">
         <v>7700</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>8000</v>
       </c>
-      <c r="F52" s="3">
-        <v>8600</v>
-      </c>
       <c r="G52" s="3">
-        <v>8700</v>
+        <v>2600</v>
       </c>
       <c r="H52" s="3">
         <v>8700</v>
       </c>
       <c r="I52" s="3">
+        <v>8700</v>
+      </c>
+      <c r="J52" s="3">
         <v>7300</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>7100</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>7000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>6500</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>6300</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>6000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>5300</v>
-      </c>
-      <c r="P52" s="3">
-        <v>5000</v>
       </c>
       <c r="Q52" s="3">
         <v>5000</v>
       </c>
       <c r="R52" s="3">
+        <v>5000</v>
+      </c>
+      <c r="S52" s="3">
         <v>10500</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>4300</v>
       </c>
-      <c r="T52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V52" s="3">
+      <c r="V52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W52" s="3">
         <v>316400</v>
       </c>
-      <c r="W52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X52" s="3">
+      <c r="X52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y52" s="3">
         <v>300</v>
       </c>
-      <c r="Y52" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3668,79 +3791,85 @@
       <c r="Y53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>966300</v>
+      </c>
+      <c r="E54" s="3">
         <v>1003800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1051200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1103400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1187700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1068400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1059800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1080000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1000600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1046000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1087300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>855900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>901500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>770600</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>753100</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>290100</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>299300</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>317700</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>317800</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>317200</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>316200</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>400</v>
       </c>
-      <c r="Y54" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3766,8 +3895,9 @@
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
-    </row>
-    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z55" s="3"/>
+    </row>
+    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3793,79 +3923,83 @@
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
-    </row>
-    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z56" s="3"/>
+    </row>
+    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>74100</v>
+      </c>
+      <c r="E57" s="3">
         <v>71400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>84100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>71100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>101700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>99000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>62000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>62100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>44500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>45100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>35400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>27600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>32100</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>28400</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>18100</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>19800</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>16700</v>
-      </c>
-      <c r="T57" s="3">
-        <v>100</v>
       </c>
       <c r="U57" s="3">
         <v>100</v>
       </c>
       <c r="V57" s="3">
+        <v>100</v>
+      </c>
+      <c r="W57" s="3">
         <v>200</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>100</v>
       </c>
-      <c r="X57" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y57" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Y57" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3876,19 +4010,19 @@
         <v>0</v>
       </c>
       <c r="F58" s="3">
-        <v>0</v>
+        <v>4500</v>
       </c>
       <c r="G58" s="3">
-        <v>0</v>
+        <v>4500</v>
       </c>
       <c r="H58" s="3">
-        <v>0</v>
+        <v>4400</v>
       </c>
       <c r="I58" s="3">
-        <v>0</v>
+        <v>4300</v>
       </c>
       <c r="J58" s="3">
-        <v>0</v>
+        <v>4300</v>
       </c>
       <c r="K58" s="3">
         <v>0</v>
@@ -3912,209 +4046,218 @@
         <v>0</v>
       </c>
       <c r="R58" s="3">
+        <v>0</v>
+      </c>
+      <c r="S58" s="3">
         <v>10200</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>5800</v>
       </c>
-      <c r="T58" s="3">
-        <v>0</v>
-      </c>
       <c r="U58" s="3">
         <v>0</v>
       </c>
       <c r="V58" s="3">
         <v>0</v>
       </c>
-      <c r="W58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X58" s="3">
+      <c r="W58" s="3">
+        <v>0</v>
+      </c>
+      <c r="X58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y58" s="3">
         <v>100</v>
       </c>
-      <c r="Y58" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>249500</v>
+        <v>102800</v>
       </c>
       <c r="E59" s="3">
-        <v>243700</v>
+        <v>199400</v>
       </c>
       <c r="F59" s="3">
-        <v>259100</v>
+        <v>185100</v>
       </c>
       <c r="G59" s="3">
-        <v>251000</v>
+        <v>187200</v>
       </c>
       <c r="H59" s="3">
-        <v>241500</v>
+        <v>176100</v>
       </c>
       <c r="I59" s="3">
-        <v>226400</v>
+        <v>156600</v>
       </c>
       <c r="J59" s="3">
+        <v>144300</v>
+      </c>
+      <c r="K59" s="3">
         <v>222300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>193800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>193600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>177500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>161500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>135400</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>99700</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>86800</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>88100</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>76700</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>900</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>800</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>600</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>400</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>300</v>
       </c>
-      <c r="Y59" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>320000</v>
+      </c>
+      <c r="E60" s="3">
         <v>321000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>327800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>330200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>352600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>340500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>288400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>284300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>238400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>238800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>212800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>189000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>167400</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>128200</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>104900</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>118100</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>99300</v>
-      </c>
-      <c r="T60" s="3">
-        <v>1000</v>
       </c>
       <c r="U60" s="3">
         <v>1000</v>
       </c>
       <c r="V60" s="3">
+        <v>1000</v>
+      </c>
+      <c r="W60" s="3">
         <v>800</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>500</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>400</v>
       </c>
-      <c r="Y60" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>285700</v>
+        <v>315400</v>
       </c>
       <c r="E61" s="3">
-        <v>284700</v>
+        <v>302800</v>
       </c>
       <c r="F61" s="3">
-        <v>283700</v>
+        <v>301000</v>
       </c>
       <c r="G61" s="3">
-        <v>282700</v>
+        <v>301100</v>
       </c>
       <c r="H61" s="3">
-        <v>295500</v>
+        <v>301200</v>
       </c>
       <c r="I61" s="3">
-        <v>295200</v>
+        <v>315100</v>
       </c>
       <c r="J61" s="3">
+        <v>315900</v>
+      </c>
+      <c r="K61" s="3">
         <v>294900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>294600</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>294300</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>294100</v>
       </c>
-      <c r="N61" s="3">
-        <v>0</v>
-      </c>
       <c r="O61" s="3">
         <v>0</v>
       </c>
@@ -4125,14 +4268,14 @@
         <v>0</v>
       </c>
       <c r="R61" s="3">
+        <v>0</v>
+      </c>
+      <c r="S61" s="3">
         <v>24700</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>28900</v>
       </c>
-      <c r="T61" s="3">
-        <v>0</v>
-      </c>
       <c r="U61" s="3">
         <v>0</v>
       </c>
@@ -4148,79 +4291,85 @@
       <c r="Y61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>166200</v>
+        <v>5500</v>
       </c>
       <c r="E62" s="3">
-        <v>160800</v>
+        <v>1500</v>
       </c>
       <c r="F62" s="3">
-        <v>161800</v>
+        <v>1600</v>
       </c>
       <c r="G62" s="3">
-        <v>159700</v>
+        <v>1800</v>
       </c>
       <c r="H62" s="3">
-        <v>157100</v>
+        <v>1600</v>
       </c>
       <c r="I62" s="3">
-        <v>148700</v>
+        <v>1600</v>
       </c>
       <c r="J62" s="3">
+        <v>1300</v>
+      </c>
+      <c r="K62" s="3">
         <v>145700</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>129000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>121200</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>115300</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>119800</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>148600</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>107400</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>163800</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>148200</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>86300</v>
-      </c>
-      <c r="T62" s="3">
-        <v>10900</v>
       </c>
       <c r="U62" s="3">
         <v>10900</v>
       </c>
       <c r="V62" s="3">
+        <v>10900</v>
+      </c>
+      <c r="W62" s="3">
         <v>20500</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>10900</v>
       </c>
-      <c r="X62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4290,8 +4439,11 @@
       <c r="Y63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4361,8 +4513,11 @@
       <c r="Y64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4432,79 +4587,85 @@
       <c r="Y65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>785400</v>
+      </c>
+      <c r="E66" s="3">
         <v>772900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>773300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>775700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>795100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>793200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>732300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>725000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>662000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>654300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>622200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>308900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>316100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>235600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>268700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>290900</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>214500</v>
-      </c>
-      <c r="T66" s="3">
-        <v>11900</v>
       </c>
       <c r="U66" s="3">
         <v>11900</v>
       </c>
       <c r="V66" s="3">
+        <v>11900</v>
+      </c>
+      <c r="W66" s="3">
         <v>21300</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>11400</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>400</v>
       </c>
-      <c r="Y66" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4530,8 +4691,9 @@
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
-    </row>
-    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z67" s="3"/>
+    </row>
+    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4601,8 +4763,11 @@
       <c r="Y68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4672,8 +4837,11 @@
       <c r="Y69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4720,14 +4888,14 @@
         <v>0</v>
       </c>
       <c r="R70" s="3">
+        <v>0</v>
+      </c>
+      <c r="S70" s="3">
         <v>615700</v>
       </c>
-      <c r="S70" s="3">
+      <c r="T70" s="3">
         <v>615800</v>
       </c>
-      <c r="T70" s="3">
-        <v>0</v>
-      </c>
       <c r="U70" s="3">
         <v>0</v>
       </c>
@@ -4743,8 +4911,11 @@
       <c r="Y70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4814,79 +4985,85 @@
       <c r="Y71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-1832600</v>
+      </c>
+      <c r="E72" s="3">
         <v>-1755000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-1686200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-1614400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-1519600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-1361400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-1236200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-1156800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-1078100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-993600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-900900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-811700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-751500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-682100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-597100</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>200</v>
       </c>
-      <c r="S72" s="3">
-        <v>0</v>
-      </c>
       <c r="T72" s="3">
+        <v>0</v>
+      </c>
+      <c r="U72" s="3">
         <v>1100</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>1200</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>300</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>100</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-100</v>
       </c>
-      <c r="Y72" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4956,8 +5133,11 @@
       <c r="Y73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5027,8 +5207,11 @@
       <c r="Y74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5098,79 +5281,85 @@
       <c r="Y75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>181000</v>
+      </c>
+      <c r="E76" s="3">
         <v>230900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>277900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>327700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>392600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>275200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>327500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>355000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>338600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>391700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>465100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>547000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>585400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>535000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>484300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>-616500</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>-531000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>305800</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>305900</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>295900</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>304800</v>
       </c>
-      <c r="X76" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y76" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Y76" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5240,155 +5429,164 @@
       <c r="Y77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45596</v>
+      </c>
+      <c r="E80" s="2">
         <v>45504</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45412</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45322</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45230</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45138</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45046</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44957</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44865</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44773</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44681</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44592</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44500</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44408</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44316</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44227</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44135</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44012</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43921</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43830</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43738</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43646</v>
       </c>
-      <c r="Y80" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-77600</v>
+      </c>
+      <c r="E81" s="3">
         <v>-68900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-71800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-94700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-158200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-125300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-79400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-78700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-84500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-92700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-89300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-60100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-69400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-84900</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-84500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-103600</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-46600</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>500</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-600</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>200</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-100</v>
       </c>
-      <c r="Y81" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5414,62 +5612,63 @@
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
-    </row>
-    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z82" s="3"/>
+    </row>
+    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>7500</v>
+        <v>4100</v>
       </c>
       <c r="E83" s="3">
-        <v>7400</v>
+        <v>3900</v>
       </c>
       <c r="F83" s="3">
-        <v>7300</v>
+        <v>4000</v>
       </c>
       <c r="G83" s="3">
-        <v>7100</v>
+        <v>3500</v>
       </c>
       <c r="H83" s="3">
-        <v>7000</v>
+        <v>3200</v>
       </c>
       <c r="I83" s="3">
-        <v>7100</v>
+        <v>3300</v>
       </c>
       <c r="J83" s="3">
+        <v>3400</v>
+      </c>
+      <c r="K83" s="3">
         <v>6500</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>6100</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>6300</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>6200</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>6300</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>4600</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>2800</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>2700</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>2600</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>2800</v>
       </c>
-      <c r="T83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U83" s="3" t="s">
         <v>3</v>
       </c>
@@ -5479,14 +5678,17 @@
       <c r="W83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X83" s="3">
-        <v>0</v>
+      <c r="X83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5556,8 +5758,11 @@
       <c r="Y84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5627,8 +5832,11 @@
       <c r="Y85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5698,8 +5906,11 @@
       <c r="Y86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5769,8 +5980,11 @@
       <c r="Y87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5840,79 +6054,85 @@
       <c r="Y88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-30600</v>
+      </c>
+      <c r="E89" s="3">
         <v>-51200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-62500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-41500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-96900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-86400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-104200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-50400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-83000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-62900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-70800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-48100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-47900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-23700</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-37500</v>
-      </c>
-      <c r="R89" s="3">
-        <v>-20900</v>
       </c>
       <c r="S89" s="3">
         <v>-20900</v>
       </c>
       <c r="T89" s="3">
+        <v>-20900</v>
+      </c>
+      <c r="U89" s="3">
         <v>-100</v>
-      </c>
-      <c r="U89" s="3">
-        <v>-300</v>
       </c>
       <c r="V89" s="3">
         <v>-300</v>
       </c>
       <c r="W89" s="3">
+        <v>-300</v>
+      </c>
+      <c r="X89" s="3">
         <v>-700</v>
       </c>
-      <c r="X89" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y89" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Y89" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5938,62 +6158,63 @@
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
-    </row>
-    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z90" s="3"/>
+    </row>
+    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="E91" s="3">
         <v>-3800</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-3500</v>
-      </c>
-      <c r="F91" s="3">
-        <v>-4800</v>
       </c>
       <c r="G91" s="3">
         <v>-4800</v>
       </c>
       <c r="H91" s="3">
+        <v>-4800</v>
+      </c>
+      <c r="I91" s="3">
         <v>-4000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-5800</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-4400</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-5300</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-5700</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-3200</v>
-      </c>
-      <c r="N91" s="3">
-        <v>-4300</v>
       </c>
       <c r="O91" s="3">
         <v>-4300</v>
       </c>
       <c r="P91" s="3">
+        <v>-4300</v>
+      </c>
+      <c r="Q91" s="3">
         <v>-3700</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-4100</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-2600</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-3000</v>
       </c>
-      <c r="T91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U91" s="3" t="s">
         <v>3</v>
       </c>
@@ -6003,14 +6224,17 @@
       <c r="W91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X91" s="3">
-        <v>0</v>
+      <c r="X91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6080,8 +6304,11 @@
       <c r="Y92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6151,70 +6378,73 @@
       <c r="Y93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="E94" s="3">
         <v>-3800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-3500</v>
-      </c>
-      <c r="F94" s="3">
-        <v>-4800</v>
       </c>
       <c r="G94" s="3">
         <v>-4800</v>
       </c>
       <c r="H94" s="3">
+        <v>-4800</v>
+      </c>
+      <c r="I94" s="3">
         <v>-4000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>99200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>100600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>69700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-290500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-5900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-4300</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-209600</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-3700</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-4100</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-2600</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-3000</v>
       </c>
-      <c r="T94" s="3">
-        <v>0</v>
-      </c>
       <c r="U94" s="3">
+        <v>0</v>
+      </c>
+      <c r="V94" s="3">
         <v>100</v>
       </c>
-      <c r="V94" s="3">
-        <v>0</v>
-      </c>
-      <c r="W94" s="3" t="s">
-        <v>3</v>
+      <c r="W94" s="3">
+        <v>0</v>
       </c>
       <c r="X94" s="3" t="s">
         <v>3</v>
@@ -6222,8 +6452,11 @@
       <c r="Y94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6249,31 +6482,32 @@
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
-    </row>
-    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z95" s="3"/>
+    </row>
+    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -6320,8 +6554,11 @@
       <c r="Y96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6391,8 +6628,11 @@
       <c r="Y97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6462,8 +6702,11 @@
       <c r="Y98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6533,132 +6776,138 @@
       <c r="Y99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>9500</v>
+      </c>
+      <c r="E100" s="3">
         <v>5900</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>1000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>5800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>236700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>40300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>23800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>54900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>14400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>303100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>2500</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>5600</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>35600</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>506000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>200</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>3400</v>
       </c>
-      <c r="T100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V100" s="3">
+      <c r="V100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W100" s="3">
         <v>-100</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>315500</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>100</v>
       </c>
-      <c r="Y100" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="E101" s="3">
+        <v>300</v>
+      </c>
+      <c r="F101" s="3">
         <v>500</v>
       </c>
-      <c r="E101" s="3">
-        <v>-600</v>
-      </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>800</v>
       </c>
-      <c r="G101" s="3">
-        <v>-1500</v>
-      </c>
       <c r="H101" s="3">
-        <v>300</v>
+        <v>-500</v>
       </c>
       <c r="I101" s="3">
-        <v>500</v>
+        <v>-100</v>
       </c>
       <c r="J101" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="K101" s="3">
         <v>800</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-500</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-100</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-1000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-300</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-700</v>
       </c>
-      <c r="P101" s="3">
-        <v>0</v>
-      </c>
       <c r="Q101" s="3">
         <v>0</v>
       </c>
       <c r="R101" s="3">
+        <v>0</v>
+      </c>
+      <c r="S101" s="3">
         <v>100</v>
       </c>
-      <c r="S101" s="3">
-        <v>0</v>
-      </c>
-      <c r="T101" s="3" t="s">
-        <v>3</v>
+      <c r="T101" s="3">
+        <v>0</v>
       </c>
       <c r="U101" s="3" t="s">
         <v>3</v>
@@ -6669,81 +6918,87 @@
       <c r="W101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X101" s="3">
-        <v>0</v>
+      <c r="X101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-23900</v>
+      </c>
+      <c r="E102" s="3">
         <v>-48600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-65600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-39600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>133500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-49800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>19200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>105900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-352900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>225300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-50300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-252600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>8300</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>464300</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-23200</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-20400</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-100</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-200</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-400</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>800</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>100</v>
       </c>
-      <c r="Y102" s="3" t="s">
+      <c r="Z102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/CHPT_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CHPT_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="92">
   <si>
     <t>CHPT</t>
   </si>
@@ -656,175 +656,179 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Z102"/>
+  <dimension ref="A5:AA102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45688</v>
+      </c>
+      <c r="E7" s="2">
         <v>45596</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45504</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45412</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45322</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45230</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45138</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45046</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44957</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44865</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44773</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44681</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44592</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44500</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44408</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44316</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44227</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44135</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44012</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43921</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43830</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43738</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43646</v>
       </c>
-      <c r="Z7" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>101900</v>
+      </c>
+      <c r="E8" s="3">
         <v>99600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>108500</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>107000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>115800</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>110300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>150500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>130000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>152800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>125300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>108300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>81600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>79300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>65000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>56100</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>40500</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>42400</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>36400</v>
       </c>
-      <c r="U8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V8" s="3" t="s">
         <v>3</v>
       </c>
@@ -834,71 +838,74 @@
       <c r="X8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y8" s="3">
-        <v>0</v>
+      <c r="Y8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Z8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>73200</v>
+      </c>
+      <c r="E9" s="3">
         <v>75900</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>83000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>83400</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>92800</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>134200</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>149400</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>99500</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>119800</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>102700</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>90100</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>69500</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>61900</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>49000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>45300</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>31300</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>33500</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>29100</v>
       </c>
-      <c r="U9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V9" s="3" t="s">
         <v>3</v>
       </c>
@@ -914,65 +921,68 @@
       <c r="Z9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>28700</v>
+      </c>
+      <c r="E10" s="3">
         <v>23700</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>25600</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>23600</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>23000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>-23900</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>30500</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>33000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>22600</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>18200</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>12100</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>17400</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>16000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>10800</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>9200</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>8900</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>7300</v>
       </c>
-      <c r="U10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V10" s="3" t="s">
         <v>3</v>
       </c>
@@ -988,8 +998,11 @@
       <c r="Z10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1016,65 +1029,66 @@
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
-    </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA11" s="3"/>
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>30400</v>
+      </c>
+      <c r="E12" s="3">
         <v>35400</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>36500</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>36100</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>47700</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>56500</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>59600</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>49400</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>46700</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>48100</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>51800</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>48300</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>42500</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>36800</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>40400</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>25400</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>20900</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>18900</v>
       </c>
-      <c r="U12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1090,8 +1104,11 @@
       <c r="Z12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1164,26 +1181,29 @@
       <c r="Z13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E14" s="3">
         <v>9800</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="F14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G14" s="3">
+      <c r="G14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H14" s="3">
         <v>12700</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1202,15 +1222,15 @@
       <c r="N14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O14" s="3">
+      <c r="O14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P14" s="3">
         <v>200</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>4800</v>
       </c>
-      <c r="Q14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1223,8 +1243,8 @@
       <c r="U14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V14" s="3">
-        <v>0</v>
+      <c r="V14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W14" s="3">
         <v>0</v>
@@ -1238,35 +1258,38 @@
       <c r="Z14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>7000</v>
+      </c>
+      <c r="E15" s="3">
         <v>7300</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>7500</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>7400</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>7300</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>7100</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>7000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>7100</v>
       </c>
-      <c r="K15" s="3">
-        <v>0</v>
-      </c>
       <c r="L15" s="3">
         <v>0</v>
       </c>
@@ -1312,8 +1335,11 @@
       <c r="Z15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1337,139 +1363,143 @@
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
-    </row>
-    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA16" s="3"/>
+    </row>
+    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>156800</v>
+      </c>
+      <c r="E17" s="3">
         <v>158000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>171300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>174200</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>196100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>264100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>273800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>210000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>231100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>208600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>198700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>171500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>158600</v>
-      </c>
-      <c r="P17" s="3">
-        <v>130400</v>
       </c>
       <c r="Q17" s="3">
         <v>130400</v>
       </c>
       <c r="R17" s="3">
+        <v>130400</v>
+      </c>
+      <c r="S17" s="3">
         <v>87100</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>77700</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>69000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>200</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>300</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1600</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>600</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>100</v>
       </c>
-      <c r="Z17" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-54900</v>
+      </c>
+      <c r="E18" s="3">
         <v>-58300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-62700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-67100</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-80300</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-153800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-123300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-79900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-78300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-83300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-90400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-89900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-79300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-65400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-74300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-46600</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-35300</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-32600</v>
       </c>
-      <c r="U18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1479,14 +1509,17 @@
       <c r="X18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Y18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z18" s="3">
         <v>-100</v>
       </c>
-      <c r="Z18" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1513,65 +1546,66 @@
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
-    </row>
-    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA19" s="3"/>
+    </row>
+    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E20" s="3">
         <v>200</v>
       </c>
-      <c r="E20" s="3">
-        <v>0</v>
-      </c>
       <c r="F20" s="3">
+        <v>0</v>
+      </c>
+      <c r="G20" s="3">
         <v>900</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-1200</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>2800</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-100</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-600</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>3200</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>1000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>200</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-300</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>16400</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-4400</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-10600</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>130400</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-54600</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-7400</v>
       </c>
-      <c r="U20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1581,71 +1615,74 @@
       <c r="X20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y20" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z20" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="Y20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-50300</v>
+      </c>
+      <c r="E21" s="3">
         <v>-51200</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-55300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-60500</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-71800</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-149400</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-116300</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-72300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-68700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-76200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-83900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-84000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-56600</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-65200</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-82000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>86600</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-87300</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-37200</v>
       </c>
-      <c r="U21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1661,16 +1698,19 @@
       <c r="Z21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>8000</v>
+      </c>
+      <c r="E22" s="3">
         <v>9300</v>
-      </c>
-      <c r="E22" s="3">
-        <v>6600</v>
       </c>
       <c r="F22" s="3">
         <v>6600</v>
@@ -1679,29 +1719,29 @@
         <v>6600</v>
       </c>
       <c r="H22" s="3">
+        <v>6600</v>
+      </c>
+      <c r="I22" s="3">
         <v>3800</v>
-      </c>
-      <c r="I22" s="3">
-        <v>2900</v>
       </c>
       <c r="J22" s="3">
         <v>2900</v>
       </c>
       <c r="K22" s="3">
+        <v>2900</v>
+      </c>
+      <c r="L22" s="3">
         <v>3000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>2600</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>2900</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>900</v>
       </c>
-      <c r="O22" s="3">
-        <v>0</v>
-      </c>
       <c r="P22" s="3">
         <v>0</v>
       </c>
@@ -1709,16 +1749,16 @@
         <v>0</v>
       </c>
       <c r="R22" s="3">
+        <v>0</v>
+      </c>
+      <c r="S22" s="3">
         <v>1500</v>
-      </c>
-      <c r="S22" s="3">
-        <v>800</v>
       </c>
       <c r="T22" s="3">
         <v>800</v>
       </c>
-      <c r="U22" s="3" t="s">
-        <v>3</v>
+      <c r="U22" s="3">
+        <v>800</v>
       </c>
       <c r="V22" s="3" t="s">
         <v>3</v>
@@ -1729,162 +1769,171 @@
       <c r="X22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y22" s="3">
-        <v>0</v>
+      <c r="Y22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Z22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-63800</v>
+      </c>
+      <c r="E23" s="3">
         <v>-76100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-67200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-71400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-94900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-158500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-124400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-79800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-78100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-84900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-93100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-91100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-62900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-69800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-84900</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>82300</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-90800</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-40800</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-100</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>700</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-400</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>400</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-100</v>
       </c>
-      <c r="Z23" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>800</v>
+      </c>
+      <c r="E24" s="3">
         <v>1500</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>1600</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>400</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-200</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-300</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>900</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-400</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>500</v>
-      </c>
-      <c r="L24" s="3">
-        <v>-400</v>
       </c>
       <c r="M24" s="3">
         <v>-400</v>
       </c>
       <c r="N24" s="3">
+        <v>-400</v>
+      </c>
+      <c r="O24" s="3">
         <v>-1900</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-2700</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-300</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>100</v>
       </c>
-      <c r="R24" s="3">
-        <v>0</v>
-      </c>
       <c r="S24" s="3">
         <v>0</v>
       </c>
       <c r="T24" s="3">
+        <v>0</v>
+      </c>
+      <c r="U24" s="3">
         <v>100</v>
       </c>
-      <c r="U24" s="3">
-        <v>0</v>
-      </c>
       <c r="V24" s="3">
+        <v>0</v>
+      </c>
+      <c r="W24" s="3">
         <v>200</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>300</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>200</v>
       </c>
-      <c r="Y24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1957,156 +2006,165 @@
       <c r="Z25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-64600</v>
+      </c>
+      <c r="E26" s="3">
         <v>-77600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-68900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-71800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-94700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-158200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-125300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-79400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-78700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-84500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-92700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-89300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-60100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-69400</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-84900</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>82300</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-90700</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-40900</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-100</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>500</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-600</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>200</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-100</v>
       </c>
-      <c r="Z26" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-64600</v>
+      </c>
+      <c r="E27" s="3">
         <v>-77600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-68900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-71800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-94700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-158200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-125300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-79400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-78700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-84500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-92700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-89300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-60100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-69400</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-84900</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-84500</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-103600</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-46600</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-100</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>500</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-600</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>200</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-100</v>
       </c>
-      <c r="Z27" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2179,8 +2237,11 @@
       <c r="Z28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2253,8 +2314,11 @@
       <c r="Z29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2327,8 +2391,11 @@
       <c r="Z30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2401,65 +2468,68 @@
       <c r="Z31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="E32" s="3">
         <v>-200</v>
       </c>
-      <c r="E32" s="3">
-        <v>0</v>
-      </c>
       <c r="F32" s="3">
+        <v>0</v>
+      </c>
+      <c r="G32" s="3">
         <v>-900</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>1200</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-2800</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>100</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>600</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-3200</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-1000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-200</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>300</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-16400</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>4400</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>10600</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-130400</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>54600</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>7400</v>
       </c>
-      <c r="U32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2469,88 +2539,94 @@
       <c r="X32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y32" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z32" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="Y32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-64600</v>
+      </c>
+      <c r="E33" s="3">
         <v>-77600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-68900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-71800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-94700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-158200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-125300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-79400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-78700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-84500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-92700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-89300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-60100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-69400</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-84900</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-84500</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-103600</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-46600</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-100</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>500</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-600</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>200</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-100</v>
       </c>
-      <c r="Z33" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2623,161 +2699,170 @@
       <c r="Z34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-64600</v>
+      </c>
+      <c r="E35" s="3">
         <v>-77600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-68900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-71800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-94700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-158200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-125300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-79400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-78700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-84500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-92700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-89300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-60100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-69400</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-84900</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-84500</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-103600</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-46600</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-100</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>500</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-600</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>200</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-100</v>
       </c>
-      <c r="Z35" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45688</v>
+      </c>
+      <c r="E38" s="2">
         <v>45596</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45504</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45412</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45322</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45230</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45138</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45046</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44957</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44865</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44773</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44681</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44592</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44500</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44408</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44316</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44227</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44135</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44012</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43921</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43830</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43738</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43646</v>
       </c>
-      <c r="Z38" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2804,8 +2889,9 @@
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
-    </row>
-    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA39" s="3"/>
+    </row>
+    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2832,82 +2918,86 @@
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
-    </row>
-    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA40" s="3"/>
+    </row>
+    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>224600</v>
+      </c>
+      <c r="E41" s="3">
         <v>219400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>243300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>261900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>327400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>367000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>233500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>283300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>264200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>188300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>187700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>540600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>315200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>365500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>618100</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>609800</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>145500</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>168700</v>
       </c>
-      <c r="U41" s="3">
-        <v>0</v>
-      </c>
       <c r="V41" s="3">
+        <v>0</v>
+      </c>
+      <c r="W41" s="3">
         <v>200</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>400</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>800</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>100</v>
       </c>
-      <c r="Z41" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2933,17 +3023,17 @@
         <v>0</v>
       </c>
       <c r="K42" s="3">
+        <v>0</v>
+      </c>
+      <c r="L42" s="3">
         <v>105000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>208900</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>283900</v>
       </c>
-      <c r="N42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2959,8 +3049,8 @@
       <c r="S42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T42" s="3">
-        <v>0</v>
+      <c r="T42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U42" s="3">
         <v>0</v>
@@ -2980,65 +3070,68 @@
       <c r="Z42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>95900</v>
+      </c>
+      <c r="E43" s="3">
         <v>111900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>111500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>117800</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>124000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>151800</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>202100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>165100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>164900</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>123000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>109900</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>79900</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>75900</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>66100</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>42700</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>34900</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>35100</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>28300</v>
       </c>
-      <c r="U43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3048,71 +3141,74 @@
       <c r="X43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y43" s="3">
-        <v>0</v>
+      <c r="Y43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Z43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>209300</v>
+      </c>
+      <c r="E44" s="3">
         <v>222000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>228500</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>223600</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>198600</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>199100</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>143600</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>115200</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>68700</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>62400</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>53400</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>45300</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>35900</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>29900</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>27900</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>28900</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>33600</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>30700</v>
       </c>
-      <c r="U44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V44" s="3" t="s">
         <v>3</v>
       </c>
@@ -3122,14 +3218,17 @@
       <c r="X44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y44" s="3">
-        <v>0</v>
+      <c r="Y44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Z44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3137,147 +3236,153 @@
         <v>3</v>
       </c>
       <c r="E45" s="3">
+        <v>25400</v>
+      </c>
+      <c r="F45" s="3">
         <v>22300</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>18700</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>3000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>25500</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>24700</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>23600</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>101400</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>59000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>45300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>46500</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>37000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>33100</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>22500</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>20300</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>12500</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>15200</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>200</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>300</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>400</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>300</v>
       </c>
-      <c r="Y45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>566600</v>
+      </c>
+      <c r="E46" s="3">
         <v>620100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>652900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>698300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>742700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>824400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>692200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>682200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>704200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>641600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>680200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>712200</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>464100</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>494600</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>711300</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>693900</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>226600</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>242900</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>300</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>500</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>800</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>1100</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>100</v>
       </c>
-      <c r="Z46" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3302,8 +3407,8 @@
       <c r="J47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
+      <c r="K47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L47" s="3">
         <v>0</v>
@@ -3333,82 +3438,85 @@
         <v>0</v>
       </c>
       <c r="U47" s="3">
+        <v>0</v>
+      </c>
+      <c r="V47" s="3">
         <v>317400</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>317300</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>316400</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>315100</v>
       </c>
-      <c r="Y47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>50000</v>
+      </c>
+      <c r="E48" s="3">
         <v>52700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>54900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>55600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>57800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>60300</v>
-      </c>
-      <c r="I48" s="3">
-        <v>62900</v>
       </c>
       <c r="J48" s="3">
         <v>62900</v>
       </c>
       <c r="K48" s="3">
+        <v>62900</v>
+      </c>
+      <c r="L48" s="3">
         <v>62300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>60600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>59300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>59200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>60100</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>58300</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>53100</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>53000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>51800</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>50800</v>
       </c>
-      <c r="U48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3418,58 +3526,61 @@
       <c r="X48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y48" s="3">
-        <v>0</v>
+      <c r="Y48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Z48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>273700</v>
+      </c>
+      <c r="E49" s="3">
         <v>286000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>288200</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>289300</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>294300</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>294200</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>304500</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>307500</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>306400</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>291400</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>300100</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>309600</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>325700</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>343200</v>
-      </c>
-      <c r="Q49" s="3">
-        <v>1200</v>
       </c>
       <c r="R49" s="3">
         <v>1200</v>
@@ -3480,8 +3591,8 @@
       <c r="T49" s="3">
         <v>1200</v>
       </c>
-      <c r="U49" s="3" t="s">
-        <v>3</v>
+      <c r="U49" s="3">
+        <v>1200</v>
       </c>
       <c r="V49" s="3" t="s">
         <v>3</v>
@@ -3492,14 +3603,17 @@
       <c r="X49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y49" s="3">
-        <v>0</v>
+      <c r="Y49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Z49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3572,8 +3686,11 @@
       <c r="Z50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3646,82 +3763,88 @@
       <c r="Z51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>7800</v>
+      </c>
+      <c r="E52" s="3">
         <v>7600</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>7700</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>8000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>2600</v>
-      </c>
-      <c r="H52" s="3">
-        <v>8700</v>
       </c>
       <c r="I52" s="3">
         <v>8700</v>
       </c>
       <c r="J52" s="3">
+        <v>8700</v>
+      </c>
+      <c r="K52" s="3">
         <v>7300</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>7100</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>7000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>6500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>6300</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>6000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>5300</v>
-      </c>
-      <c r="Q52" s="3">
-        <v>5000</v>
       </c>
       <c r="R52" s="3">
         <v>5000</v>
       </c>
       <c r="S52" s="3">
+        <v>5000</v>
+      </c>
+      <c r="T52" s="3">
         <v>10500</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>4300</v>
       </c>
-      <c r="U52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W52" s="3">
+      <c r="W52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X52" s="3">
         <v>316400</v>
       </c>
-      <c r="X52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y52" s="3">
+      <c r="Y52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z52" s="3">
         <v>300</v>
       </c>
-      <c r="Z52" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3794,82 +3917,88 @@
       <c r="Z53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>898200</v>
+      </c>
+      <c r="E54" s="3">
         <v>966300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1003800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1051200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1103400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1187700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1068400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1059800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1080000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1000600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1046000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1087300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>855900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>901500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>770600</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>753100</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>290100</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>299300</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>317700</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>317800</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>317200</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>316200</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>400</v>
       </c>
-      <c r="Z54" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3896,8 +4025,9 @@
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
-    </row>
-    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA55" s="3"/>
+    </row>
+    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3924,82 +4054,86 @@
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
-    </row>
-    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA56" s="3"/>
+    </row>
+    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>64100</v>
+      </c>
+      <c r="E57" s="3">
         <v>74100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>71400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>84100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>71100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>101700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>99000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>62000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>62100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>44500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>45100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>35400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>27600</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>32100</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>28400</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>18100</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>19800</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>16700</v>
-      </c>
-      <c r="U57" s="3">
-        <v>100</v>
       </c>
       <c r="V57" s="3">
         <v>100</v>
       </c>
       <c r="W57" s="3">
+        <v>100</v>
+      </c>
+      <c r="X57" s="3">
         <v>200</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>100</v>
       </c>
-      <c r="Y57" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z57" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="Z57" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4007,25 +4141,25 @@
         <v>0</v>
       </c>
       <c r="E58" s="3">
-        <v>0</v>
+        <v>4600</v>
       </c>
       <c r="F58" s="3">
-        <v>4500</v>
+        <v>0</v>
       </c>
       <c r="G58" s="3">
         <v>4500</v>
       </c>
       <c r="H58" s="3">
+        <v>4500</v>
+      </c>
+      <c r="I58" s="3">
         <v>4400</v>
-      </c>
-      <c r="I58" s="3">
-        <v>4300</v>
       </c>
       <c r="J58" s="3">
         <v>4300</v>
       </c>
       <c r="K58" s="3">
-        <v>0</v>
+        <v>4300</v>
       </c>
       <c r="L58" s="3">
         <v>0</v>
@@ -4049,218 +4183,227 @@
         <v>0</v>
       </c>
       <c r="S58" s="3">
+        <v>0</v>
+      </c>
+      <c r="T58" s="3">
         <v>10200</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>5800</v>
       </c>
-      <c r="U58" s="3">
-        <v>0</v>
-      </c>
       <c r="V58" s="3">
         <v>0</v>
       </c>
       <c r="W58" s="3">
         <v>0</v>
       </c>
-      <c r="X58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y58" s="3">
+      <c r="X58" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z58" s="3">
         <v>100</v>
       </c>
-      <c r="Z58" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>102800</v>
+        <v>105000</v>
       </c>
       <c r="E59" s="3">
+        <v>189300</v>
+      </c>
+      <c r="F59" s="3">
         <v>199400</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>185100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>187200</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>176100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>156600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>144300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>222300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>193800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>193600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>177500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>161500</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>135400</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>99700</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>86800</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>88100</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>76700</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>900</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>800</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>600</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>400</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>300</v>
       </c>
-      <c r="Z59" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>293700</v>
+      </c>
+      <c r="E60" s="3">
         <v>320000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>321000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>327800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>330200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>352600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>340500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>288400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>284300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>238400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>238800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>212800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>189000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>167400</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>128200</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>104900</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>118100</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>99300</v>
-      </c>
-      <c r="U60" s="3">
-        <v>1000</v>
       </c>
       <c r="V60" s="3">
         <v>1000</v>
       </c>
       <c r="W60" s="3">
+        <v>1000</v>
+      </c>
+      <c r="X60" s="3">
         <v>800</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>500</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>400</v>
       </c>
-      <c r="Z60" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>315700</v>
+      </c>
+      <c r="E61" s="3">
         <v>315400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>302800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>301000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>301100</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>301200</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>315100</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>315900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>294900</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>294600</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>294300</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>294100</v>
       </c>
-      <c r="O61" s="3">
-        <v>0</v>
-      </c>
       <c r="P61" s="3">
         <v>0</v>
       </c>
@@ -4271,14 +4414,14 @@
         <v>0</v>
       </c>
       <c r="S61" s="3">
+        <v>0</v>
+      </c>
+      <c r="T61" s="3">
         <v>24700</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>28900</v>
       </c>
-      <c r="U61" s="3">
-        <v>0</v>
-      </c>
       <c r="V61" s="3">
         <v>0</v>
       </c>
@@ -4294,82 +4437,88 @@
       <c r="Z61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>10900</v>
+      </c>
+      <c r="E62" s="3">
         <v>5500</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>1500</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>1600</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>1800</v>
-      </c>
-      <c r="H62" s="3">
-        <v>1600</v>
       </c>
       <c r="I62" s="3">
         <v>1600</v>
       </c>
       <c r="J62" s="3">
+        <v>1600</v>
+      </c>
+      <c r="K62" s="3">
         <v>1300</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>145700</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>129000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>121200</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>115300</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>119800</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>148600</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>107400</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>163800</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>148200</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>86300</v>
-      </c>
-      <c r="U62" s="3">
-        <v>10900</v>
       </c>
       <c r="V62" s="3">
         <v>10900</v>
       </c>
       <c r="W62" s="3">
+        <v>10900</v>
+      </c>
+      <c r="X62" s="3">
         <v>20500</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>10900</v>
       </c>
-      <c r="Y62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4442,8 +4591,11 @@
       <c r="Z63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4516,8 +4668,11 @@
       <c r="Z64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4590,82 +4745,88 @@
       <c r="Z65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>766500</v>
+      </c>
+      <c r="E66" s="3">
         <v>785400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>772900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>773300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>775700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>795100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>793200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>732300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>725000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>662000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>654300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>622200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>308900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>316100</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>235600</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>268700</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>290900</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>214500</v>
-      </c>
-      <c r="U66" s="3">
-        <v>11900</v>
       </c>
       <c r="V66" s="3">
         <v>11900</v>
       </c>
       <c r="W66" s="3">
+        <v>11900</v>
+      </c>
+      <c r="X66" s="3">
         <v>21300</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>11400</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>400</v>
       </c>
-      <c r="Z66" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4692,8 +4853,9 @@
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
-    </row>
-    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA67" s="3"/>
+    </row>
+    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4766,8 +4928,11 @@
       <c r="Z68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4840,8 +5005,11 @@
       <c r="Z69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4891,14 +5059,14 @@
         <v>0</v>
       </c>
       <c r="S70" s="3">
+        <v>0</v>
+      </c>
+      <c r="T70" s="3">
         <v>615700</v>
       </c>
-      <c r="T70" s="3">
+      <c r="U70" s="3">
         <v>615800</v>
       </c>
-      <c r="U70" s="3">
-        <v>0</v>
-      </c>
       <c r="V70" s="3">
         <v>0</v>
       </c>
@@ -4914,8 +5082,11 @@
       <c r="Z70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4988,82 +5159,88 @@
       <c r="Z71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-1897300</v>
+      </c>
+      <c r="E72" s="3">
         <v>-1832600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-1755000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-1686200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-1614400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-1519600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-1361400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-1236200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-1156800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-1078100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-993600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-900900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-811700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-751500</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-682100</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-597100</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>200</v>
       </c>
-      <c r="T72" s="3">
-        <v>0</v>
-      </c>
       <c r="U72" s="3">
+        <v>0</v>
+      </c>
+      <c r="V72" s="3">
         <v>1100</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>1200</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>300</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>100</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-100</v>
       </c>
-      <c r="Z72" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5136,8 +5313,11 @@
       <c r="Z73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5210,8 +5390,11 @@
       <c r="Z74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5284,82 +5467,88 @@
       <c r="Z75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>131600</v>
+      </c>
+      <c r="E76" s="3">
         <v>181000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>230900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>277900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>327700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>392600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>275200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>327500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>355000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>338600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>391700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>465100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>547000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>585400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>535000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>484300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>-616500</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>-531000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>305800</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>305900</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>295900</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>304800</v>
       </c>
-      <c r="Y76" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z76" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="Z76" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5432,161 +5621,170 @@
       <c r="Z77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45688</v>
+      </c>
+      <c r="E80" s="2">
         <v>45596</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45504</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45412</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45322</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45230</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45138</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45046</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44957</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44865</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44773</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44681</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44592</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44500</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44408</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44316</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44227</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44135</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44012</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43921</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43830</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43738</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43646</v>
       </c>
-      <c r="Z80" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-64600</v>
+      </c>
+      <c r="E81" s="3">
         <v>-77600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-68900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-71800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-94700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-158200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-125300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-79400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-78700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-84500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-92700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-89300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-60100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-69400</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-84900</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-84500</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-103600</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-46600</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-100</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>500</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-600</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>200</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-100</v>
       </c>
-      <c r="Z81" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5613,65 +5811,66 @@
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
-    </row>
-    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA82" s="3"/>
+    </row>
+    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>4300</v>
+      </c>
+      <c r="E83" s="3">
         <v>4100</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>3900</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>4000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>3500</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>3200</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>3300</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>3400</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>6500</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>6100</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>6300</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>6200</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>6300</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>4600</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>2800</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>2700</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>2600</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>2800</v>
       </c>
-      <c r="U83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V83" s="3" t="s">
         <v>3</v>
       </c>
@@ -5681,14 +5880,17 @@
       <c r="X83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y83" s="3">
-        <v>0</v>
+      <c r="Y83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Z83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5761,8 +5963,11 @@
       <c r="Z84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5835,8 +6040,11 @@
       <c r="Z85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5909,8 +6117,11 @@
       <c r="Z86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5983,8 +6194,11 @@
       <c r="Z87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6057,82 +6271,88 @@
       <c r="Z88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="E89" s="3">
         <v>-30600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-51200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-62500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-41500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-96900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-86400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-104200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-50400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-83000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-62900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-70800</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-48100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-47900</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-23700</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-37500</v>
-      </c>
-      <c r="S89" s="3">
-        <v>-20900</v>
       </c>
       <c r="T89" s="3">
         <v>-20900</v>
       </c>
       <c r="U89" s="3">
+        <v>-20900</v>
+      </c>
+      <c r="V89" s="3">
         <v>-100</v>
-      </c>
-      <c r="V89" s="3">
-        <v>-300</v>
       </c>
       <c r="W89" s="3">
         <v>-300</v>
       </c>
       <c r="X89" s="3">
+        <v>-300</v>
+      </c>
+      <c r="Y89" s="3">
         <v>-700</v>
       </c>
-      <c r="Y89" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z89" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="Z89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6159,65 +6379,66 @@
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
-    </row>
-    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA90" s="3"/>
+    </row>
+    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="E91" s="3">
         <v>-2800</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-3800</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-3500</v>
-      </c>
-      <c r="G91" s="3">
-        <v>-4800</v>
       </c>
       <c r="H91" s="3">
         <v>-4800</v>
       </c>
       <c r="I91" s="3">
+        <v>-4800</v>
+      </c>
+      <c r="J91" s="3">
         <v>-4000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-5800</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-4400</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-5300</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-5700</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-3200</v>
-      </c>
-      <c r="O91" s="3">
-        <v>-4300</v>
       </c>
       <c r="P91" s="3">
         <v>-4300</v>
       </c>
       <c r="Q91" s="3">
+        <v>-4300</v>
+      </c>
+      <c r="R91" s="3">
         <v>-3700</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-4100</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-2600</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-3000</v>
       </c>
-      <c r="U91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V91" s="3" t="s">
         <v>3</v>
       </c>
@@ -6227,14 +6448,17 @@
       <c r="X91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y91" s="3">
-        <v>0</v>
+      <c r="Y91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Z91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6307,8 +6531,11 @@
       <c r="Z92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6381,73 +6608,76 @@
       <c r="Z93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="E94" s="3">
         <v>-2800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-3800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-3500</v>
-      </c>
-      <c r="G94" s="3">
-        <v>-4800</v>
       </c>
       <c r="H94" s="3">
         <v>-4800</v>
       </c>
       <c r="I94" s="3">
+        <v>-4800</v>
+      </c>
+      <c r="J94" s="3">
         <v>-4000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>99200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>100600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>69700</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-290500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-5900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-4300</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-209600</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-3700</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-4100</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-2600</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-3000</v>
       </c>
-      <c r="U94" s="3">
-        <v>0</v>
-      </c>
       <c r="V94" s="3">
+        <v>0</v>
+      </c>
+      <c r="W94" s="3">
         <v>100</v>
       </c>
-      <c r="W94" s="3">
-        <v>0</v>
-      </c>
-      <c r="X94" s="3" t="s">
-        <v>3</v>
+      <c r="X94" s="3">
+        <v>0</v>
       </c>
       <c r="Y94" s="3" t="s">
         <v>3</v>
@@ -6455,8 +6685,11 @@
       <c r="Z94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6483,8 +6716,9 @@
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
-    </row>
-    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA95" s="3"/>
+    </row>
+    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6509,8 +6743,8 @@
       <c r="J96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L96" s="3">
         <v>0</v>
@@ -6557,8 +6791,11 @@
       <c r="Z96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6631,8 +6868,11 @@
       <c r="Z97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6705,8 +6945,11 @@
       <c r="Z98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6779,138 +7022,144 @@
       <c r="Z99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>12100</v>
+      </c>
+      <c r="E100" s="3">
         <v>9500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>5900</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>1000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>5800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>236700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>40300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>23800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>54900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>14400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>303100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>2500</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>5600</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>35600</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>506000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>200</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>3400</v>
       </c>
-      <c r="U100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W100" s="3">
+      <c r="W100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X100" s="3">
         <v>-100</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>315500</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>100</v>
       </c>
-      <c r="Z100" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>800</v>
+      </c>
+      <c r="E101" s="3">
         <v>-1500</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>300</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>500</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>800</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-500</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-100</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-1000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>800</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-500</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-100</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-1000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-300</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-700</v>
       </c>
-      <c r="Q101" s="3">
-        <v>0</v>
-      </c>
       <c r="R101" s="3">
         <v>0</v>
       </c>
       <c r="S101" s="3">
+        <v>0</v>
+      </c>
+      <c r="T101" s="3">
         <v>100</v>
       </c>
-      <c r="T101" s="3">
-        <v>0</v>
-      </c>
-      <c r="U101" s="3" t="s">
-        <v>3</v>
+      <c r="U101" s="3">
+        <v>0</v>
       </c>
       <c r="V101" s="3" t="s">
         <v>3</v>
@@ -6921,84 +7170,90 @@
       <c r="X101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y101" s="3">
-        <v>0</v>
+      <c r="Y101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Z101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>5200</v>
+      </c>
+      <c r="E102" s="3">
         <v>-23900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-48600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-65600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-39600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>133500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-49800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>19200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>105900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-352900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>225300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-50300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-252600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>8300</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>464300</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-23200</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-20400</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-100</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-200</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-400</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>800</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>100</v>
       </c>
-      <c r="Z102" s="3" t="s">
+      <c r="AA102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/CHPT_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CHPT_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="92">
   <si>
     <t>CHPT</t>
   </si>
@@ -865,7 +865,7 @@
         <v>83400</v>
       </c>
       <c r="H9" s="3">
-        <v>92800</v>
+        <v>91800</v>
       </c>
       <c r="I9" s="3">
         <v>134200</v>
@@ -942,7 +942,7 @@
         <v>23600</v>
       </c>
       <c r="H10" s="3">
-        <v>23000</v>
+        <v>24000</v>
       </c>
       <c r="I10" s="3">
         <v>-23900</v>
@@ -1048,7 +1048,7 @@
         <v>36100</v>
       </c>
       <c r="H12" s="3">
-        <v>47700</v>
+        <v>43500</v>
       </c>
       <c r="I12" s="3">
         <v>56500</v>
@@ -1189,8 +1189,8 @@
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>3</v>
+      <c r="D14" s="3">
+        <v>0</v>
       </c>
       <c r="E14" s="3">
         <v>9800</v>
@@ -1202,7 +1202,7 @@
         <v>3</v>
       </c>
       <c r="H14" s="3">
-        <v>12700</v>
+        <v>28300</v>
       </c>
       <c r="I14" s="3" t="s">
         <v>3</v>
@@ -1382,7 +1382,7 @@
         <v>174200</v>
       </c>
       <c r="H17" s="3">
-        <v>196100</v>
+        <v>180500</v>
       </c>
       <c r="I17" s="3">
         <v>264100</v>
@@ -1459,7 +1459,7 @@
         <v>-67100</v>
       </c>
       <c r="H18" s="3">
-        <v>-80300</v>
+        <v>-64700</v>
       </c>
       <c r="I18" s="3">
         <v>-153800</v>
@@ -1642,7 +1642,7 @@
         <v>-60500</v>
       </c>
       <c r="H21" s="3">
-        <v>-71800</v>
+        <v>-56200</v>
       </c>
       <c r="I21" s="3">
         <v>-149400</v>
@@ -1707,7 +1707,7 @@
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>8000</v>
+        <v>2200</v>
       </c>
       <c r="E22" s="3">
         <v>9300</v>
@@ -1784,7 +1784,7 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-63800</v>
+        <v>-58000</v>
       </c>
       <c r="E23" s="3">
         <v>-76100</v>
@@ -2015,7 +2015,7 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-64600</v>
+        <v>-58800</v>
       </c>
       <c r="E26" s="3">
         <v>-77600</v>
@@ -2092,7 +2092,7 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-64600</v>
+        <v>-58800</v>
       </c>
       <c r="E27" s="3">
         <v>-77600</v>
@@ -2554,7 +2554,7 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-64600</v>
+        <v>-58800</v>
       </c>
       <c r="E33" s="3">
         <v>-77600</v>
@@ -2708,7 +2708,7 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-64600</v>
+        <v>-58800</v>
       </c>
       <c r="E35" s="3">
         <v>-77600</v>
@@ -3232,8 +3232,8 @@
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3" t="s">
-        <v>3</v>
+      <c r="D45" s="3">
+        <v>3200</v>
       </c>
       <c r="E45" s="3">
         <v>25400</v>
@@ -3772,7 +3772,7 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>7800</v>
+        <v>1700</v>
       </c>
       <c r="E52" s="3">
         <v>7600</v>
@@ -4138,7 +4138,7 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>4600</v>
       </c>
       <c r="E58" s="3">
         <v>4600</v>
@@ -4215,7 +4215,7 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>105000</v>
+        <v>175800</v>
       </c>
       <c r="E59" s="3">
         <v>189300</v>
@@ -4369,7 +4369,7 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>315700</v>
+        <v>312400</v>
       </c>
       <c r="E61" s="3">
         <v>315400</v>
@@ -4446,7 +4446,7 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>10900</v>
+        <v>8400</v>
       </c>
       <c r="E62" s="3">
         <v>5500</v>
@@ -4754,7 +4754,7 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>766500</v>
+        <v>760700</v>
       </c>
       <c r="E66" s="3">
         <v>785400</v>
@@ -5168,7 +5168,7 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>-1897300</v>
+        <v>-1891400</v>
       </c>
       <c r="E72" s="3">
         <v>-1832600</v>
@@ -5476,7 +5476,7 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>131600</v>
+        <v>137500</v>
       </c>
       <c r="E76" s="3">
         <v>181000</v>
@@ -5712,7 +5712,7 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-64600</v>
+        <v>-58800</v>
       </c>
       <c r="E81" s="3">
         <v>-77600</v>

--- a/AAII_Financials/Quarterly/CHPT_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CHPT_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="92">
   <si>
     <t>CHPT</t>
   </si>
@@ -656,182 +656,185 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AA102"/>
+  <dimension ref="A5:AB102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45777</v>
+      </c>
+      <c r="E7" s="2">
         <v>45688</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45596</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45504</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45412</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45322</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45230</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45138</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45046</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44957</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44865</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44773</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44681</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44592</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44500</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44408</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44316</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44227</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44135</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44012</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43921</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43830</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43738</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43646</v>
       </c>
-      <c r="AA7" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>97600</v>
+      </c>
+      <c r="E8" s="3">
         <v>101900</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>99600</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>108500</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>107000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>115800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>110300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>150500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>130000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>152800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>125300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>108300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>81600</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>79300</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>65000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>56100</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>40500</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>42400</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>36400</v>
       </c>
-      <c r="V8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W8" s="3" t="s">
         <v>3</v>
       </c>
@@ -841,74 +844,77 @@
       <c r="Y8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z8" s="3">
-        <v>0</v>
+      <c r="Z8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AA8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>69700</v>
+      </c>
+      <c r="E9" s="3">
         <v>73200</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>75900</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>83000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>83400</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>91800</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>134200</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>149400</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>99500</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>119800</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>102700</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>90100</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>69500</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>61900</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>49000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>45300</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>31300</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>33500</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>29100</v>
       </c>
-      <c r="V9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W9" s="3" t="s">
         <v>3</v>
       </c>
@@ -924,68 +930,71 @@
       <c r="AA9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>28000</v>
+      </c>
+      <c r="E10" s="3">
         <v>28700</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>23700</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>25600</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>23600</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>24000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>-23900</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>30500</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>33000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>22600</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>18200</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>12100</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>17400</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>16000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>10800</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>9200</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>8900</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>7300</v>
       </c>
-      <c r="V10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W10" s="3" t="s">
         <v>3</v>
       </c>
@@ -1001,8 +1010,11 @@
       <c r="AA10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1030,68 +1042,69 @@
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
-    </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB11" s="3"/>
+    </row>
+    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>33500</v>
+      </c>
+      <c r="E12" s="3">
         <v>30400</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>35400</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>36500</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>36100</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>43500</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>56500</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>59600</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>49400</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>46700</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>48100</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>51800</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>48300</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>42500</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>36800</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>40400</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>25400</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>20900</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>18900</v>
       </c>
-      <c r="V12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1107,8 +1120,11 @@
       <c r="AA12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1184,29 +1200,32 @@
       <c r="AA13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
+      <c r="D14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3">
         <v>9800</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H14" s="3">
+      <c r="H14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I14" s="3">
         <v>28300</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1225,15 +1244,15 @@
       <c r="O14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P14" s="3">
+      <c r="P14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q14" s="3">
         <v>200</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>4800</v>
       </c>
-      <c r="R14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1246,8 +1265,8 @@
       <c r="V14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W14" s="3">
-        <v>0</v>
+      <c r="W14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X14" s="3">
         <v>0</v>
@@ -1261,38 +1280,41 @@
       <c r="AA14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>6900</v>
+      </c>
+      <c r="E15" s="3">
         <v>7000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>7300</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>7500</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>7400</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>7300</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>7100</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>7000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>7100</v>
       </c>
-      <c r="L15" s="3">
-        <v>0</v>
-      </c>
       <c r="M15" s="3">
         <v>0</v>
       </c>
@@ -1338,8 +1360,11 @@
       <c r="AA15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1364,145 +1389,149 @@
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
-    </row>
-    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB16" s="3"/>
+    </row>
+    <row r="17" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>151500</v>
+      </c>
+      <c r="E17" s="3">
         <v>156800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>158000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>171300</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>174200</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>180500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>264100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>273800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>210000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>231100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>208600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>198700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>171500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>158600</v>
-      </c>
-      <c r="Q17" s="3">
-        <v>130400</v>
       </c>
       <c r="R17" s="3">
         <v>130400</v>
       </c>
       <c r="S17" s="3">
+        <v>130400</v>
+      </c>
+      <c r="T17" s="3">
         <v>87100</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>77700</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>69000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>200</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>300</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>1600</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>600</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>100</v>
       </c>
-      <c r="AA17" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-53800</v>
+      </c>
+      <c r="E18" s="3">
         <v>-54900</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-58300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-62700</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-67100</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-64700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-153800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-123300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-79900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-78300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-83300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-90400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-89900</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-79300</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-65400</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-74300</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-46600</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-35300</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-32600</v>
       </c>
-      <c r="V18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1512,14 +1541,17 @@
       <c r="Y18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="Z18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA18" s="3">
         <v>-100</v>
       </c>
-      <c r="AA18" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1547,68 +1579,69 @@
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
-    </row>
-    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB19" s="3"/>
+    </row>
+    <row r="20" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="E20" s="3">
         <v>2300</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>200</v>
       </c>
-      <c r="F20" s="3">
-        <v>0</v>
-      </c>
       <c r="G20" s="3">
+        <v>0</v>
+      </c>
+      <c r="H20" s="3">
         <v>900</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-1200</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>2800</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-600</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>3200</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>1000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>200</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-300</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>16400</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-4400</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-10600</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>130400</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-54600</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-7400</v>
       </c>
-      <c r="V20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1618,74 +1651,77 @@
       <c r="Y20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z20" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA20" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="Z20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-44300</v>
+      </c>
+      <c r="E21" s="3">
         <v>-50300</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-51200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-55300</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-60500</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-56200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-149400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-116300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-72300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-68700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-76200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-83900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-84000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-56600</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-65200</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-82000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>86600</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-87300</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-37200</v>
       </c>
-      <c r="V21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1701,19 +1737,22 @@
       <c r="AA21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>6400</v>
+      </c>
+      <c r="E22" s="3">
         <v>2200</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>9300</v>
-      </c>
-      <c r="F22" s="3">
-        <v>6600</v>
       </c>
       <c r="G22" s="3">
         <v>6600</v>
@@ -1722,29 +1761,29 @@
         <v>6600</v>
       </c>
       <c r="I22" s="3">
+        <v>6600</v>
+      </c>
+      <c r="J22" s="3">
         <v>3800</v>
-      </c>
-      <c r="J22" s="3">
-        <v>2900</v>
       </c>
       <c r="K22" s="3">
         <v>2900</v>
       </c>
       <c r="L22" s="3">
+        <v>2900</v>
+      </c>
+      <c r="M22" s="3">
         <v>3000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>2600</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>2900</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>900</v>
       </c>
-      <c r="P22" s="3">
-        <v>0</v>
-      </c>
       <c r="Q22" s="3">
         <v>0</v>
       </c>
@@ -1752,16 +1791,16 @@
         <v>0</v>
       </c>
       <c r="S22" s="3">
+        <v>0</v>
+      </c>
+      <c r="T22" s="3">
         <v>1500</v>
-      </c>
-      <c r="T22" s="3">
-        <v>800</v>
       </c>
       <c r="U22" s="3">
         <v>800</v>
       </c>
-      <c r="V22" s="3" t="s">
-        <v>3</v>
+      <c r="V22" s="3">
+        <v>800</v>
       </c>
       <c r="W22" s="3" t="s">
         <v>3</v>
@@ -1772,168 +1811,177 @@
       <c r="Y22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z22" s="3">
-        <v>0</v>
+      <c r="Z22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AA22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-56500</v>
+      </c>
+      <c r="E23" s="3">
         <v>-58000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-76100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-67200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-71400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-94900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-158500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-124400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-79800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-78100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-84900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-93100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-91100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-62900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-69800</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-84900</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>82300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-90800</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-40800</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-100</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>700</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-400</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>400</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-100</v>
       </c>
-      <c r="AA23" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>600</v>
+      </c>
+      <c r="E24" s="3">
         <v>800</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>1500</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>1600</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>400</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-200</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-300</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>900</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-400</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>500</v>
-      </c>
-      <c r="M24" s="3">
-        <v>-400</v>
       </c>
       <c r="N24" s="3">
         <v>-400</v>
       </c>
       <c r="O24" s="3">
+        <v>-400</v>
+      </c>
+      <c r="P24" s="3">
         <v>-1900</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-2700</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-300</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>100</v>
       </c>
-      <c r="S24" s="3">
-        <v>0</v>
-      </c>
       <c r="T24" s="3">
         <v>0</v>
       </c>
       <c r="U24" s="3">
+        <v>0</v>
+      </c>
+      <c r="V24" s="3">
         <v>100</v>
       </c>
-      <c r="V24" s="3">
-        <v>0</v>
-      </c>
       <c r="W24" s="3">
+        <v>0</v>
+      </c>
+      <c r="X24" s="3">
         <v>200</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>300</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>200</v>
       </c>
-      <c r="Z24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2009,162 +2057,171 @@
       <c r="AA25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-57100</v>
+      </c>
+      <c r="E26" s="3">
         <v>-58800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-77600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-68900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-71800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-94700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-158200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-125300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-79400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-78700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-84500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-92700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-89300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-60100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-69400</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-84900</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>82300</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-90700</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-40900</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-100</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>500</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-600</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>200</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-100</v>
       </c>
-      <c r="AA26" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-57100</v>
+      </c>
+      <c r="E27" s="3">
         <v>-58800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-77600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-68900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-71800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-94700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-158200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-125300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-79400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-78700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-84500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-92700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-89300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-60100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-69400</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-84900</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-84500</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-103600</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-46600</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-100</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>500</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-600</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>200</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-100</v>
       </c>
-      <c r="AA27" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2240,8 +2297,11 @@
       <c r="AA28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2317,8 +2377,11 @@
       <c r="AA29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2394,8 +2457,11 @@
       <c r="AA30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2471,68 +2537,71 @@
       <c r="AA31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>2600</v>
+      </c>
+      <c r="E32" s="3">
         <v>-2300</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-200</v>
       </c>
-      <c r="F32" s="3">
-        <v>0</v>
-      </c>
       <c r="G32" s="3">
+        <v>0</v>
+      </c>
+      <c r="H32" s="3">
         <v>-900</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>1200</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-2800</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>600</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-3200</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-1000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-200</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>300</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-16400</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>4400</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>10600</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-130400</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>54600</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>7400</v>
       </c>
-      <c r="V32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2542,91 +2611,97 @@
       <c r="Y32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z32" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA32" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="Z32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-57100</v>
+      </c>
+      <c r="E33" s="3">
         <v>-58800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-77600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-68900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-71800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-94700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-158200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-125300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-79400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-78700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-84500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-92700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-89300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-60100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-69400</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-84900</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-84500</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-103600</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-46600</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-100</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>500</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-600</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>200</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-100</v>
       </c>
-      <c r="AA33" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2702,167 +2777,176 @@
       <c r="AA34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-57100</v>
+      </c>
+      <c r="E35" s="3">
         <v>-58800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-77600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-68900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-71800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-94700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-158200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-125300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-79400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-78700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-84500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-92700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-89300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-60100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-69400</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-84900</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-84500</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-103600</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-46600</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-100</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>500</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-600</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>200</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-100</v>
       </c>
-      <c r="AA35" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45777</v>
+      </c>
+      <c r="E38" s="2">
         <v>45688</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45596</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45504</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45412</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45322</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45230</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45138</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45046</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44957</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44865</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44773</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44681</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44592</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44500</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44408</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44316</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44227</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44135</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44012</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43921</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43830</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43738</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43646</v>
       </c>
-      <c r="AA38" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2890,8 +2974,9 @@
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
-    </row>
-    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB39" s="3"/>
+    </row>
+    <row r="40" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2919,85 +3004,89 @@
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
-    </row>
-    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB40" s="3"/>
+    </row>
+    <row r="41" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>195900</v>
+      </c>
+      <c r="E41" s="3">
         <v>224600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>219400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>243300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>261900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>327400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>367000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>233500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>283300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>264200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>188300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>187700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>540600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>315200</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>365500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>618100</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>609800</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>145500</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>168700</v>
       </c>
-      <c r="V41" s="3">
-        <v>0</v>
-      </c>
       <c r="W41" s="3">
+        <v>0</v>
+      </c>
+      <c r="X41" s="3">
         <v>200</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>400</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>800</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>100</v>
       </c>
-      <c r="AA41" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3026,17 +3115,17 @@
         <v>0</v>
       </c>
       <c r="L42" s="3">
+        <v>0</v>
+      </c>
+      <c r="M42" s="3">
         <v>105000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>208900</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>283900</v>
       </c>
-      <c r="O42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P42" s="3" t="s">
         <v>3</v>
       </c>
@@ -3052,8 +3141,8 @@
       <c r="T42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U42" s="3">
-        <v>0</v>
+      <c r="U42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V42" s="3">
         <v>0</v>
@@ -3073,68 +3162,71 @@
       <c r="AA42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>98700</v>
+      </c>
+      <c r="E43" s="3">
         <v>95900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>111900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>111500</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>117800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>124000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>151800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>202100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>165100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>164900</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>123000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>109900</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>79900</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>75900</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>66100</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>42700</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>34900</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>35100</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>28300</v>
       </c>
-      <c r="V43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3144,74 +3236,77 @@
       <c r="Y43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z43" s="3">
-        <v>0</v>
+      <c r="Z43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AA43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>212400</v>
+      </c>
+      <c r="E44" s="3">
         <v>209300</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>222000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>228500</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>223600</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>198600</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>199100</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>143600</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>115200</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>68700</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>62400</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>53400</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>45300</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>35900</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>29900</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>27900</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>28900</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>33600</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>30700</v>
       </c>
-      <c r="V44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W44" s="3" t="s">
         <v>3</v>
       </c>
@@ -3221,168 +3316,177 @@
       <c r="Y44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z44" s="3">
-        <v>0</v>
+      <c r="Z44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AA44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>26900</v>
+      </c>
+      <c r="E45" s="3">
         <v>3200</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>25400</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>22300</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>18700</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>3000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>25500</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>24700</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>23600</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>101400</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>59000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>45300</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>46500</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>37000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>33100</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>22500</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>20300</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>12500</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>15200</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>200</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>300</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>400</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>300</v>
       </c>
-      <c r="Z45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>554300</v>
+      </c>
+      <c r="E46" s="3">
         <v>566600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>620100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>652900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>698300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>742700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>824400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>692200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>682200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>704200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>641600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>680200</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>712200</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>464100</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>494600</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>711300</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>693900</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>226600</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>242900</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>300</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>500</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>800</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>1100</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>100</v>
       </c>
-      <c r="AA46" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3410,8 +3514,8 @@
       <c r="K47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L47" s="3">
-        <v>0</v>
+      <c r="L47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M47" s="3">
         <v>0</v>
@@ -3441,85 +3545,88 @@
         <v>0</v>
       </c>
       <c r="V47" s="3">
+        <v>0</v>
+      </c>
+      <c r="W47" s="3">
         <v>317400</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>317300</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>316400</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>315100</v>
       </c>
-      <c r="Z47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>46800</v>
+      </c>
+      <c r="E48" s="3">
         <v>50000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>52700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>54900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>55600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>57800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>60300</v>
-      </c>
-      <c r="J48" s="3">
-        <v>62900</v>
       </c>
       <c r="K48" s="3">
         <v>62900</v>
       </c>
       <c r="L48" s="3">
+        <v>62900</v>
+      </c>
+      <c r="M48" s="3">
         <v>62300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>60600</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>59300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>59200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>60100</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>58300</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>53100</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>53000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>51800</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>50800</v>
       </c>
-      <c r="V48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3529,61 +3636,64 @@
       <c r="Y48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z48" s="3">
-        <v>0</v>
+      <c r="Z48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AA48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>289100</v>
+      </c>
+      <c r="E49" s="3">
         <v>273700</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>286000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>288200</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>289300</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>294300</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>294200</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>304500</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>307500</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>306400</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>291400</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>300100</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>309600</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>325700</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>343200</v>
-      </c>
-      <c r="R49" s="3">
-        <v>1200</v>
       </c>
       <c r="S49" s="3">
         <v>1200</v>
@@ -3594,8 +3704,8 @@
       <c r="U49" s="3">
         <v>1200</v>
       </c>
-      <c r="V49" s="3" t="s">
-        <v>3</v>
+      <c r="V49" s="3">
+        <v>1200</v>
       </c>
       <c r="W49" s="3" t="s">
         <v>3</v>
@@ -3606,14 +3716,17 @@
       <c r="Y49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z49" s="3">
-        <v>0</v>
+      <c r="Z49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AA49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3689,8 +3802,11 @@
       <c r="AA50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3766,85 +3882,91 @@
       <c r="AA51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>7300</v>
+      </c>
+      <c r="E52" s="3">
         <v>1700</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>7600</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>7700</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>8000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>2600</v>
-      </c>
-      <c r="I52" s="3">
-        <v>8700</v>
       </c>
       <c r="J52" s="3">
         <v>8700</v>
       </c>
       <c r="K52" s="3">
+        <v>8700</v>
+      </c>
+      <c r="L52" s="3">
         <v>7300</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>7100</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>7000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>6500</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>6300</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>6000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>5300</v>
-      </c>
-      <c r="R52" s="3">
-        <v>5000</v>
       </c>
       <c r="S52" s="3">
         <v>5000</v>
       </c>
       <c r="T52" s="3">
+        <v>5000</v>
+      </c>
+      <c r="U52" s="3">
         <v>10500</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>4300</v>
       </c>
-      <c r="V52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X52" s="3">
+      <c r="X52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y52" s="3">
         <v>316400</v>
       </c>
-      <c r="Y52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z52" s="3">
+      <c r="Z52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA52" s="3">
         <v>300</v>
       </c>
-      <c r="AA52" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3920,85 +4042,91 @@
       <c r="AA53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>897600</v>
+      </c>
+      <c r="E54" s="3">
         <v>898200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>966300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1003800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1051200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1103400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1187700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1068400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1059800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1080000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1000600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1046000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1087300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>855900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>901500</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>770600</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>753100</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>290100</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>299300</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>317700</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>317800</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>317200</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>316200</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>400</v>
       </c>
-      <c r="AA54" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4026,8 +4154,9 @@
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
-    </row>
-    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB55" s="3"/>
+    </row>
+    <row r="56" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4055,114 +4184,118 @@
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
-    </row>
-    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB56" s="3"/>
+    </row>
+    <row r="57" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>52200</v>
+      </c>
+      <c r="E57" s="3">
         <v>64100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>74100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>71400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>84100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>71100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>101700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>99000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>62000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>62100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>44500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>45100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>35400</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>27600</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>32100</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>28400</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>18100</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>19800</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>16700</v>
-      </c>
-      <c r="V57" s="3">
-        <v>100</v>
       </c>
       <c r="W57" s="3">
         <v>100</v>
       </c>
       <c r="X57" s="3">
+        <v>100</v>
+      </c>
+      <c r="Y57" s="3">
         <v>200</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>100</v>
       </c>
-      <c r="Z57" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA57" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AA57" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>4600</v>
+        <v>4800</v>
       </c>
       <c r="E58" s="3">
         <v>4600</v>
       </c>
       <c r="F58" s="3">
-        <v>0</v>
+        <v>4600</v>
       </c>
       <c r="G58" s="3">
-        <v>4500</v>
+        <v>4400</v>
       </c>
       <c r="H58" s="3">
         <v>4500</v>
       </c>
       <c r="I58" s="3">
+        <v>4500</v>
+      </c>
+      <c r="J58" s="3">
         <v>4400</v>
-      </c>
-      <c r="J58" s="3">
-        <v>4300</v>
       </c>
       <c r="K58" s="3">
         <v>4300</v>
       </c>
       <c r="L58" s="3">
-        <v>0</v>
+        <v>4300</v>
       </c>
       <c r="M58" s="3">
         <v>0</v>
@@ -4186,227 +4319,236 @@
         <v>0</v>
       </c>
       <c r="T58" s="3">
+        <v>0</v>
+      </c>
+      <c r="U58" s="3">
         <v>10200</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>5800</v>
       </c>
-      <c r="V58" s="3">
-        <v>0</v>
-      </c>
       <c r="W58" s="3">
         <v>0</v>
       </c>
       <c r="X58" s="3">
         <v>0</v>
       </c>
-      <c r="Y58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z58" s="3">
+      <c r="Y58" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA58" s="3">
         <v>100</v>
       </c>
-      <c r="AA58" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>188000</v>
+      </c>
+      <c r="E59" s="3">
         <v>175800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>189300</v>
       </c>
-      <c r="F59" s="3">
-        <v>199400</v>
-      </c>
       <c r="G59" s="3">
+        <v>195000</v>
+      </c>
+      <c r="H59" s="3">
         <v>185100</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>187200</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>176100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>156600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>144300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>222300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>193800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>193600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>177500</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>161500</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>135400</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>99700</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>86800</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>88100</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>76700</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>900</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>800</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>600</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>400</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>300</v>
       </c>
-      <c r="AA59" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>304400</v>
+      </c>
+      <c r="E60" s="3">
         <v>293700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>320000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>321000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>327800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>330200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>352600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>340500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>288400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>284300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>238400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>238800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>212800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>189000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>167400</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>128200</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>104900</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>118100</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>99300</v>
-      </c>
-      <c r="V60" s="3">
-        <v>1000</v>
       </c>
       <c r="W60" s="3">
         <v>1000</v>
       </c>
       <c r="X60" s="3">
+        <v>1000</v>
+      </c>
+      <c r="Y60" s="3">
         <v>800</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>500</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>400</v>
       </c>
-      <c r="AA60" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>322200</v>
+      </c>
+      <c r="E61" s="3">
         <v>312400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>315400</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>302800</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>301000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>301100</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>301200</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>315100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>315900</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>294900</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>294600</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>294300</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>294100</v>
       </c>
-      <c r="P61" s="3">
-        <v>0</v>
-      </c>
       <c r="Q61" s="3">
         <v>0</v>
       </c>
@@ -4417,14 +4559,14 @@
         <v>0</v>
       </c>
       <c r="T61" s="3">
+        <v>0</v>
+      </c>
+      <c r="U61" s="3">
         <v>24700</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>28900</v>
       </c>
-      <c r="V61" s="3">
-        <v>0</v>
-      </c>
       <c r="W61" s="3">
         <v>0</v>
       </c>
@@ -4440,85 +4582,91 @@
       <c r="AA61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>4000</v>
+      </c>
+      <c r="E62" s="3">
         <v>8400</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>5500</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>1500</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>1600</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>1800</v>
-      </c>
-      <c r="I62" s="3">
-        <v>1600</v>
       </c>
       <c r="J62" s="3">
         <v>1600</v>
       </c>
       <c r="K62" s="3">
+        <v>1600</v>
+      </c>
+      <c r="L62" s="3">
         <v>1300</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>145700</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>129000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>121200</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>115300</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>119800</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>148600</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>107400</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>163800</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>148200</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>86300</v>
-      </c>
-      <c r="V62" s="3">
-        <v>10900</v>
       </c>
       <c r="W62" s="3">
         <v>10900</v>
       </c>
       <c r="X62" s="3">
+        <v>10900</v>
+      </c>
+      <c r="Y62" s="3">
         <v>20500</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>10900</v>
       </c>
-      <c r="Z62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4594,8 +4742,11 @@
       <c r="AA63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4671,8 +4822,11 @@
       <c r="AA64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4748,85 +4902,91 @@
       <c r="AA65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>779000</v>
+      </c>
+      <c r="E66" s="3">
         <v>760700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>785400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>772900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>773300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>775700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>795100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>793200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>732300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>725000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>662000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>654300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>622200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>308900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>316100</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>235600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>268700</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>290900</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>214500</v>
-      </c>
-      <c r="V66" s="3">
-        <v>11900</v>
       </c>
       <c r="W66" s="3">
         <v>11900</v>
       </c>
       <c r="X66" s="3">
+        <v>11900</v>
+      </c>
+      <c r="Y66" s="3">
         <v>21300</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>11400</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>400</v>
       </c>
-      <c r="AA66" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4854,8 +5014,9 @@
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
       <c r="AA67" s="3"/>
-    </row>
-    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB67" s="3"/>
+    </row>
+    <row r="68" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4931,8 +5092,11 @@
       <c r="AA68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5008,8 +5172,11 @@
       <c r="AA69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5062,14 +5229,14 @@
         <v>0</v>
       </c>
       <c r="T70" s="3">
+        <v>0</v>
+      </c>
+      <c r="U70" s="3">
         <v>615700</v>
       </c>
-      <c r="U70" s="3">
+      <c r="V70" s="3">
         <v>615800</v>
       </c>
-      <c r="V70" s="3">
-        <v>0</v>
-      </c>
       <c r="W70" s="3">
         <v>0</v>
       </c>
@@ -5085,8 +5252,11 @@
       <c r="AA70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5162,85 +5332,91 @@
       <c r="AA71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-1948600</v>
+      </c>
+      <c r="E72" s="3">
         <v>-1891400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-1832600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-1755000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-1686200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-1614400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-1519600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-1361400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-1236200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-1156800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-1078100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-993600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-900900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-811700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-751500</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-682100</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-597100</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>200</v>
       </c>
-      <c r="U72" s="3">
-        <v>0</v>
-      </c>
       <c r="V72" s="3">
+        <v>0</v>
+      </c>
+      <c r="W72" s="3">
         <v>1100</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>1200</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>300</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>100</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-100</v>
       </c>
-      <c r="AA72" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5316,8 +5492,11 @@
       <c r="AA73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5393,8 +5572,11 @@
       <c r="AA74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5470,85 +5652,91 @@
       <c r="AA75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>118600</v>
+      </c>
+      <c r="E76" s="3">
         <v>137500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>181000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>230900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>277900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>327700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>392600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>275200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>327500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>355000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>338600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>391700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>465100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>547000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>585400</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>535000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>484300</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>-616500</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>-531000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>305800</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>305900</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>295900</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>304800</v>
       </c>
-      <c r="Z76" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA76" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AA76" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5624,167 +5812,176 @@
       <c r="AA77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45777</v>
+      </c>
+      <c r="E80" s="2">
         <v>45688</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45596</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45504</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45412</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45322</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45230</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45138</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45046</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44957</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44865</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44773</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44681</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44592</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44500</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44408</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44316</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44227</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44135</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44012</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43921</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43830</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43738</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43646</v>
       </c>
-      <c r="AA80" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-57100</v>
+      </c>
+      <c r="E81" s="3">
         <v>-58800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-77600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-68900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-71800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-94700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-158200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-125300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-79400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-78700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-84500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-92700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-89300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-60100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-69400</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-84900</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-84500</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-103600</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-46600</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-100</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>500</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-600</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>200</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-100</v>
       </c>
-      <c r="AA81" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5812,68 +6009,69 @@
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
-    </row>
-    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB82" s="3"/>
+    </row>
+    <row r="83" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>4400</v>
+      </c>
+      <c r="E83" s="3">
         <v>4300</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>4100</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>3900</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>4000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>3500</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>3200</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>3300</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>3400</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>6500</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>6100</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>6300</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>6200</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>6300</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>4600</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>2800</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>2700</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>2600</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>2800</v>
       </c>
-      <c r="V83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W83" s="3" t="s">
         <v>3</v>
       </c>
@@ -5883,14 +6081,17 @@
       <c r="Y83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z83" s="3">
-        <v>0</v>
+      <c r="Z83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AA83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5966,8 +6167,11 @@
       <c r="AA84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6043,8 +6247,11 @@
       <c r="AA85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6120,8 +6327,11 @@
       <c r="AA86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6197,8 +6407,11 @@
       <c r="AA87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6274,85 +6487,91 @@
       <c r="AA88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-33000</v>
+      </c>
+      <c r="E89" s="3">
         <v>-2700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-30600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-51200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-62500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-41500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-96900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-86400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-104200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-50400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-83000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-62900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-70800</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-48100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-47900</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-23700</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-37500</v>
-      </c>
-      <c r="T89" s="3">
-        <v>-20900</v>
       </c>
       <c r="U89" s="3">
         <v>-20900</v>
       </c>
       <c r="V89" s="3">
+        <v>-20900</v>
+      </c>
+      <c r="W89" s="3">
         <v>-100</v>
-      </c>
-      <c r="W89" s="3">
-        <v>-300</v>
       </c>
       <c r="X89" s="3">
         <v>-300</v>
       </c>
       <c r="Y89" s="3">
+        <v>-300</v>
+      </c>
+      <c r="Z89" s="3">
         <v>-700</v>
       </c>
-      <c r="Z89" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA89" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AA89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6380,68 +6599,69 @@
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
-    </row>
-    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB90" s="3"/>
+    </row>
+    <row r="91" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1900</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-2800</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-3800</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-3500</v>
-      </c>
-      <c r="H91" s="3">
-        <v>-4800</v>
       </c>
       <c r="I91" s="3">
         <v>-4800</v>
       </c>
       <c r="J91" s="3">
+        <v>-4800</v>
+      </c>
+      <c r="K91" s="3">
         <v>-4000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-5800</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-4400</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-5300</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-5700</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-3200</v>
-      </c>
-      <c r="P91" s="3">
-        <v>-4300</v>
       </c>
       <c r="Q91" s="3">
         <v>-4300</v>
       </c>
       <c r="R91" s="3">
+        <v>-4300</v>
+      </c>
+      <c r="S91" s="3">
         <v>-3700</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-4100</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-2600</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-3000</v>
       </c>
-      <c r="V91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W91" s="3" t="s">
         <v>3</v>
       </c>
@@ -6451,14 +6671,17 @@
       <c r="Y91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z91" s="3">
-        <v>0</v>
+      <c r="Z91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AA91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6534,8 +6757,11 @@
       <c r="AA92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6611,76 +6837,79 @@
       <c r="AA93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="E94" s="3">
         <v>-1900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-2800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-3800</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-3500</v>
-      </c>
-      <c r="H94" s="3">
-        <v>-4800</v>
       </c>
       <c r="I94" s="3">
         <v>-4800</v>
       </c>
       <c r="J94" s="3">
+        <v>-4800</v>
+      </c>
+      <c r="K94" s="3">
         <v>-4000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>99200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>100600</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>69700</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-290500</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-5900</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-4300</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-209600</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-3700</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-4100</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-2600</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-3000</v>
       </c>
-      <c r="V94" s="3">
-        <v>0</v>
-      </c>
       <c r="W94" s="3">
+        <v>0</v>
+      </c>
+      <c r="X94" s="3">
         <v>100</v>
       </c>
-      <c r="X94" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y94" s="3" t="s">
-        <v>3</v>
+      <c r="Y94" s="3">
+        <v>0</v>
       </c>
       <c r="Z94" s="3" t="s">
         <v>3</v>
@@ -6688,8 +6917,11 @@
       <c r="AA94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6717,8 +6949,9 @@
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
-    </row>
-    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB95" s="3"/>
+    </row>
+    <row r="96" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6746,8 +6979,8 @@
       <c r="K96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="L96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -6794,8 +7027,11 @@
       <c r="AA96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6871,8 +7107,11 @@
       <c r="AA97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6948,8 +7187,11 @@
       <c r="AA98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7025,144 +7267,150 @@
       <c r="AA99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E100" s="3">
         <v>12100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>9500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>5900</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>1000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>5800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>236700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>40300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>23800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>54900</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>14400</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>500</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>303100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>2500</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>5600</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>35600</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>506000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>200</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>3400</v>
       </c>
-      <c r="V100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X100" s="3">
+      <c r="X100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y100" s="3">
         <v>-100</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>315500</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>100</v>
       </c>
-      <c r="AA100" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E101" s="3">
         <v>800</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-1500</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>300</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>500</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>800</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-500</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-100</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-1000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>800</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-500</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-100</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-1000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-300</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-700</v>
       </c>
-      <c r="R101" s="3">
-        <v>0</v>
-      </c>
       <c r="S101" s="3">
         <v>0</v>
       </c>
       <c r="T101" s="3">
+        <v>0</v>
+      </c>
+      <c r="U101" s="3">
         <v>100</v>
       </c>
-      <c r="U101" s="3">
-        <v>0</v>
-      </c>
-      <c r="V101" s="3" t="s">
-        <v>3</v>
+      <c r="V101" s="3">
+        <v>0</v>
       </c>
       <c r="W101" s="3" t="s">
         <v>3</v>
@@ -7173,87 +7421,93 @@
       <c r="Y101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z101" s="3">
-        <v>0</v>
+      <c r="Z101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AA101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-28600</v>
+      </c>
+      <c r="E102" s="3">
         <v>5200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-23900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-48600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-65600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-39600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>133500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-49800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>19200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>105900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-352900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>225300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-50300</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-252600</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>8300</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>464300</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-23200</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-20400</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-100</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-200</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-400</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>800</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>100</v>
       </c>
-      <c r="AA102" s="3" t="s">
+      <c r="AB102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/CHPT_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CHPT_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="92">
   <si>
     <t>CHPT</t>
   </si>
@@ -656,195 +656,199 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AC102"/>
+  <dimension ref="A5:AD102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45961</v>
+      </c>
+      <c r="E7" s="2">
         <v>45869</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45777</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45688</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45596</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45504</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45412</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45322</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45230</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45138</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45046</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44957</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44865</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44773</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44681</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44592</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44500</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44408</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44316</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44227</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44135</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44012</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43921</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43830</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43738</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43646</v>
       </c>
-      <c r="AC7" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>105700</v>
+      </c>
+      <c r="E8" s="3">
         <v>98600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>97600</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>101900</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>99600</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>108500</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>107000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>115800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>110300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>150500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>130000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>152800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>125300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>108300</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>81600</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>79300</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>65000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>56100</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>40500</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>42400</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>36400</v>
       </c>
-      <c r="X8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y8" s="3" t="s">
         <v>3</v>
       </c>
@@ -854,80 +858,83 @@
       <c r="AA8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AB8" s="3">
-        <v>0</v>
+      <c r="AB8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AC8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>73200</v>
+      </c>
+      <c r="E9" s="3">
         <v>67900</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>69700</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>73200</v>
       </c>
-      <c r="G9" s="3">
-        <v>75900</v>
-      </c>
       <c r="H9" s="3">
+        <v>76800</v>
+      </c>
+      <c r="I9" s="3">
         <v>83000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>83400</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>91800</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>134200</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>149400</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>99500</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>119800</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>102700</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>90100</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>69500</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>61900</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>49000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>45300</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>31300</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>33500</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>29100</v>
       </c>
-      <c r="X9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y9" s="3" t="s">
         <v>3</v>
       </c>
@@ -943,74 +950,77 @@
       <c r="AC9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>32500</v>
+      </c>
+      <c r="E10" s="3">
         <v>30700</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>28000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>28700</v>
       </c>
-      <c r="G10" s="3">
-        <v>23700</v>
-      </c>
       <c r="H10" s="3">
+        <v>22800</v>
+      </c>
+      <c r="I10" s="3">
         <v>25600</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>23600</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>24000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>-23900</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1100</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>30500</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>33000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>22600</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>18200</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>12100</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>17400</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>16000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>10800</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>9200</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>8900</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>7300</v>
       </c>
-      <c r="X10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y10" s="3" t="s">
         <v>3</v>
       </c>
@@ -1026,8 +1036,11 @@
       <c r="AC10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1057,74 +1070,75 @@
       <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
-    </row>
-    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD11" s="3"/>
+    </row>
+    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>34700</v>
+      </c>
+      <c r="E12" s="3">
         <v>36500</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>33500</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>30400</v>
       </c>
-      <c r="G12" s="3">
-        <v>35400</v>
-      </c>
       <c r="H12" s="3">
+        <v>38300</v>
+      </c>
+      <c r="I12" s="3">
         <v>36500</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>36100</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>43500</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>56500</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>59600</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>49400</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>46700</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>48100</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>51800</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>48300</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>42500</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>36800</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>40400</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>25400</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>20900</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>18900</v>
       </c>
-      <c r="X12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1140,8 +1154,11 @@
       <c r="AC12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1223,8 +1240,11 @@
       <c r="AC13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1234,11 +1254,11 @@
       <c r="E14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F14" s="3">
-        <v>0</v>
+      <c r="F14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G14" s="3">
-        <v>9800</v>
+        <v>0</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>3</v>
@@ -1246,12 +1266,12 @@
       <c r="I14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J14" s="3">
+      <c r="J14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K14" s="3">
         <v>28300</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1270,15 +1290,15 @@
       <c r="Q14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R14" s="3">
+      <c r="R14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S14" s="3">
         <v>200</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>4800</v>
       </c>
-      <c r="T14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1291,8 +1311,8 @@
       <c r="X14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y14" s="3">
-        <v>0</v>
+      <c r="Y14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Z14" s="3">
         <v>0</v>
@@ -1306,44 +1326,47 @@
       <c r="AC14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>6900</v>
+        <v>6700</v>
       </c>
       <c r="E15" s="3">
         <v>6900</v>
       </c>
       <c r="F15" s="3">
+        <v>6900</v>
+      </c>
+      <c r="G15" s="3">
         <v>7000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>7300</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>7500</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>7400</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>7300</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>7100</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>7000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>7100</v>
       </c>
-      <c r="N15" s="3">
-        <v>0</v>
-      </c>
       <c r="O15" s="3">
         <v>0</v>
       </c>
@@ -1389,8 +1412,11 @@
       <c r="AC15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1417,157 +1443,161 @@
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
-    </row>
-    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD16" s="3"/>
+    </row>
+    <row r="17" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>150000</v>
+      </c>
+      <c r="E17" s="3">
         <v>157600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>151500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>156800</v>
       </c>
-      <c r="G17" s="3">
-        <v>158000</v>
-      </c>
       <c r="H17" s="3">
+        <v>167800</v>
+      </c>
+      <c r="I17" s="3">
         <v>171300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>174200</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>180500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>264100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>273800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>210000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>231100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>208600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>198700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>171500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>158600</v>
-      </c>
-      <c r="S17" s="3">
-        <v>130400</v>
       </c>
       <c r="T17" s="3">
         <v>130400</v>
       </c>
       <c r="U17" s="3">
+        <v>130400</v>
+      </c>
+      <c r="V17" s="3">
         <v>87100</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>77700</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>69000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>200</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>300</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>1600</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>600</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>100</v>
       </c>
-      <c r="AC17" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-44300</v>
+      </c>
+      <c r="E18" s="3">
         <v>-59000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-53800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-54900</v>
       </c>
-      <c r="G18" s="3">
-        <v>-58300</v>
-      </c>
       <c r="H18" s="3">
+        <v>-68200</v>
+      </c>
+      <c r="I18" s="3">
         <v>-62700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-67100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-64700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-153800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-123300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-79900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-78300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-83300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-90400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-89900</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-79300</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-65400</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-74300</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-46600</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-35300</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-32600</v>
       </c>
-      <c r="X18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1577,14 +1607,17 @@
       <c r="AA18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AB18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC18" s="3">
         <v>-100</v>
       </c>
-      <c r="AC18" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1614,8 +1647,9 @@
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
-    </row>
-    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD19" s="3"/>
+    </row>
+    <row r="20" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1623,65 +1657,65 @@
         <v>300</v>
       </c>
       <c r="E20" s="3">
+        <v>300</v>
+      </c>
+      <c r="F20" s="3">
         <v>-2600</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>2300</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>200</v>
       </c>
-      <c r="H20" s="3">
-        <v>0</v>
-      </c>
       <c r="I20" s="3">
+        <v>0</v>
+      </c>
+      <c r="J20" s="3">
         <v>900</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-1200</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>2800</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-100</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-600</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>3200</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>1000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>200</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-300</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>16400</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-4400</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-10600</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>130400</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-54600</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-7400</v>
       </c>
-      <c r="X20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1691,80 +1725,83 @@
       <c r="AA20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AB20" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC20" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AB20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-37900</v>
+      </c>
+      <c r="E21" s="3">
         <v>-52400</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-44300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-50300</v>
       </c>
-      <c r="G21" s="3">
-        <v>-51200</v>
-      </c>
       <c r="H21" s="3">
+        <v>-61100</v>
+      </c>
+      <c r="I21" s="3">
         <v>-55300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-60500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-56200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-149400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-116300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-72300</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-68700</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-76200</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-83900</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-84000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-56600</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-65200</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-82000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>86600</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-87300</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-37200</v>
       </c>
-      <c r="X21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1780,25 +1817,28 @@
       <c r="AC21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>8100</v>
+      </c>
+      <c r="E22" s="3">
         <v>6800</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>6400</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>2200</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>9300</v>
-      </c>
-      <c r="H22" s="3">
-        <v>6600</v>
       </c>
       <c r="I22" s="3">
         <v>6600</v>
@@ -1807,29 +1847,29 @@
         <v>6600</v>
       </c>
       <c r="K22" s="3">
+        <v>6600</v>
+      </c>
+      <c r="L22" s="3">
         <v>3800</v>
-      </c>
-      <c r="L22" s="3">
-        <v>2900</v>
       </c>
       <c r="M22" s="3">
         <v>2900</v>
       </c>
       <c r="N22" s="3">
+        <v>2900</v>
+      </c>
+      <c r="O22" s="3">
         <v>3000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>2600</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>2900</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>900</v>
       </c>
-      <c r="R22" s="3">
-        <v>0</v>
-      </c>
       <c r="S22" s="3">
         <v>0</v>
       </c>
@@ -1837,16 +1877,16 @@
         <v>0</v>
       </c>
       <c r="U22" s="3">
+        <v>0</v>
+      </c>
+      <c r="V22" s="3">
         <v>1500</v>
-      </c>
-      <c r="V22" s="3">
-        <v>800</v>
       </c>
       <c r="W22" s="3">
         <v>800</v>
       </c>
-      <c r="X22" s="3" t="s">
-        <v>3</v>
+      <c r="X22" s="3">
+        <v>800</v>
       </c>
       <c r="Y22" s="3" t="s">
         <v>3</v>
@@ -1857,180 +1897,189 @@
       <c r="AA22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AB22" s="3">
-        <v>0</v>
+      <c r="AB22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AC22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-51600</v>
+      </c>
+      <c r="E23" s="3">
         <v>-65000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-56500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-58000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-76100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-67200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-71400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-94900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-158500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-124400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-79800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-78100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-84900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-93100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-91100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-62900</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-69800</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-84900</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>82300</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-90800</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-40800</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-100</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>700</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-400</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>400</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-100</v>
       </c>
-      <c r="AC23" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>900</v>
+      </c>
+      <c r="E24" s="3">
         <v>1200</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>600</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>800</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>1500</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>1600</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>400</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-200</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-300</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>900</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-400</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>500</v>
-      </c>
-      <c r="O24" s="3">
-        <v>-400</v>
       </c>
       <c r="P24" s="3">
         <v>-400</v>
       </c>
       <c r="Q24" s="3">
+        <v>-400</v>
+      </c>
+      <c r="R24" s="3">
         <v>-1900</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-2700</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-300</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>100</v>
       </c>
-      <c r="U24" s="3">
-        <v>0</v>
-      </c>
       <c r="V24" s="3">
         <v>0</v>
       </c>
       <c r="W24" s="3">
+        <v>0</v>
+      </c>
+      <c r="X24" s="3">
         <v>100</v>
       </c>
-      <c r="X24" s="3">
-        <v>0</v>
-      </c>
       <c r="Y24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z24" s="3">
         <v>200</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>300</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>200</v>
       </c>
-      <c r="AB24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2112,174 +2161,183 @@
       <c r="AC25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-52500</v>
+      </c>
+      <c r="E26" s="3">
         <v>-66200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-57100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-58800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-77600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-68900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-71800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-94700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-158200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-125300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-79400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-78700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-84500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-92700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-89300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-60100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-69400</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-84900</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>82300</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-90700</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-40900</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-100</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>500</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-600</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>200</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-100</v>
       </c>
-      <c r="AC26" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-52500</v>
+      </c>
+      <c r="E27" s="3">
         <v>-66200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-57100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-58800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-77600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-68900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-71800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-94700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-158200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-125300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-79400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-78700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-84500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-92700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-89300</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-60100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-69400</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-84900</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-84500</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-103600</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-46600</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-100</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>500</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-600</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>200</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-100</v>
       </c>
-      <c r="AC27" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2361,8 +2419,11 @@
       <c r="AC28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2444,8 +2505,11 @@
       <c r="AC29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2527,8 +2591,11 @@
       <c r="AC30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2610,8 +2677,11 @@
       <c r="AC31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2619,65 +2689,65 @@
         <v>-300</v>
       </c>
       <c r="E32" s="3">
+        <v>-300</v>
+      </c>
+      <c r="F32" s="3">
         <v>2600</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-2300</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-200</v>
       </c>
-      <c r="H32" s="3">
-        <v>0</v>
-      </c>
       <c r="I32" s="3">
+        <v>0</v>
+      </c>
+      <c r="J32" s="3">
         <v>-900</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>1200</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-2800</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>100</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>600</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-3200</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-1000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-200</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>300</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-16400</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>4400</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>10600</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-130400</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>54600</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>7400</v>
       </c>
-      <c r="X32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2687,97 +2757,103 @@
       <c r="AA32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AB32" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC32" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AB32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-52500</v>
+      </c>
+      <c r="E33" s="3">
         <v>-66200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-57100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-58800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-77600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-68900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-71800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-94700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-158200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-125300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-79400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-78700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-84500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-92700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-89300</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-60100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-69400</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-84900</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-84500</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-103600</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-46600</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-100</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>500</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-600</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>200</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-100</v>
       </c>
-      <c r="AC33" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2859,179 +2935,188 @@
       <c r="AC34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-52500</v>
+      </c>
+      <c r="E35" s="3">
         <v>-66200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-57100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-58800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-77600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-68900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-71800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-94700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-158200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-125300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-79400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-78700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-84500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-92700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-89300</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-60100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-69400</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-84900</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-84500</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-103600</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-46600</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-100</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>500</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-600</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>200</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-100</v>
       </c>
-      <c r="AC35" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45961</v>
+      </c>
+      <c r="E38" s="2">
         <v>45869</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45777</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45688</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45596</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45504</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45412</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45322</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45230</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45138</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45046</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44957</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44865</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44773</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44681</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44592</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44500</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44408</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44316</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44227</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44135</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44012</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43921</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43830</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43738</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43646</v>
       </c>
-      <c r="AC38" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3061,8 +3146,9 @@
       <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
       <c r="AC39" s="3"/>
-    </row>
-    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD39" s="3"/>
+    </row>
+    <row r="40" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3092,91 +3178,95 @@
       <c r="AA40" s="3"/>
       <c r="AB40" s="3"/>
       <c r="AC40" s="3"/>
-    </row>
-    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD40" s="3"/>
+    </row>
+    <row r="41" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>180500</v>
+      </c>
+      <c r="E41" s="3">
         <v>194100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>195900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>224600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>219400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>243300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>261900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>327400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>367000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>233500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>283300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>264200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>188300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>187700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>540600</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>315200</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>365500</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>618100</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>609800</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>145500</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>168700</v>
       </c>
-      <c r="X41" s="3">
-        <v>0</v>
-      </c>
       <c r="Y41" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z41" s="3">
         <v>200</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>400</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>800</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>100</v>
       </c>
-      <c r="AC41" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3211,17 +3301,17 @@
         <v>0</v>
       </c>
       <c r="N42" s="3">
+        <v>0</v>
+      </c>
+      <c r="O42" s="3">
         <v>105000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>208900</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>283900</v>
       </c>
-      <c r="Q42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R42" s="3" t="s">
         <v>3</v>
       </c>
@@ -3237,8 +3327,8 @@
       <c r="V42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W42" s="3">
-        <v>0</v>
+      <c r="W42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X42" s="3">
         <v>0</v>
@@ -3258,74 +3348,77 @@
       <c r="AC42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>97100</v>
+      </c>
+      <c r="E43" s="3">
         <v>96000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>98700</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>95900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>111900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>111500</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>117800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>124000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>151800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>202100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>165100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>164900</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>123000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>109900</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>79900</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>75900</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>66100</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>42700</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>34900</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>35100</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>28300</v>
       </c>
-      <c r="X43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3335,80 +3428,83 @@
       <c r="AA43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AB43" s="3">
-        <v>0</v>
+      <c r="AB43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AC43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>212400</v>
+        <v>212200</v>
       </c>
       <c r="E44" s="3">
         <v>212400</v>
       </c>
       <c r="F44" s="3">
+        <v>212400</v>
+      </c>
+      <c r="G44" s="3">
         <v>209300</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>222000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>228500</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>223600</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>198600</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>199100</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>143600</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>115200</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>68700</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>62400</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>53400</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>45300</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>35900</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>29900</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>27900</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>28900</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>33600</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>30700</v>
       </c>
-      <c r="X44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y44" s="3" t="s">
         <v>3</v>
       </c>
@@ -3418,180 +3514,189 @@
       <c r="AA44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AB44" s="3">
-        <v>0</v>
+      <c r="AB44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AC44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>18400</v>
+      </c>
+      <c r="E45" s="3">
         <v>19500</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>26900</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>3200</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>25400</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>22300</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>18700</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>3000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>25500</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>24700</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>23600</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>101400</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>59000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>45300</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>46500</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>37000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>33100</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>22500</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>20300</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>12500</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>15200</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>200</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>300</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>400</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>300</v>
       </c>
-      <c r="AB45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>516100</v>
+      </c>
+      <c r="E46" s="3">
         <v>533400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>554300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>566600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>620100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>652900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>698300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>742700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>824400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>692200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>682200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>704200</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>641600</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>680200</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>712200</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>464100</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>494600</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>711300</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>693900</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>226600</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>242900</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>300</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>500</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>800</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>1100</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>100</v>
       </c>
-      <c r="AC46" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3625,8 +3730,8 @@
       <c r="M47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N47" s="3">
-        <v>0</v>
+      <c r="N47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O47" s="3">
         <v>0</v>
@@ -3656,91 +3761,94 @@
         <v>0</v>
       </c>
       <c r="X47" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y47" s="3">
         <v>317400</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>317300</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>316400</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>315100</v>
       </c>
-      <c r="AB47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>39300</v>
+      </c>
+      <c r="E48" s="3">
         <v>42900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>46800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>50000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>52700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>54900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>55600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>57800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>60300</v>
-      </c>
-      <c r="L48" s="3">
-        <v>62900</v>
       </c>
       <c r="M48" s="3">
         <v>62900</v>
       </c>
       <c r="N48" s="3">
+        <v>62900</v>
+      </c>
+      <c r="O48" s="3">
         <v>62300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>60600</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>59300</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>59200</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>60100</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>58300</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>53100</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>53000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>51800</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>50800</v>
       </c>
-      <c r="X48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3750,67 +3858,70 @@
       <c r="AA48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AB48" s="3">
-        <v>0</v>
+      <c r="AB48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AC48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>286700</v>
+      </c>
+      <c r="E49" s="3">
         <v>287300</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>289100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>273700</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>286000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>288200</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>289300</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>294300</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>294200</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>304500</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>307500</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>306400</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>291400</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>300100</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>309600</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>325700</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>343200</v>
-      </c>
-      <c r="T49" s="3">
-        <v>1200</v>
       </c>
       <c r="U49" s="3">
         <v>1200</v>
@@ -3821,8 +3932,8 @@
       <c r="W49" s="3">
         <v>1200</v>
       </c>
-      <c r="X49" s="3" t="s">
-        <v>3</v>
+      <c r="X49" s="3">
+        <v>1200</v>
       </c>
       <c r="Y49" s="3" t="s">
         <v>3</v>
@@ -3833,14 +3944,17 @@
       <c r="AA49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AB49" s="3">
-        <v>0</v>
+      <c r="AB49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AC49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3922,8 +4036,11 @@
       <c r="AC50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4005,91 +4122,97 @@
       <c r="AC51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>5900</v>
+      </c>
+      <c r="E52" s="3">
         <v>6700</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>7300</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>1700</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>7600</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>7700</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>8000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>2600</v>
-      </c>
-      <c r="K52" s="3">
-        <v>8700</v>
       </c>
       <c r="L52" s="3">
         <v>8700</v>
       </c>
       <c r="M52" s="3">
+        <v>8700</v>
+      </c>
+      <c r="N52" s="3">
         <v>7300</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>7100</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>7000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>6500</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>6300</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>6000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>5300</v>
-      </c>
-      <c r="T52" s="3">
-        <v>5000</v>
       </c>
       <c r="U52" s="3">
         <v>5000</v>
       </c>
       <c r="V52" s="3">
+        <v>5000</v>
+      </c>
+      <c r="W52" s="3">
         <v>10500</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>4300</v>
       </c>
-      <c r="X52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="Z52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA52" s="3">
         <v>316400</v>
       </c>
-      <c r="AA52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AB52" s="3">
+      <c r="AB52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC52" s="3">
         <v>300</v>
       </c>
-      <c r="AC52" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4171,91 +4294,97 @@
       <c r="AC53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>848000</v>
+      </c>
+      <c r="E54" s="3">
         <v>870300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>897600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>898200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>966300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1003800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1051200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1103400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1187700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1068400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1059800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1080000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1000600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1046000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1087300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>855900</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>901500</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>770600</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>753100</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>290100</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>299300</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>317700</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>317800</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>317200</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>316200</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>400</v>
       </c>
-      <c r="AC54" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4285,8 +4414,9 @@
       <c r="AA55" s="3"/>
       <c r="AB55" s="3"/>
       <c r="AC55" s="3"/>
-    </row>
-    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD55" s="3"/>
+    </row>
+    <row r="56" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4316,126 +4446,130 @@
       <c r="AA56" s="3"/>
       <c r="AB56" s="3"/>
       <c r="AC56" s="3"/>
-    </row>
-    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD56" s="3"/>
+    </row>
+    <row r="57" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>69300</v>
+      </c>
+      <c r="E57" s="3">
         <v>72500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>52200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>64100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>74100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>71400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>84100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>71100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>101700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>99000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>62000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>62100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>44500</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>45100</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>35400</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>27600</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>32100</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>28400</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>18100</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>19800</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>16700</v>
-      </c>
-      <c r="X57" s="3">
-        <v>100</v>
       </c>
       <c r="Y57" s="3">
         <v>100</v>
       </c>
       <c r="Z57" s="3">
+        <v>100</v>
+      </c>
+      <c r="AA57" s="3">
         <v>200</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>100</v>
       </c>
-      <c r="AB57" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC57" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AC57" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>5000</v>
+      </c>
+      <c r="E58" s="3">
         <v>4900</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>4800</v>
-      </c>
-      <c r="F58" s="3">
-        <v>4600</v>
       </c>
       <c r="G58" s="3">
         <v>4600</v>
       </c>
       <c r="H58" s="3">
+        <v>4600</v>
+      </c>
+      <c r="I58" s="3">
         <v>4400</v>
-      </c>
-      <c r="I58" s="3">
-        <v>4500</v>
       </c>
       <c r="J58" s="3">
         <v>4500</v>
       </c>
       <c r="K58" s="3">
+        <v>4500</v>
+      </c>
+      <c r="L58" s="3">
         <v>4400</v>
-      </c>
-      <c r="L58" s="3">
-        <v>4300</v>
       </c>
       <c r="M58" s="3">
         <v>4300</v>
       </c>
       <c r="N58" s="3">
-        <v>0</v>
+        <v>4300</v>
       </c>
       <c r="O58" s="3">
         <v>0</v>
@@ -4459,245 +4593,254 @@
         <v>0</v>
       </c>
       <c r="V58" s="3">
+        <v>0</v>
+      </c>
+      <c r="W58" s="3">
         <v>10200</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>5800</v>
       </c>
-      <c r="X58" s="3">
-        <v>0</v>
-      </c>
       <c r="Y58" s="3">
         <v>0</v>
       </c>
       <c r="Z58" s="3">
         <v>0</v>
       </c>
-      <c r="AA58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AB58" s="3">
+      <c r="AA58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC58" s="3">
         <v>100</v>
       </c>
-      <c r="AC58" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>200300</v>
+      </c>
+      <c r="E59" s="3">
         <v>191800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>188000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>175800</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>189300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>195000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>185100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>187200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>176100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>156600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>144300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>222300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>193800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>193600</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>177500</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>161500</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>135400</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>99700</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>86800</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>88100</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>76700</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>900</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>800</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>600</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>400</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>300</v>
       </c>
-      <c r="AC59" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>325500</v>
+      </c>
+      <c r="E60" s="3">
         <v>320000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>304400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>293700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>320000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>321000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>327800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>330200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>352600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>340500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>288400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>284300</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>238400</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>238800</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>212800</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>189000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>167400</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>128200</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>104900</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>118100</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>99300</v>
-      </c>
-      <c r="X60" s="3">
-        <v>1000</v>
       </c>
       <c r="Y60" s="3">
         <v>1000</v>
       </c>
       <c r="Z60" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AA60" s="3">
         <v>800</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>500</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>400</v>
       </c>
-      <c r="AC60" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>333700</v>
+      </c>
+      <c r="E61" s="3">
         <v>322600</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>322200</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>312400</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>315400</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>302800</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>301000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>301100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>301200</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>315100</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>315900</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>294900</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>294600</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>294300</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>294100</v>
       </c>
-      <c r="R61" s="3">
-        <v>0</v>
-      </c>
       <c r="S61" s="3">
         <v>0</v>
       </c>
@@ -4708,14 +4851,14 @@
         <v>0</v>
       </c>
       <c r="V61" s="3">
+        <v>0</v>
+      </c>
+      <c r="W61" s="3">
         <v>24700</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>28900</v>
       </c>
-      <c r="X61" s="3">
-        <v>0</v>
-      </c>
       <c r="Y61" s="3">
         <v>0</v>
       </c>
@@ -4731,91 +4874,97 @@
       <c r="AC61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>5400</v>
+      </c>
+      <c r="E62" s="3">
         <v>9500</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>4000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>8400</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>5500</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>1500</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>1600</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>1800</v>
-      </c>
-      <c r="K62" s="3">
-        <v>1600</v>
       </c>
       <c r="L62" s="3">
         <v>1600</v>
       </c>
       <c r="M62" s="3">
+        <v>1600</v>
+      </c>
+      <c r="N62" s="3">
         <v>1300</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>145700</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>129000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>121200</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>115300</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>119800</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>148600</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>107400</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>163800</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>148200</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>86300</v>
-      </c>
-      <c r="X62" s="3">
-        <v>10900</v>
       </c>
       <c r="Y62" s="3">
         <v>10900</v>
       </c>
       <c r="Z62" s="3">
+        <v>10900</v>
+      </c>
+      <c r="AA62" s="3">
         <v>20500</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>10900</v>
       </c>
-      <c r="AB62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4897,8 +5046,11 @@
       <c r="AC63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4980,8 +5132,11 @@
       <c r="AC64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5063,91 +5218,97 @@
       <c r="AC65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>809700</v>
+      </c>
+      <c r="E66" s="3">
         <v>799500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>779000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>760700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>785400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>772900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>773300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>775700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>795100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>793200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>732300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>725000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>662000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>654300</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>622200</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>308900</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>316100</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>235600</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>268700</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>290900</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>214500</v>
-      </c>
-      <c r="X66" s="3">
-        <v>11900</v>
       </c>
       <c r="Y66" s="3">
         <v>11900</v>
       </c>
       <c r="Z66" s="3">
+        <v>11900</v>
+      </c>
+      <c r="AA66" s="3">
         <v>21300</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>11400</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>400</v>
       </c>
-      <c r="AC66" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5177,8 +5338,9 @@
       <c r="AA67" s="3"/>
       <c r="AB67" s="3"/>
       <c r="AC67" s="3"/>
-    </row>
-    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD67" s="3"/>
+    </row>
+    <row r="68" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5260,8 +5422,11 @@
       <c r="AC68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5343,8 +5508,11 @@
       <c r="AC69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5403,14 +5571,14 @@
         <v>0</v>
       </c>
       <c r="V70" s="3">
+        <v>0</v>
+      </c>
+      <c r="W70" s="3">
         <v>615700</v>
       </c>
-      <c r="W70" s="3">
+      <c r="X70" s="3">
         <v>615800</v>
       </c>
-      <c r="X70" s="3">
-        <v>0</v>
-      </c>
       <c r="Y70" s="3">
         <v>0</v>
       </c>
@@ -5426,8 +5594,11 @@
       <c r="AC70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5509,91 +5680,97 @@
       <c r="AC71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-2067200</v>
+      </c>
+      <c r="E72" s="3">
         <v>-2014700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-1948600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-1891400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-1832600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-1755000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-1686200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-1614400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-1519600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-1361400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-1236200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-1156800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-1078100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-993600</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-900900</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-811700</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-751500</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-682100</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-597100</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>200</v>
       </c>
-      <c r="W72" s="3">
-        <v>0</v>
-      </c>
       <c r="X72" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y72" s="3">
         <v>1100</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>1200</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>300</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>100</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-100</v>
       </c>
-      <c r="AC72" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5675,8 +5852,11 @@
       <c r="AC73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5758,8 +5938,11 @@
       <c r="AC74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5841,91 +6024,97 @@
       <c r="AC75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>38400</v>
+      </c>
+      <c r="E76" s="3">
         <v>70700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>118600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>137500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>181000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>230900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>277900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>327700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>392600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>275200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>327500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>355000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>338600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>391700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>465100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>547000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>585400</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>535000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>484300</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>-616500</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>-531000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>305800</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>305900</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>295900</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>304800</v>
       </c>
-      <c r="AB76" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC76" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AC76" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6007,179 +6196,188 @@
       <c r="AC77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45961</v>
+      </c>
+      <c r="E80" s="2">
         <v>45869</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45777</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45688</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45596</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45504</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45412</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45322</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45230</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45138</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45046</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44957</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44865</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44773</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44681</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44592</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44500</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44408</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44316</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44227</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44135</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44012</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43921</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43830</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43738</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43646</v>
       </c>
-      <c r="AC80" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-52500</v>
+      </c>
+      <c r="E81" s="3">
         <v>-66200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-57100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-58800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-77600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-68900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-71800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-94700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-158200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-125300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-79400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-78700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-84500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-92700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-89300</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-60100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-69400</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-84900</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-84500</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-103600</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-46600</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-100</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>500</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-600</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>200</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-100</v>
       </c>
-      <c r="AC81" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6209,74 +6407,75 @@
       <c r="AA82" s="3"/>
       <c r="AB82" s="3"/>
       <c r="AC82" s="3"/>
-    </row>
-    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD82" s="3"/>
+    </row>
+    <row r="83" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>4400</v>
+        <v>4200</v>
       </c>
       <c r="E83" s="3">
         <v>4400</v>
       </c>
       <c r="F83" s="3">
+        <v>4400</v>
+      </c>
+      <c r="G83" s="3">
         <v>4300</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>4100</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>3900</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>4000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>3500</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>3200</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>3300</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>3400</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>6500</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>6100</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>6300</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>6200</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>6300</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>4600</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>2800</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>2700</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>2600</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>2800</v>
       </c>
-      <c r="X83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y83" s="3" t="s">
         <v>3</v>
       </c>
@@ -6286,14 +6485,17 @@
       <c r="AA83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AB83" s="3">
-        <v>0</v>
+      <c r="AB83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AC83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6375,8 +6577,11 @@
       <c r="AC84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6458,8 +6663,11 @@
       <c r="AC85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6541,8 +6749,11 @@
       <c r="AC86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6624,8 +6835,11 @@
       <c r="AC87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6707,91 +6921,97 @@
       <c r="AC88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-22500</v>
+      </c>
+      <c r="E89" s="3">
         <v>-6200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-33000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-2700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-30600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-51200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-62500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-41500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-96900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-86400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-104200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-50400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-83000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-62900</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-70800</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-48100</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-47900</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-23700</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-37500</v>
-      </c>
-      <c r="V89" s="3">
-        <v>-20900</v>
       </c>
       <c r="W89" s="3">
         <v>-20900</v>
       </c>
       <c r="X89" s="3">
+        <v>-20900</v>
+      </c>
+      <c r="Y89" s="3">
         <v>-100</v>
-      </c>
-      <c r="Y89" s="3">
-        <v>-300</v>
       </c>
       <c r="Z89" s="3">
         <v>-300</v>
       </c>
       <c r="AA89" s="3">
+        <v>-300</v>
+      </c>
+      <c r="AB89" s="3">
         <v>-700</v>
       </c>
-      <c r="AB89" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC89" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AC89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6821,74 +7041,75 @@
       <c r="AA90" s="3"/>
       <c r="AB90" s="3"/>
       <c r="AC90" s="3"/>
-    </row>
-    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD90" s="3"/>
+    </row>
+    <row r="91" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-1100</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-1900</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-2800</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-3800</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-3500</v>
-      </c>
-      <c r="J91" s="3">
-        <v>-4800</v>
       </c>
       <c r="K91" s="3">
         <v>-4800</v>
       </c>
       <c r="L91" s="3">
+        <v>-4800</v>
+      </c>
+      <c r="M91" s="3">
         <v>-4000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-5800</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-4400</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-5300</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-5700</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-3200</v>
-      </c>
-      <c r="R91" s="3">
-        <v>-4300</v>
       </c>
       <c r="S91" s="3">
         <v>-4300</v>
       </c>
       <c r="T91" s="3">
+        <v>-4300</v>
+      </c>
+      <c r="U91" s="3">
         <v>-3700</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-4100</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-2600</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-3000</v>
       </c>
-      <c r="X91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y91" s="3" t="s">
         <v>3</v>
       </c>
@@ -6898,14 +7119,17 @@
       <c r="AA91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AB91" s="3">
-        <v>0</v>
+      <c r="AB91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AC91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6987,8 +7211,11 @@
       <c r="AC92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7070,82 +7297,85 @@
       <c r="AC93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="E94" s="3">
         <v>-1300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-1100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-1900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-2800</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-3800</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-3500</v>
-      </c>
-      <c r="J94" s="3">
-        <v>-4800</v>
       </c>
       <c r="K94" s="3">
         <v>-4800</v>
       </c>
       <c r="L94" s="3">
+        <v>-4800</v>
+      </c>
+      <c r="M94" s="3">
         <v>-4000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>99200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>100600</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>69700</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-290500</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-5900</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-4300</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-209600</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-3700</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-4100</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-2600</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-3000</v>
       </c>
-      <c r="X94" s="3">
-        <v>0</v>
-      </c>
       <c r="Y94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z94" s="3">
         <v>100</v>
       </c>
-      <c r="Z94" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA94" s="3" t="s">
-        <v>3</v>
+      <c r="AA94" s="3">
+        <v>0</v>
       </c>
       <c r="AB94" s="3" t="s">
         <v>3</v>
@@ -7153,8 +7383,11 @@
       <c r="AC94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7184,8 +7417,9 @@
       <c r="AA95" s="3"/>
       <c r="AB95" s="3"/>
       <c r="AC95" s="3"/>
-    </row>
-    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD95" s="3"/>
+    </row>
+    <row r="96" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7219,8 +7453,8 @@
       <c r="M96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N96" s="3">
-        <v>0</v>
+      <c r="N96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O96" s="3">
         <v>0</v>
@@ -7267,8 +7501,11 @@
       <c r="AC96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7350,8 +7587,11 @@
       <c r="AC97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7433,8 +7673,11 @@
       <c r="AC98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7516,156 +7759,162 @@
       <c r="AC99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>10000</v>
+      </c>
+      <c r="E100" s="3">
         <v>5700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>2400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>12100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>9500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>5900</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>1000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>5800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>236700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>40300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>23800</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>54900</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>14400</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>500</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>303100</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>2500</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>5600</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>35600</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>506000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>200</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>3400</v>
       </c>
-      <c r="X100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="Z100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA100" s="3">
         <v>-100</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>315500</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>100</v>
       </c>
-      <c r="AC100" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>100</v>
+      </c>
+      <c r="E101" s="3">
         <v>500</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-600</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>800</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-1500</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>300</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>500</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>800</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-500</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-100</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-1000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>800</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-500</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-100</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-1000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-300</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-700</v>
       </c>
-      <c r="T101" s="3">
-        <v>0</v>
-      </c>
       <c r="U101" s="3">
         <v>0</v>
       </c>
       <c r="V101" s="3">
+        <v>0</v>
+      </c>
+      <c r="W101" s="3">
         <v>100</v>
       </c>
-      <c r="W101" s="3">
-        <v>0</v>
-      </c>
-      <c r="X101" s="3" t="s">
-        <v>3</v>
+      <c r="X101" s="3">
+        <v>0</v>
       </c>
       <c r="Y101" s="3" t="s">
         <v>3</v>
@@ -7676,93 +7925,99 @@
       <c r="AA101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AB101" s="3">
-        <v>0</v>
+      <c r="AB101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AC101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-13600</v>
+      </c>
+      <c r="E102" s="3">
         <v>-1800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-28600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>5200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-23900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-48600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-65600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-39600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>133500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-49800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>19200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>105900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-352900</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>225300</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-50300</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-252600</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>8300</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>464300</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-23200</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-20400</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-100</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-200</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-400</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>800</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>100</v>
       </c>
-      <c r="AC102" s="3" t="s">
+      <c r="AD102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/CHPT_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CHPT_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="92">
   <si>
     <t>CHPT</t>
   </si>
@@ -656,202 +656,206 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AD102"/>
+  <dimension ref="A5:AE102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46053</v>
+      </c>
+      <c r="E7" s="2">
         <v>45961</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45869</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45777</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45688</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45596</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45504</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45412</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45322</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45230</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45138</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45046</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44957</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44865</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44773</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44681</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44592</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44500</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44408</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44316</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44227</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44135</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44012</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43921</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43830</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43738</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43646</v>
       </c>
-      <c r="AD7" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>109300</v>
+      </c>
+      <c r="E8" s="3">
         <v>105700</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>98600</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>97600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>101900</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>99600</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>108500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>107000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>115800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>110300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>150500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>130000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>152800</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>125300</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>108300</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>81600</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>79300</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>65000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>56100</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>40500</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>42400</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>36400</v>
       </c>
-      <c r="Y8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z8" s="3" t="s">
         <v>3</v>
       </c>
@@ -861,83 +865,86 @@
       <c r="AB8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AC8" s="3">
-        <v>0</v>
+      <c r="AC8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AD8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>74900</v>
+      </c>
+      <c r="E9" s="3">
         <v>73200</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>67900</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>69700</v>
       </c>
-      <c r="G9" s="3">
-        <v>73200</v>
-      </c>
       <c r="H9" s="3">
+        <v>72200</v>
+      </c>
+      <c r="I9" s="3">
         <v>76800</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>83000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>83400</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>91800</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>134200</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>149400</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>99500</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>119800</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>102700</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>90100</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>69500</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>61900</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>49000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>45300</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>31300</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>33500</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>29100</v>
       </c>
-      <c r="Y9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z9" s="3" t="s">
         <v>3</v>
       </c>
@@ -953,77 +960,80 @@
       <c r="AD9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>34400</v>
+      </c>
+      <c r="E10" s="3">
         <v>32500</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>30700</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>28000</v>
       </c>
-      <c r="G10" s="3">
-        <v>28700</v>
-      </c>
       <c r="H10" s="3">
+        <v>29700</v>
+      </c>
+      <c r="I10" s="3">
         <v>22800</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>25600</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>23600</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>24000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>-23900</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1100</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>30500</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>33000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>22600</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>18200</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>12100</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>17400</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>16000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>10800</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>9200</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>8900</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>7300</v>
       </c>
-      <c r="Y10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z10" s="3" t="s">
         <v>3</v>
       </c>
@@ -1039,8 +1049,11 @@
       <c r="AD10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1071,77 +1084,78 @@
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
-    </row>
-    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE11" s="3"/>
+    </row>
+    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>34600</v>
+      </c>
+      <c r="E12" s="3">
         <v>34700</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>36500</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>33500</v>
       </c>
-      <c r="G12" s="3">
-        <v>30400</v>
-      </c>
       <c r="H12" s="3">
+        <v>27500</v>
+      </c>
+      <c r="I12" s="3">
         <v>38300</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>36500</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>36100</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>43500</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>56500</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>59600</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>49400</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>46700</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>48100</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>51800</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>48300</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>42500</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>36800</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>40400</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>25400</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>20900</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>18900</v>
       </c>
-      <c r="Y12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1157,8 +1171,11 @@
       <c r="AD12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1243,13 +1260,16 @@
       <c r="AD13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>3</v>
+      <c r="D14" s="3">
+        <v>-11200</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>3</v>
@@ -1257,11 +1277,11 @@
       <c r="F14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>3</v>
+      <c r="G14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H14" s="3">
+        <v>9800</v>
       </c>
       <c r="I14" s="3" t="s">
         <v>3</v>
@@ -1269,12 +1289,12 @@
       <c r="J14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K14" s="3">
+      <c r="K14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L14" s="3">
         <v>28300</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1293,15 +1313,15 @@
       <c r="R14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S14" s="3">
+      <c r="S14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T14" s="3">
         <v>200</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>4800</v>
       </c>
-      <c r="U14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1314,8 +1334,8 @@
       <c r="Y14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z14" s="3">
-        <v>0</v>
+      <c r="Z14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AA14" s="3">
         <v>0</v>
@@ -1329,47 +1349,50 @@
       <c r="AD14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>6500</v>
+      </c>
+      <c r="E15" s="3">
         <v>6700</v>
-      </c>
-      <c r="E15" s="3">
-        <v>6900</v>
       </c>
       <c r="F15" s="3">
         <v>6900</v>
       </c>
       <c r="G15" s="3">
+        <v>6900</v>
+      </c>
+      <c r="H15" s="3">
         <v>7000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>7300</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>7500</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>7400</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>7300</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>7100</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>7000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>7100</v>
       </c>
-      <c r="O15" s="3">
-        <v>0</v>
-      </c>
       <c r="P15" s="3">
         <v>0</v>
       </c>
@@ -1415,8 +1438,11 @@
       <c r="AD15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1444,163 +1470,167 @@
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
-    </row>
-    <row r="17" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE16" s="3"/>
+    </row>
+    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>162300</v>
+      </c>
+      <c r="E17" s="3">
         <v>150000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>157600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>151500</v>
       </c>
-      <c r="G17" s="3">
-        <v>156800</v>
-      </c>
       <c r="H17" s="3">
+        <v>147000</v>
+      </c>
+      <c r="I17" s="3">
         <v>167800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>171300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>174200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>180500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>264100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>273800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>210000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>231100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>208600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>198700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>171500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>158600</v>
-      </c>
-      <c r="T17" s="3">
-        <v>130400</v>
       </c>
       <c r="U17" s="3">
         <v>130400</v>
       </c>
       <c r="V17" s="3">
+        <v>130400</v>
+      </c>
+      <c r="W17" s="3">
         <v>87100</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>77700</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>69000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>200</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>300</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>1600</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>600</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>100</v>
       </c>
-      <c r="AD17" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-53000</v>
+      </c>
+      <c r="E18" s="3">
         <v>-44300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-59000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-53800</v>
       </c>
-      <c r="G18" s="3">
-        <v>-54900</v>
-      </c>
       <c r="H18" s="3">
+        <v>-45100</v>
+      </c>
+      <c r="I18" s="3">
         <v>-68200</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-62700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-67100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-64700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-153800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-123300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-79900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-78300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-83300</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-90400</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-89900</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-79300</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-65400</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-74300</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-46600</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-35300</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-32600</v>
       </c>
-      <c r="Y18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1610,14 +1640,17 @@
       <c r="AB18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AC18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD18" s="3">
         <v>-100</v>
       </c>
-      <c r="AD18" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1648,77 +1681,78 @@
       <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
-    </row>
-    <row r="20" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE19" s="3"/>
+    </row>
+    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>300</v>
+        <v>-100</v>
       </c>
       <c r="E20" s="3">
         <v>300</v>
       </c>
       <c r="F20" s="3">
+        <v>300</v>
+      </c>
+      <c r="G20" s="3">
         <v>-2600</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>2300</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>200</v>
       </c>
-      <c r="I20" s="3">
-        <v>0</v>
-      </c>
       <c r="J20" s="3">
+        <v>0</v>
+      </c>
+      <c r="K20" s="3">
         <v>900</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-1200</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>2800</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-100</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-600</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>3200</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>1000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>200</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-300</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>16400</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-4400</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-10600</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>130400</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-54600</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-7400</v>
       </c>
-      <c r="Y20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1728,83 +1762,86 @@
       <c r="AB20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AC20" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD20" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AC20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-46400</v>
+      </c>
+      <c r="E21" s="3">
         <v>-37900</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-52400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-44300</v>
       </c>
-      <c r="G21" s="3">
-        <v>-50300</v>
-      </c>
       <c r="H21" s="3">
+        <v>-40400</v>
+      </c>
+      <c r="I21" s="3">
         <v>-61100</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-55300</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-60500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-56200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-149400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-116300</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-72300</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-68700</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-76200</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-83900</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-84000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-56600</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-65200</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-82000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>86600</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-87300</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-37200</v>
       </c>
-      <c r="Y21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1820,28 +1857,31 @@
       <c r="AD21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>2500</v>
+      </c>
+      <c r="E22" s="3">
         <v>8100</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>6800</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>6400</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>2200</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>9300</v>
-      </c>
-      <c r="I22" s="3">
-        <v>6600</v>
       </c>
       <c r="J22" s="3">
         <v>6600</v>
@@ -1850,29 +1890,29 @@
         <v>6600</v>
       </c>
       <c r="L22" s="3">
+        <v>6600</v>
+      </c>
+      <c r="M22" s="3">
         <v>3800</v>
-      </c>
-      <c r="M22" s="3">
-        <v>2900</v>
       </c>
       <c r="N22" s="3">
         <v>2900</v>
       </c>
       <c r="O22" s="3">
+        <v>2900</v>
+      </c>
+      <c r="P22" s="3">
         <v>3000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>2600</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>2900</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>900</v>
       </c>
-      <c r="S22" s="3">
-        <v>0</v>
-      </c>
       <c r="T22" s="3">
         <v>0</v>
       </c>
@@ -1880,16 +1920,16 @@
         <v>0</v>
       </c>
       <c r="V22" s="3">
+        <v>0</v>
+      </c>
+      <c r="W22" s="3">
         <v>1500</v>
-      </c>
-      <c r="W22" s="3">
-        <v>800</v>
       </c>
       <c r="X22" s="3">
         <v>800</v>
       </c>
-      <c r="Y22" s="3" t="s">
-        <v>3</v>
+      <c r="Y22" s="3">
+        <v>800</v>
       </c>
       <c r="Z22" s="3" t="s">
         <v>3</v>
@@ -1900,186 +1940,195 @@
       <c r="AB22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AC22" s="3">
-        <v>0</v>
+      <c r="AC22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AD22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-43000</v>
+      </c>
+      <c r="E23" s="3">
         <v>-51600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-65000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-56500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-58000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-76100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-67200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-71400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-94900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-158500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-124400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-79800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-78100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-84900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-93100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-91100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-62900</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-69800</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-84900</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>82300</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-90800</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-40800</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-100</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>700</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-400</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>400</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-100</v>
       </c>
-      <c r="AD23" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E24" s="3">
         <v>900</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>1200</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>600</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>800</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>1500</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>1600</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>400</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-300</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>900</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-400</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>500</v>
-      </c>
-      <c r="P24" s="3">
-        <v>-400</v>
       </c>
       <c r="Q24" s="3">
         <v>-400</v>
       </c>
       <c r="R24" s="3">
+        <v>-400</v>
+      </c>
+      <c r="S24" s="3">
         <v>-1900</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-2700</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-300</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>100</v>
       </c>
-      <c r="V24" s="3">
-        <v>0</v>
-      </c>
       <c r="W24" s="3">
         <v>0</v>
       </c>
       <c r="X24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y24" s="3">
         <v>100</v>
       </c>
-      <c r="Y24" s="3">
-        <v>0</v>
-      </c>
       <c r="Z24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA24" s="3">
         <v>200</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>300</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>200</v>
       </c>
-      <c r="AC24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2164,180 +2213,189 @@
       <c r="AD25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-44400</v>
+      </c>
+      <c r="E26" s="3">
         <v>-52500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-66200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-57100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-58800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-77600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-68900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-71800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-94700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-158200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-125300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-79400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-78700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-84500</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-92700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-89300</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-60100</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-69400</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-84900</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>82300</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-90700</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-40900</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-100</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>500</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-600</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>200</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-100</v>
       </c>
-      <c r="AD26" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-44400</v>
+      </c>
+      <c r="E27" s="3">
         <v>-52500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-66200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-57100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-58800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-77600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-68900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-71800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-94700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-158200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-125300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-79400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-78700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-84500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-92700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-89300</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-60100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-69400</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-84900</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-84500</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-103600</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-46600</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-100</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>500</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-600</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>200</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-100</v>
       </c>
-      <c r="AD27" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2422,8 +2480,11 @@
       <c r="AD28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2508,8 +2569,11 @@
       <c r="AD29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2594,8 +2658,11 @@
       <c r="AD30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2680,77 +2747,80 @@
       <c r="AD31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-300</v>
+        <v>100</v>
       </c>
       <c r="E32" s="3">
         <v>-300</v>
       </c>
       <c r="F32" s="3">
+        <v>-300</v>
+      </c>
+      <c r="G32" s="3">
         <v>2600</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-2300</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-200</v>
       </c>
-      <c r="I32" s="3">
-        <v>0</v>
-      </c>
       <c r="J32" s="3">
+        <v>0</v>
+      </c>
+      <c r="K32" s="3">
         <v>-900</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>1200</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-2800</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>100</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>600</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-3200</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-1000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-200</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>300</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-16400</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>4400</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>10600</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-130400</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>54600</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>7400</v>
       </c>
-      <c r="Y32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2760,100 +2830,106 @@
       <c r="AB32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AC32" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD32" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AC32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-44400</v>
+      </c>
+      <c r="E33" s="3">
         <v>-52500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-66200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-57100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-58800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-77600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-68900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-71800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-94700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-158200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-125300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-79400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-78700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-84500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-92700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-89300</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-60100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-69400</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-84900</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-84500</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-103600</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-46600</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-100</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>500</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-600</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>200</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-100</v>
       </c>
-      <c r="AD33" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2938,185 +3014,194 @@
       <c r="AD34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-44400</v>
+      </c>
+      <c r="E35" s="3">
         <v>-52500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-66200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-57100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-58800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-77600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-68900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-71800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-94700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-158200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-125300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-79400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-78700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-84500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-92700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-89300</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-60100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-69400</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-84900</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-84500</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-103600</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-46600</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-100</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>500</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-600</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>200</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-100</v>
       </c>
-      <c r="AD35" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46053</v>
+      </c>
+      <c r="E38" s="2">
         <v>45961</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45869</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45777</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45688</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45596</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45504</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45412</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45322</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45230</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45138</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45046</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44957</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44865</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44773</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44681</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44592</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44500</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44408</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44316</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44227</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44135</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44012</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43921</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43830</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43738</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43646</v>
       </c>
-      <c r="AD38" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3147,8 +3232,9 @@
       <c r="AB39" s="3"/>
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
-    </row>
-    <row r="40" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE39" s="3"/>
+    </row>
+    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3179,94 +3265,98 @@
       <c r="AB40" s="3"/>
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
-    </row>
-    <row r="41" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE40" s="3"/>
+    </row>
+    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>141600</v>
+      </c>
+      <c r="E41" s="3">
         <v>180500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>194100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>195900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>224600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>219400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>243300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>261900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>327400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>367000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>233500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>283300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>264200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>188300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>187700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>540600</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>315200</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>365500</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>618100</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>609800</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>145500</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>168700</v>
       </c>
-      <c r="Y41" s="3">
-        <v>0</v>
-      </c>
       <c r="Z41" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA41" s="3">
         <v>200</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>400</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>800</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>100</v>
       </c>
-      <c r="AD41" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="42" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3304,17 +3394,17 @@
         <v>0</v>
       </c>
       <c r="O42" s="3">
+        <v>0</v>
+      </c>
+      <c r="P42" s="3">
         <v>105000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>208900</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>283900</v>
       </c>
-      <c r="R42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S42" s="3" t="s">
         <v>3</v>
       </c>
@@ -3330,8 +3420,8 @@
       <c r="W42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X42" s="3">
-        <v>0</v>
+      <c r="X42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y42" s="3">
         <v>0</v>
@@ -3351,77 +3441,80 @@
       <c r="AD42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>86100</v>
+      </c>
+      <c r="E43" s="3">
         <v>97100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>96000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>98700</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>95900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>111900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>111500</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>117800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>124000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>151800</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>202100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>165100</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>164900</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>123000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>109900</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>79900</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>75900</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>66100</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>42700</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>34900</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>35100</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>28300</v>
       </c>
-      <c r="Y43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3431,83 +3524,86 @@
       <c r="AB43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AC43" s="3">
-        <v>0</v>
+      <c r="AC43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AD43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>214900</v>
+      </c>
+      <c r="E44" s="3">
         <v>212200</v>
-      </c>
-      <c r="E44" s="3">
-        <v>212400</v>
       </c>
       <c r="F44" s="3">
         <v>212400</v>
       </c>
       <c r="G44" s="3">
+        <v>212400</v>
+      </c>
+      <c r="H44" s="3">
         <v>209300</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>222000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>228500</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>223600</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>198600</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>199100</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>143600</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>115200</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>68700</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>62400</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>53400</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>45300</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>35900</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>29900</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>27900</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>28900</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>33600</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>30700</v>
       </c>
-      <c r="Y44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z44" s="3" t="s">
         <v>3</v>
       </c>
@@ -3517,186 +3613,195 @@
       <c r="AB44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AC44" s="3">
-        <v>0</v>
+      <c r="AC44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AD44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>2900</v>
+      </c>
+      <c r="E45" s="3">
         <v>18400</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>19500</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>26900</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>3200</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>25400</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>22300</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>18700</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>3000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>25500</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>24700</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>23600</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>101400</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>59000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>45300</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>46500</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>37000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>33100</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>22500</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>20300</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>12500</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>15200</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>200</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>300</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>400</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>300</v>
       </c>
-      <c r="AC45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>462000</v>
+      </c>
+      <c r="E46" s="3">
         <v>516100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>533400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>554300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>566600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>620100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>652900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>698300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>742700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>824400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>692200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>682200</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>704200</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>641600</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>680200</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>712200</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>464100</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>494600</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>711300</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>693900</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>226600</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>242900</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>300</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>500</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>800</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>1100</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>100</v>
       </c>
-      <c r="AD46" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="47" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3733,8 +3838,8 @@
       <c r="N47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O47" s="3">
-        <v>0</v>
+      <c r="O47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P47" s="3">
         <v>0</v>
@@ -3764,94 +3869,97 @@
         <v>0</v>
       </c>
       <c r="Y47" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z47" s="3">
         <v>317400</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>317300</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>316400</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>315100</v>
       </c>
-      <c r="AC47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>36100</v>
+      </c>
+      <c r="E48" s="3">
         <v>39300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>42900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>46800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>50000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>52700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>54900</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>55600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>57800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>60300</v>
-      </c>
-      <c r="M48" s="3">
-        <v>62900</v>
       </c>
       <c r="N48" s="3">
         <v>62900</v>
       </c>
       <c r="O48" s="3">
+        <v>62900</v>
+      </c>
+      <c r="P48" s="3">
         <v>62300</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>60600</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>59300</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>59200</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>60100</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>58300</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>53100</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>53000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>51800</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>50800</v>
       </c>
-      <c r="Y48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3861,70 +3969,73 @@
       <c r="AB48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AC48" s="3">
-        <v>0</v>
+      <c r="AC48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AD48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>288500</v>
+      </c>
+      <c r="E49" s="3">
         <v>286700</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>287300</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>289100</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>273700</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>286000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>288200</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>289300</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>294300</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>294200</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>304500</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>307500</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>306400</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>291400</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>300100</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>309600</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>325700</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>343200</v>
-      </c>
-      <c r="U49" s="3">
-        <v>1200</v>
       </c>
       <c r="V49" s="3">
         <v>1200</v>
@@ -3935,8 +4046,8 @@
       <c r="X49" s="3">
         <v>1200</v>
       </c>
-      <c r="Y49" s="3" t="s">
-        <v>3</v>
+      <c r="Y49" s="3">
+        <v>1200</v>
       </c>
       <c r="Z49" s="3" t="s">
         <v>3</v>
@@ -3947,14 +4058,17 @@
       <c r="AB49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AC49" s="3">
-        <v>0</v>
+      <c r="AC49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AD49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4039,8 +4153,11 @@
       <c r="AD50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4125,94 +4242,100 @@
       <c r="AD51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>900</v>
+      </c>
+      <c r="E52" s="3">
         <v>5900</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>6700</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>7300</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>1700</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>7600</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>7700</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>8000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>2600</v>
-      </c>
-      <c r="L52" s="3">
-        <v>8700</v>
       </c>
       <c r="M52" s="3">
         <v>8700</v>
       </c>
       <c r="N52" s="3">
+        <v>8700</v>
+      </c>
+      <c r="O52" s="3">
         <v>7300</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>7100</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>7000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>6500</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>6300</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>6000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>5300</v>
-      </c>
-      <c r="U52" s="3">
-        <v>5000</v>
       </c>
       <c r="V52" s="3">
         <v>5000</v>
       </c>
       <c r="W52" s="3">
+        <v>5000</v>
+      </c>
+      <c r="X52" s="3">
         <v>10500</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>4300</v>
       </c>
-      <c r="Y52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AA52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB52" s="3">
         <v>316400</v>
       </c>
-      <c r="AB52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AC52" s="3">
+      <c r="AC52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD52" s="3">
         <v>300</v>
       </c>
-      <c r="AD52" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="53" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4297,94 +4420,100 @@
       <c r="AD53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>792200</v>
+      </c>
+      <c r="E54" s="3">
         <v>848000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>870300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>897600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>898200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>966300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1003800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1051200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1103400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1187700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1068400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1059800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1080000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1000600</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1046000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1087300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>855900</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>901500</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>770600</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>753100</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>290100</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>299300</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>317700</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>317800</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>317200</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>316200</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>400</v>
       </c>
-      <c r="AD54" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="55" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4415,8 +4544,9 @@
       <c r="AB55" s="3"/>
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
-    </row>
-    <row r="56" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE55" s="3"/>
+    </row>
+    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4447,132 +4577,136 @@
       <c r="AB56" s="3"/>
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
-    </row>
-    <row r="57" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE56" s="3"/>
+    </row>
+    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>90100</v>
+      </c>
+      <c r="E57" s="3">
         <v>69300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>72500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>52200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>64100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>74100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>71400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>84100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>71100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>101700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>99000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>62000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>62100</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>44500</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>45100</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>35400</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>27600</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>32100</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>28400</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>18100</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>19800</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>16700</v>
-      </c>
-      <c r="Y57" s="3">
-        <v>100</v>
       </c>
       <c r="Z57" s="3">
         <v>100</v>
       </c>
       <c r="AA57" s="3">
+        <v>100</v>
+      </c>
+      <c r="AB57" s="3">
         <v>200</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>100</v>
       </c>
-      <c r="AC57" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD57" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="58" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AD57" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>37300</v>
+      </c>
+      <c r="E58" s="3">
         <v>5000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>4900</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>4800</v>
-      </c>
-      <c r="G58" s="3">
-        <v>4600</v>
       </c>
       <c r="H58" s="3">
         <v>4600</v>
       </c>
       <c r="I58" s="3">
+        <v>4600</v>
+      </c>
+      <c r="J58" s="3">
         <v>4400</v>
-      </c>
-      <c r="J58" s="3">
-        <v>4500</v>
       </c>
       <c r="K58" s="3">
         <v>4500</v>
       </c>
       <c r="L58" s="3">
+        <v>4500</v>
+      </c>
+      <c r="M58" s="3">
         <v>4400</v>
-      </c>
-      <c r="M58" s="3">
-        <v>4300</v>
       </c>
       <c r="N58" s="3">
         <v>4300</v>
       </c>
       <c r="O58" s="3">
-        <v>0</v>
+        <v>4300</v>
       </c>
       <c r="P58" s="3">
         <v>0</v>
@@ -4596,254 +4730,263 @@
         <v>0</v>
       </c>
       <c r="W58" s="3">
+        <v>0</v>
+      </c>
+      <c r="X58" s="3">
         <v>10200</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>5800</v>
       </c>
-      <c r="Y58" s="3">
-        <v>0</v>
-      </c>
       <c r="Z58" s="3">
         <v>0</v>
       </c>
       <c r="AA58" s="3">
         <v>0</v>
       </c>
-      <c r="AB58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AC58" s="3">
+      <c r="AB58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD58" s="3">
         <v>100</v>
       </c>
-      <c r="AD58" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="59" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>201600</v>
+      </c>
+      <c r="E59" s="3">
         <v>200300</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>191800</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>188000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>175800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>189300</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>195000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>185100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>187200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>176100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>156600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>144300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>222300</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>193800</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>193600</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>177500</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>161500</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>135400</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>99700</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>86800</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>88100</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>76700</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>900</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>800</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>600</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>400</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>300</v>
       </c>
-      <c r="AD59" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="60" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>383600</v>
+      </c>
+      <c r="E60" s="3">
         <v>325500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>320000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>304400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>293700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>320000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>321000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>327800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>330200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>352600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>340500</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>288400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>284300</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>238400</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>238800</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>212800</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>189000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>167400</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>128200</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>104900</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>118100</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>99300</v>
-      </c>
-      <c r="Y60" s="3">
-        <v>1000</v>
       </c>
       <c r="Z60" s="3">
         <v>1000</v>
       </c>
       <c r="AA60" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AB60" s="3">
         <v>800</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>500</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>400</v>
       </c>
-      <c r="AD60" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="61" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>239200</v>
+      </c>
+      <c r="E61" s="3">
         <v>333700</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>322600</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>322200</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>312400</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>315400</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>302800</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>301000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>301100</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>301200</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>315100</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>315900</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>294900</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>294600</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>294300</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>294100</v>
       </c>
-      <c r="S61" s="3">
-        <v>0</v>
-      </c>
       <c r="T61" s="3">
         <v>0</v>
       </c>
@@ -4854,14 +4997,14 @@
         <v>0</v>
       </c>
       <c r="W61" s="3">
+        <v>0</v>
+      </c>
+      <c r="X61" s="3">
         <v>24700</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>28900</v>
       </c>
-      <c r="Y61" s="3">
-        <v>0</v>
-      </c>
       <c r="Z61" s="3">
         <v>0</v>
       </c>
@@ -4877,94 +5020,100 @@
       <c r="AD61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>4000</v>
+      </c>
+      <c r="E62" s="3">
         <v>5400</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>9500</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>4000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>8400</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>5500</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>1500</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>1600</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>1800</v>
-      </c>
-      <c r="L62" s="3">
-        <v>1600</v>
       </c>
       <c r="M62" s="3">
         <v>1600</v>
       </c>
       <c r="N62" s="3">
+        <v>1600</v>
+      </c>
+      <c r="O62" s="3">
         <v>1300</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>145700</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>129000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>121200</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>115300</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>119800</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>148600</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>107400</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>163800</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>148200</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>86300</v>
-      </c>
-      <c r="Y62" s="3">
-        <v>10900</v>
       </c>
       <c r="Z62" s="3">
         <v>10900</v>
       </c>
       <c r="AA62" s="3">
+        <v>10900</v>
+      </c>
+      <c r="AB62" s="3">
         <v>20500</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>10900</v>
       </c>
-      <c r="AC62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5049,8 +5198,11 @@
       <c r="AD63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5135,8 +5287,11 @@
       <c r="AD64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5221,94 +5376,100 @@
       <c r="AD65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>770900</v>
+      </c>
+      <c r="E66" s="3">
         <v>809700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>799500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>779000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>760700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>785400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>772900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>773300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>775700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>795100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>793200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>732300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>725000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>662000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>654300</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>622200</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>308900</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>316100</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>235600</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>268700</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>290900</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>214500</v>
-      </c>
-      <c r="Y66" s="3">
-        <v>11900</v>
       </c>
       <c r="Z66" s="3">
         <v>11900</v>
       </c>
       <c r="AA66" s="3">
+        <v>11900</v>
+      </c>
+      <c r="AB66" s="3">
         <v>21300</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>11400</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>400</v>
       </c>
-      <c r="AD66" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="67" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5339,8 +5500,9 @@
       <c r="AB67" s="3"/>
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
-    </row>
-    <row r="68" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE67" s="3"/>
+    </row>
+    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5425,8 +5587,11 @@
       <c r="AD68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5511,8 +5676,11 @@
       <c r="AD69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5574,14 +5742,14 @@
         <v>0</v>
       </c>
       <c r="W70" s="3">
+        <v>0</v>
+      </c>
+      <c r="X70" s="3">
         <v>615700</v>
       </c>
-      <c r="X70" s="3">
+      <c r="Y70" s="3">
         <v>615800</v>
       </c>
-      <c r="Y70" s="3">
-        <v>0</v>
-      </c>
       <c r="Z70" s="3">
         <v>0</v>
       </c>
@@ -5597,8 +5765,11 @@
       <c r="AD70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5683,94 +5854,100 @@
       <c r="AD71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-2111600</v>
+      </c>
+      <c r="E72" s="3">
         <v>-2067200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-2014700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-1948600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-1891400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-1832600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-1755000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-1686200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-1614400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-1519600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-1361400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-1236200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-1156800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-1078100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-993600</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-900900</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-811700</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-751500</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-682100</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-597100</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>200</v>
       </c>
-      <c r="X72" s="3">
-        <v>0</v>
-      </c>
       <c r="Y72" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z72" s="3">
         <v>1100</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>1200</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>300</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>100</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-100</v>
       </c>
-      <c r="AD72" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="73" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5855,8 +6032,11 @@
       <c r="AD73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5941,8 +6121,11 @@
       <c r="AD74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6027,94 +6210,100 @@
       <c r="AD75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>21300</v>
+      </c>
+      <c r="E76" s="3">
         <v>38400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>70700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>118600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>137500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>181000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>230900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>277900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>327700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>392600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>275200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>327500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>355000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>338600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>391700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>465100</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>547000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>585400</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>535000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>484300</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>-616500</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>-531000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>305800</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>305900</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>295900</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>304800</v>
       </c>
-      <c r="AC76" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD76" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="77" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AD76" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6199,185 +6388,194 @@
       <c r="AD77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46053</v>
+      </c>
+      <c r="E80" s="2">
         <v>45961</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45869</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45777</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45688</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45596</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45504</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45412</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45322</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45230</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45138</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45046</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44957</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44865</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44773</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44681</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44592</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44500</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44408</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44316</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44227</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44135</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44012</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43921</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43830</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43738</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43646</v>
       </c>
-      <c r="AD80" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="81" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-44400</v>
+      </c>
+      <c r="E81" s="3">
         <v>-52500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-66200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-57100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-58800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-77600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-68900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-71800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-94700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-158200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-125300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-79400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-78700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-84500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-92700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-89300</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-60100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-69400</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-84900</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-84500</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-103600</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-46600</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-100</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>500</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-600</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>200</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-100</v>
       </c>
-      <c r="AD81" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="82" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6408,77 +6606,78 @@
       <c r="AB82" s="3"/>
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
-    </row>
-    <row r="83" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE82" s="3"/>
+    </row>
+    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>4000</v>
+      </c>
+      <c r="E83" s="3">
         <v>4200</v>
-      </c>
-      <c r="E83" s="3">
-        <v>4400</v>
       </c>
       <c r="F83" s="3">
         <v>4400</v>
       </c>
       <c r="G83" s="3">
+        <v>4400</v>
+      </c>
+      <c r="H83" s="3">
         <v>4300</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>4100</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>3900</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>4000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>3500</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>3200</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>3300</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>3400</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>6500</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>6100</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>6300</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>6200</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>6300</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>4600</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>2800</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>2700</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>2600</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>2800</v>
       </c>
-      <c r="Y83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z83" s="3" t="s">
         <v>3</v>
       </c>
@@ -6488,14 +6687,17 @@
       <c r="AB83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AC83" s="3">
-        <v>0</v>
+      <c r="AC83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AD83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6580,8 +6782,11 @@
       <c r="AD84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6666,8 +6871,11 @@
       <c r="AD85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6752,8 +6960,11 @@
       <c r="AD86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6838,8 +7049,11 @@
       <c r="AD87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6924,94 +7138,100 @@
       <c r="AD88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="E89" s="3">
         <v>-22500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-6200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-33000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-2700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-30600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-51200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-62500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-41500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-96900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-86400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-104200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-50400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-83000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-62900</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-70800</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-48100</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-47900</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-23700</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-37500</v>
-      </c>
-      <c r="W89" s="3">
-        <v>-20900</v>
       </c>
       <c r="X89" s="3">
         <v>-20900</v>
       </c>
       <c r="Y89" s="3">
+        <v>-20900</v>
+      </c>
+      <c r="Z89" s="3">
         <v>-100</v>
-      </c>
-      <c r="Z89" s="3">
-        <v>-300</v>
       </c>
       <c r="AA89" s="3">
         <v>-300</v>
       </c>
       <c r="AB89" s="3">
+        <v>-300</v>
+      </c>
+      <c r="AC89" s="3">
         <v>-700</v>
       </c>
-      <c r="AC89" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD89" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="90" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AD89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7042,77 +7262,78 @@
       <c r="AB90" s="3"/>
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
-    </row>
-    <row r="91" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE90" s="3"/>
+    </row>
+    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1100</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-1300</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-1100</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-1900</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-2800</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-3800</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-3500</v>
-      </c>
-      <c r="K91" s="3">
-        <v>-4800</v>
       </c>
       <c r="L91" s="3">
         <v>-4800</v>
       </c>
       <c r="M91" s="3">
+        <v>-4800</v>
+      </c>
+      <c r="N91" s="3">
         <v>-4000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-5800</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-4400</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-5300</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-5700</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-3200</v>
-      </c>
-      <c r="S91" s="3">
-        <v>-4300</v>
       </c>
       <c r="T91" s="3">
         <v>-4300</v>
       </c>
       <c r="U91" s="3">
+        <v>-4300</v>
+      </c>
+      <c r="V91" s="3">
         <v>-3700</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-4100</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-2600</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-3000</v>
       </c>
-      <c r="Y91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z91" s="3" t="s">
         <v>3</v>
       </c>
@@ -7122,14 +7343,17 @@
       <c r="AB91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AC91" s="3">
-        <v>0</v>
+      <c r="AC91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AD91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7214,8 +7438,11 @@
       <c r="AD92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7300,85 +7527,88 @@
       <c r="AD93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E94" s="3">
         <v>-1100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-1300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-1100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-1900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-2800</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-3800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-3500</v>
-      </c>
-      <c r="K94" s="3">
-        <v>-4800</v>
       </c>
       <c r="L94" s="3">
         <v>-4800</v>
       </c>
       <c r="M94" s="3">
+        <v>-4800</v>
+      </c>
+      <c r="N94" s="3">
         <v>-4000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>99200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>100600</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>69700</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-290500</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-5900</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-4300</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-209600</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-3700</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-4100</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-2600</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-3000</v>
       </c>
-      <c r="Y94" s="3">
-        <v>0</v>
-      </c>
       <c r="Z94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA94" s="3">
         <v>100</v>
       </c>
-      <c r="AA94" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB94" s="3" t="s">
-        <v>3</v>
+      <c r="AB94" s="3">
+        <v>0</v>
       </c>
       <c r="AC94" s="3" t="s">
         <v>3</v>
@@ -7386,8 +7616,11 @@
       <c r="AD94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7418,8 +7651,9 @@
       <c r="AB95" s="3"/>
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
-    </row>
-    <row r="96" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE95" s="3"/>
+    </row>
+    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7456,8 +7690,8 @@
       <c r="N96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
+      <c r="O96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P96" s="3">
         <v>0</v>
@@ -7504,8 +7738,11 @@
       <c r="AD96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7590,8 +7827,11 @@
       <c r="AD97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7676,8 +7916,11 @@
       <c r="AD98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7762,162 +8005,168 @@
       <c r="AD99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-38100</v>
+      </c>
+      <c r="E100" s="3">
         <v>10000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>5700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>2400</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>12100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>9500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>5900</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>1000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>5800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>236700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>40300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>23800</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>54900</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>14400</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>500</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>303100</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>2500</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>5600</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>35600</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>506000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>200</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>3400</v>
       </c>
-      <c r="Y100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AA100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB100" s="3">
         <v>-100</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>315500</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>100</v>
       </c>
-      <c r="AD100" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="101" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="E101" s="3">
         <v>100</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>500</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-600</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>800</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-1500</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>300</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>500</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>800</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-500</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-100</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-1000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>800</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-500</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-100</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-1000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-300</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-700</v>
       </c>
-      <c r="U101" s="3">
-        <v>0</v>
-      </c>
       <c r="V101" s="3">
         <v>0</v>
       </c>
       <c r="W101" s="3">
+        <v>0</v>
+      </c>
+      <c r="X101" s="3">
         <v>100</v>
       </c>
-      <c r="X101" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y101" s="3" t="s">
-        <v>3</v>
+      <c r="Y101" s="3">
+        <v>0</v>
       </c>
       <c r="Z101" s="3" t="s">
         <v>3</v>
@@ -7928,96 +8177,102 @@
       <c r="AB101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AC101" s="3">
-        <v>0</v>
+      <c r="AC101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AD101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-39000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-13600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-1800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-28600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>5200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-23900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-48600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-65600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-39600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>133500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-49800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>19200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>105900</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-352900</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>225300</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-50300</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-252600</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>8300</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>464300</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-23200</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-20400</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-100</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-200</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-400</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>800</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>100</v>
       </c>
-      <c r="AD102" s="3" t="s">
+      <c r="AE102" s="3" t="s">
         <v>3</v>
       </c>
     </row>
